--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1725,7 +1725,7 @@
         <v>4.611152257665639</v>
       </c>
       <c r="E74" t="n">
-        <v>4.364371699435161</v>
+        <v>4.365643155423357</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -1744,7 +1744,7 @@
         <v>4.578826210648489</v>
       </c>
       <c r="E75" t="n">
-        <v>4.352855257373601</v>
+        <v>4.354141431184346</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
         <v>4.575741375297279</v>
       </c>
       <c r="E76" t="n">
-        <v>4.343805421853684</v>
+        <v>4.345103280569283</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
         <v>4.570578741218473</v>
       </c>
       <c r="E77" t="n">
-        <v>4.33729074083249</v>
+        <v>4.338597076746545</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         <v>4.572646994282532</v>
       </c>
       <c r="E78" t="n">
-        <v>4.334672938290411</v>
+        <v>4.335982696172475</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
         <v>4.566429357671661</v>
       </c>
       <c r="E79" t="n">
-        <v>4.355425952876702</v>
+        <v>4.356708826689592</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
@@ -1839,7 +1839,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="E80" t="n">
-        <v>4.335982696172475</v>
+        <v>4.33729074083249</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -1858,7 +1858,7 @@
         <v>4.547541073151455</v>
       </c>
       <c r="E81" t="n">
-        <v>4.334672938290411</v>
+        <v>4.335982696172475</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
@@ -1877,7 +1877,7 @@
         <v>4.543294782270004</v>
       </c>
       <c r="E82" t="n">
-        <v>4.33729074083249</v>
+        <v>4.338597076746545</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="E83" t="n">
-        <v>4.341204640153626</v>
+        <v>4.342505876511598</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
         <v>4.548599834499697</v>
       </c>
       <c r="E84" t="n">
-        <v>4.351567427189173</v>
+        <v>4.352855257373601</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
@@ -1934,7 +1934,7 @@
         <v>4.543294782270004</v>
       </c>
       <c r="E85" t="n">
-        <v>4.345103280569283</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>4.530446639792155</v>
       </c>
       <c r="E86" t="n">
-        <v>4.356708826689592</v>
+        <v>4.35799005684564</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>4.543294782270004</v>
       </c>
       <c r="E87" t="n">
-        <v>4.361823927356363</v>
+        <v>4.363098624788363</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
         <v>4.523960130562548</v>
       </c>
       <c r="E88" t="n">
-        <v>4.350277936359301</v>
+        <v>4.351567427189173</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>4.498697941477575</v>
       </c>
       <c r="E89" t="n">
-        <v>4.348986780595681</v>
+        <v>4.350277936359301</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
         <v>4.487512142519859</v>
       </c>
       <c r="E91" t="n">
-        <v>4.333361462692601</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
         <v>4.455509411433685</v>
       </c>
       <c r="E92" t="n">
-        <v>4.320151230955794</v>
+        <v>4.321480134805848</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
         <v>4.433194921248282</v>
       </c>
       <c r="E93" t="n">
-        <v>4.320151230955794</v>
+        <v>4.321480134805848</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
         <v>4.387014176184921</v>
       </c>
       <c r="E94" t="n">
-        <v>4.309455941839047</v>
+        <v>4.310799125385514</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
@@ -2143,7 +2143,7 @@
         <v>4.302712827954156</v>
       </c>
       <c r="E96" t="n">
-        <v>4.30406509320417</v>
+        <v>4.305415532302042</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
         <v>4.264087336809195</v>
       </c>
       <c r="E98" t="n">
-        <v>4.290459441148391</v>
+        <v>4.291828366755733</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>4.28496492183075</v>
       </c>
       <c r="E100" t="n">
-        <v>4.278054044290903</v>
+        <v>4.279440045898781</v>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
         <v>4.290459441148391</v>
       </c>
       <c r="E101" t="n">
-        <v>4.275276264727001</v>
+        <v>4.276666119016055</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
         <v>4.301358731606427</v>
       </c>
       <c r="E102" t="n">
-        <v>4.273884476054178</v>
+        <v>4.275276264727001</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
         <v>4.269697449699962</v>
       </c>
       <c r="E104" t="n">
-        <v>4.259859000699674</v>
+        <v>4.261270433538082</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
         <v>4.297285406218791</v>
       </c>
       <c r="E105" t="n">
-        <v>4.275276264727001</v>
+        <v>4.276666119016055</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
         <v>4.394449154672439</v>
       </c>
       <c r="E109" t="n">
-        <v>4.282206299391671</v>
+        <v>4.283586561860629</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -2411,7 +2411,7 @@
         <v>4.417635062141249</v>
       </c>
       <c r="E110" t="n">
-        <v>4.283586561860629</v>
+        <v>4.28496492183075</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
         <v>4.534747721691546</v>
       </c>
       <c r="E113" t="n">
-        <v>4.314817884980432</v>
+        <v>4.316153890523174</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
@@ -2495,7 +2495,7 @@
         <v>4.553876891600541</v>
       </c>
       <c r="E114" t="n">
-        <v>4.313480092138771</v>
+        <v>4.314817884980432</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
         <v>4.566429357671661</v>
       </c>
       <c r="E115" t="n">
-        <v>4.320151230955794</v>
+        <v>4.321480134805848</v>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
         <v>4.597138014290827</v>
       </c>
       <c r="E116" t="n">
-        <v>4.32280727501391</v>
+        <v>4.324132656254979</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
         <v>4.612145799724517</v>
       </c>
       <c r="E117" t="n">
-        <v>4.324132656254979</v>
+        <v>4.325456283185487</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
         <v>4.638604962074329</v>
       </c>
       <c r="E118" t="n">
-        <v>4.33204826486764</v>
+        <v>4.333361462692601</v>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
         <v>4.65681341913993</v>
       </c>
       <c r="E119" t="n">
-        <v>4.342505876511598</v>
+        <v>4.343805421853684</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
         <v>4.653960350157523</v>
       </c>
       <c r="E120" t="n">
-        <v>4.347693955593376</v>
+        <v>4.348986780595681</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
         <v>4.658710952916121</v>
       </c>
       <c r="E121" t="n">
-        <v>4.359269647551265</v>
+        <v>4.360547602996758</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
         <v>4.651099117876491</v>
       </c>
       <c r="E122" t="n">
-        <v>4.354141431184346</v>
+        <v>4.355425952876702</v>
       </c>
       <c r="F122" t="n">
         <v>4.691347882229143</v>
@@ -2686,7 +2686,7 @@
         <v>4.654912277882906</v>
       </c>
       <c r="E123" t="n">
-        <v>4.352855257373601</v>
+        <v>4.354141431184346</v>
       </c>
       <c r="F123" t="n">
         <v>4.780802754631249</v>
@@ -2711,7 +2711,7 @@
         <v>4.636668853047462</v>
       </c>
       <c r="E124" t="n">
-        <v>4.354141431184346</v>
+        <v>4.355425952876702</v>
       </c>
       <c r="F124" t="n">
         <v>4.74493212836325</v>
@@ -2734,7 +2734,7 @@
         <v>4.664382045619937</v>
       </c>
       <c r="E125" t="n">
-        <v>4.356708826689592</v>
+        <v>4.35799005684564</v>
       </c>
       <c r="F125" t="n">
         <v>4.746669748261791</v>
@@ -2757,7 +2757,7 @@
         <v>4.65586330030361</v>
       </c>
       <c r="E126" t="n">
-        <v>4.360547602996758</v>
+        <v>4.361823927356363</v>
       </c>
       <c r="F126" t="n">
         <v>4.747537427275013</v>
@@ -2782,7 +2782,7 @@
         <v>4.653960350157523</v>
       </c>
       <c r="E127" t="n">
-        <v>4.35799005684564</v>
+        <v>4.359269647551265</v>
       </c>
       <c r="F127" t="n">
         <v>4.739701078945697</v>
@@ -2805,7 +2805,7 @@
         <v>4.65586330030361</v>
       </c>
       <c r="E128" t="n">
-        <v>4.355425952876702</v>
+        <v>4.356708826689592</v>
       </c>
       <c r="F128" t="n">
         <v>4.74406218485471</v>
@@ -2828,7 +2828,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="E129" t="n">
-        <v>4.354141431184346</v>
+        <v>4.355425952876702</v>
       </c>
       <c r="F129" t="n">
         <v>4.754451888703846</v>
@@ -2853,7 +2853,7 @@
         <v>4.619073091157083</v>
       </c>
       <c r="E130" t="n">
-        <v>4.361823927356363</v>
+        <v>4.363098624788363</v>
       </c>
       <c r="F130" t="n">
         <v>4.729156165769083</v>
@@ -2876,7 +2876,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="E131" t="n">
-        <v>4.347693955593376</v>
+        <v>4.348986780595681</v>
       </c>
       <c r="F131" t="n">
         <v>4.745801315727837</v>
@@ -2899,7 +2899,7 @@
         <v>4.575741375297279</v>
       </c>
       <c r="E132" t="n">
-        <v>4.351567427189173</v>
+        <v>4.352855257373601</v>
       </c>
       <c r="F132" t="n">
         <v>4.760463070394127</v>
@@ -2924,7 +2924,7 @@
         <v>4.560172820057356</v>
       </c>
       <c r="E133" t="n">
-        <v>4.363098624788363</v>
+        <v>4.364371699435161</v>
       </c>
       <c r="F133" t="n">
         <v>4.715816706075155</v>
@@ -2947,7 +2947,7 @@
         <v>4.55597994179732</v>
       </c>
       <c r="E134" t="n">
-        <v>4.354141431184346</v>
+        <v>4.355425952876702</v>
       </c>
       <c r="F134" t="n">
         <v>4.649187071404866</v>
@@ -2970,7 +2970,7 @@
         <v>4.525044141508807</v>
       </c>
       <c r="E135" t="n">
-        <v>4.352855257373601</v>
+        <v>4.354141431184346</v>
       </c>
       <c r="F135" t="n">
         <v>4.564348191467836</v>
@@ -2995,7 +2995,7 @@
         <v>4.52178857704904</v>
       </c>
       <c r="E136" t="n">
-        <v>4.351567427189173</v>
+        <v>4.352855257373601</v>
       </c>
       <c r="F136" t="n">
         <v>4.643428898105181</v>
@@ -3018,7 +3018,7 @@
         <v>4.52178857704904</v>
       </c>
       <c r="E137" t="n">
-        <v>4.342505876511598</v>
+        <v>4.343805421853684</v>
       </c>
       <c r="F137" t="n">
         <v>4.71760561531788</v>
@@ -3041,7 +3041,7 @@
         <v>4.519612297626445</v>
       </c>
       <c r="E138" t="n">
-        <v>4.352855257373601</v>
+        <v>4.354141431184346</v>
       </c>
       <c r="F138" t="n">
         <v>4.720282993088596</v>
@@ -3066,7 +3066,7 @@
         <v>4.52720864451838</v>
       </c>
       <c r="E139" t="n">
-        <v>4.355425952876702</v>
+        <v>4.356708826689592</v>
       </c>
       <c r="F139" t="n">
         <v>4.73707525686803</v>
@@ -3089,7 +3089,7 @@
         <v>4.530446639792155</v>
       </c>
       <c r="E140" t="n">
-        <v>4.345103280569283</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="F140" t="n">
         <v>4.712229258281499</v>
@@ -3112,7 +3112,7 @@
         <v>4.553876891600541</v>
       </c>
       <c r="E141" t="n">
-        <v>4.35799005684564</v>
+        <v>4.359269647551265</v>
       </c>
       <c r="F141" t="n">
         <v>4.722063937459591</v>
@@ -3137,7 +3137,7 @@
         <v>4.564348191467836</v>
       </c>
       <c r="E142" t="n">
-        <v>4.35799005684564</v>
+        <v>4.359269647551265</v>
       </c>
       <c r="F142" t="n">
         <v>4.731802836921458</v>
@@ -3160,7 +3160,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="E143" t="n">
-        <v>4.354141431184346</v>
+        <v>4.355425952876702</v>
       </c>
       <c r="F143" t="n">
         <v>4.694096395182493</v>
@@ -3183,7 +3183,7 @@
         <v>4.593097604753822</v>
       </c>
       <c r="E144" t="n">
-        <v>4.360547602996758</v>
+        <v>4.361823927356363</v>
       </c>
       <c r="F144" t="n">
         <v>4.688591794127164</v>
@@ -3208,7 +3208,7 @@
         <v>4.599152113662528</v>
       </c>
       <c r="E145" t="n">
-        <v>4.360547602996758</v>
+        <v>4.361823927356363</v>
       </c>
       <c r="F145" t="n">
         <v>4.712229258281499</v>
@@ -3231,7 +3231,7 @@
         <v>4.609162207257629</v>
       </c>
       <c r="E146" t="n">
-        <v>4.360547602996758</v>
+        <v>4.361823927356363</v>
       </c>
       <c r="F146" t="n">
         <v>4.571613402459248</v>
@@ -3254,7 +3254,7 @@
         <v>4.623010104116422</v>
       </c>
       <c r="E147" t="n">
-        <v>4.366912996863833</v>
+        <v>4.368181227851829</v>
       </c>
       <c r="F147" t="n">
         <v>4.671893818030999</v>
@@ -3279,7 +3279,7 @@
         <v>4.628886712605407</v>
       </c>
       <c r="E148" t="n">
-        <v>4.380775852772229</v>
+        <v>4.382026634673881</v>
       </c>
       <c r="F148" t="n">
         <v>4.674696248636701</v>
@@ -3302,7 +3302,7 @@
         <v>4.626931677769604</v>
       </c>
       <c r="E149" t="n">
-        <v>4.390738575275903</v>
+        <v>4.39197696552705</v>
       </c>
       <c r="F149" t="n">
         <v>4.683056724645162</v>
@@ -3325,7 +3325,7 @@
         <v>4.652053771886941</v>
       </c>
       <c r="E150" t="n">
-        <v>4.379523504455763</v>
+        <v>4.380775852772229</v>
       </c>
       <c r="F150" t="n">
         <v>4.665324108807838</v>
@@ -3373,7 +3373,7 @@
         <v>4.664382045619937</v>
       </c>
       <c r="E152" t="n">
-        <v>4.406719247264253</v>
+        <v>4.407938016458383</v>
       </c>
       <c r="F152" t="n">
         <v>4.683056724645162</v>
@@ -3396,7 +3396,7 @@
         <v>4.675628649636653</v>
       </c>
       <c r="E153" t="n">
-        <v>4.405498990859024</v>
+        <v>4.406719247264253</v>
       </c>
       <c r="F153" t="n">
         <v>4.671893818030999</v>
@@ -3421,7 +3421,7 @@
         <v>4.692264892839025</v>
       </c>
       <c r="E154" t="n">
-        <v>4.404277243608702</v>
+        <v>4.405498990859024</v>
       </c>
       <c r="F154" t="n">
         <v>4.684905154006945</v>
@@ -3444,7 +3444,7 @@
         <v>4.69866052907543</v>
       </c>
       <c r="E155" t="n">
-        <v>4.420044701861403</v>
+        <v>4.421247347827163</v>
       </c>
       <c r="F155" t="n">
         <v>4.679349584162343</v>
@@ -3467,7 +3467,7 @@
         <v>4.708628894356321</v>
       </c>
       <c r="E156" t="n">
-        <v>4.417635062141249</v>
+        <v>4.418840607796598</v>
       </c>
       <c r="F156" t="n">
         <v>4.669083511731744</v>
@@ -3492,7 +3492,7 @@
         <v>4.716711560720999</v>
       </c>
       <c r="E157" t="n">
-        <v>4.42484663185681</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="F157" t="n">
         <v>4.676560182074764</v>
@@ -3515,7 +3515,7 @@
         <v>4.714024590900173</v>
       </c>
       <c r="E158" t="n">
-        <v>4.427238977495429</v>
+        <v>4.428433007488037</v>
       </c>
       <c r="F158" t="n">
         <v>4.670021158307708</v>
@@ -3538,7 +3538,7 @@
         <v>4.721173861744398</v>
       </c>
       <c r="E159" t="n">
-        <v>4.433194921248282</v>
+        <v>4.43438186500781</v>
       </c>
       <c r="F159" t="n">
         <v>4.662495252607361</v>
@@ -3563,7 +3563,7 @@
         <v>4.73356340075649</v>
       </c>
       <c r="E160" t="n">
-        <v>4.433194921248282</v>
+        <v>4.43438186500781</v>
       </c>
       <c r="F160" t="n">
         <v>4.670957926526095</v>
@@ -3609,7 +3609,7 @@
         <v>4.711330381816482</v>
       </c>
       <c r="E162" t="n">
-        <v>4.440295542797857</v>
+        <v>4.441474093317302</v>
       </c>
       <c r="F162" t="n">
         <v>4.666265285347902</v>
@@ -3634,7 +3634,7 @@
         <v>4.726502471155617</v>
       </c>
       <c r="E163" t="n">
-        <v>4.43438186500781</v>
+        <v>4.435567401601912</v>
       </c>
       <c r="F163" t="n">
         <v>4.66814498514948</v>
@@ -3657,7 +3657,7 @@
         <v>4.724729421045731</v>
       </c>
       <c r="E164" t="n">
-        <v>4.446174454497633</v>
+        <v>4.447346100794524</v>
       </c>
       <c r="F164" t="n">
         <v>4.670021158307708</v>
@@ -3680,7 +3680,7 @@
         <v>4.72384171570559</v>
       </c>
       <c r="E165" t="n">
-        <v>4.433194921248282</v>
+        <v>4.43438186500781</v>
       </c>
       <c r="F165" t="n">
         <v>4.657762636107262</v>
@@ -3705,7 +3705,7 @@
         <v>4.705920089088234</v>
       </c>
       <c r="E166" t="n">
-        <v>4.43438186500781</v>
+        <v>4.435567401601912</v>
       </c>
       <c r="F166" t="n">
         <v>4.664382045619937</v>
@@ -3728,7 +3728,7 @@
         <v>4.687671407499835</v>
       </c>
       <c r="E167" t="n">
-        <v>4.436751534363128</v>
+        <v>4.437934266612178</v>
       </c>
       <c r="F167" t="n">
         <v>4.658710952916121</v>
@@ -3776,7 +3776,7 @@
         <v>4.692264892839025</v>
       </c>
       <c r="E169" t="n">
-        <v>4.42484663185681</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="F169" t="n">
         <v>4.637637376125593</v>
@@ -3799,7 +3799,7 @@
         <v>4.65586330030361</v>
       </c>
       <c r="E170" t="n">
-        <v>4.441474093317302</v>
+        <v>4.442651256490317</v>
       </c>
       <c r="F170" t="n">
         <v>4.705015520957808</v>
@@ -3824,7 +3824,7 @@
         <v>4.660604892876192</v>
       </c>
       <c r="E171" t="n">
-        <v>4.428433007488037</v>
+        <v>4.429625613473161</v>
       </c>
       <c r="F171" t="n">
         <v>4.620058798481842</v>
@@ -3851,7 +3851,7 @@
         <v>4.65586330030361</v>
       </c>
       <c r="E172" t="n">
-        <v>4.432006566978902</v>
+        <v>4.433194921248282</v>
       </c>
       <c r="F172" t="n">
         <v>4.701389043728634</v>
@@ -3876,7 +3876,7 @@
         <v>4.632785353021065</v>
       </c>
       <c r="E173" t="n">
-        <v>4.435567401601912</v>
+        <v>4.436751534363128</v>
       </c>
       <c r="F173" t="n">
         <v>4.691347882229143</v>
@@ -3901,7 +3901,7 @@
         <v>4.644390899141372</v>
       </c>
       <c r="E174" t="n">
-        <v>4.440295542797857</v>
+        <v>4.441474093317302</v>
       </c>
       <c r="F174" t="n">
         <v>4.695010889987881</v>
@@ -3928,7 +3928,7 @@
         <v>4.65681341913993</v>
       </c>
       <c r="E175" t="n">
-        <v>4.44500143383527</v>
+        <v>4.446174454497633</v>
       </c>
       <c r="F175" t="n">
         <v>4.693181063310805</v>
@@ -3953,7 +3953,7 @@
         <v>4.65681341913993</v>
       </c>
       <c r="E176" t="n">
-        <v>4.454347296253507</v>
+        <v>4.455509411433685</v>
       </c>
       <c r="F176" t="n">
         <v>4.706823839714591</v>
@@ -3978,7 +3978,7 @@
         <v>4.672828834461906</v>
       </c>
       <c r="E177" t="n">
-        <v>4.454347296253507</v>
+        <v>4.455509411433685</v>
       </c>
       <c r="F177" t="n">
         <v>4.694096395182493</v>
@@ -4005,7 +4005,7 @@
         <v>4.695010889987881</v>
       </c>
       <c r="E178" t="n">
-        <v>4.461299815568389</v>
+        <v>4.462453883786496</v>
       </c>
       <c r="F178" t="n">
         <v>4.704110133842995</v>
@@ -4030,7 +4030,7 @@
         <v>4.729156165769083</v>
       </c>
       <c r="E179" t="n">
-        <v>4.471638793363569</v>
+        <v>4.472780997942346</v>
       </c>
       <c r="F179" t="n">
         <v>4.711330381816482</v>
@@ -4055,7 +4055,7 @@
         <v>4.745801315727837</v>
       </c>
       <c r="E180" t="n">
-        <v>4.473921899378137</v>
+        <v>4.475061500641071</v>
       </c>
       <c r="F180" t="n">
         <v>4.709530201312334</v>
@@ -4082,7 +4082,7 @@
         <v>4.749270529961848</v>
       </c>
       <c r="E181" t="n">
-        <v>4.473921899378137</v>
+        <v>4.475061500641071</v>
       </c>
       <c r="F181" t="n">
         <v>4.69866052907543</v>
@@ -4109,7 +4109,7 @@
         <v>4.752727750345706</v>
       </c>
       <c r="E182" t="n">
-        <v>4.471638793363569</v>
+        <v>4.472780997942346</v>
       </c>
       <c r="F182" t="n">
         <v>4.708628894356321</v>
@@ -4140,7 +4140,7 @@
         <v>4.774912960575186</v>
       </c>
       <c r="E183" t="n">
-        <v>4.484131857611035</v>
+        <v>4.485259889315534</v>
       </c>
       <c r="F183" t="n">
         <v>4.73444252169223</v>
@@ -4173,7 +4173,7 @@
         <v>4.783316371371566</v>
       </c>
       <c r="E184" t="n">
-        <v>4.486386649998124</v>
+        <v>4.487512142519859</v>
       </c>
       <c r="F184" t="n">
         <v>4.719391330078114</v>
@@ -4204,7 +4204,7 @@
         <v>4.763881877142913</v>
       </c>
       <c r="E185" t="n">
-        <v>4.497584975308154</v>
+        <v>4.498697941477575</v>
       </c>
       <c r="F185" t="n">
         <v>4.709530201312334</v>
@@ -4235,7 +4235,7 @@
         <v>4.776599301615622</v>
       </c>
       <c r="E186" t="n">
-        <v>4.51085950651685</v>
+        <v>4.511957804265912</v>
       </c>
       <c r="F186" t="n">
         <v>4.73707525686803</v>
@@ -4268,7 +4268,7 @@
         <v>4.757032535297338</v>
       </c>
       <c r="E187" t="n">
-        <v>4.497584975308154</v>
+        <v>4.498697941477575</v>
       </c>
       <c r="F187" t="n">
         <v>4.705015520957808</v>
@@ -4299,7 +4299,7 @@
         <v>4.762173934797756</v>
       </c>
       <c r="E188" t="n">
-        <v>4.508659285607248</v>
+        <v>4.509760001183433</v>
       </c>
       <c r="F188" t="n">
         <v>4.706823839714591</v>
@@ -4330,7 +4330,7 @@
         <v>4.766438333584214</v>
       </c>
       <c r="E189" t="n">
-        <v>4.509760001183433</v>
+        <v>4.51085950651685</v>
       </c>
       <c r="F189" t="n">
         <v>4.728272383122075</v>
@@ -4363,7 +4363,7 @@
         <v>4.745801315727837</v>
       </c>
       <c r="E190" t="n">
-        <v>4.51085950651685</v>
+        <v>4.511957804265912</v>
       </c>
       <c r="F190" t="n">
         <v>4.705015520957808</v>
@@ -4394,7 +4394,7 @@
         <v>4.756173059524619</v>
       </c>
       <c r="E191" t="n">
-        <v>4.511957804265912</v>
+        <v>4.513054897080286</v>
       </c>
       <c r="F191" t="n">
         <v>4.696837374513915</v>
@@ -4425,7 +4425,7 @@
         <v>4.750135956238277</v>
       </c>
       <c r="E192" t="n">
-        <v>4.52178857704904</v>
+        <v>4.522874943261261</v>
       </c>
       <c r="F192" t="n">
         <v>4.711330381816482</v>
@@ -4458,7 +4458,7 @@
         <v>4.743191483885466</v>
       </c>
       <c r="E193" t="n">
-        <v>4.528289141652134</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="F193" t="n">
         <v>4.752727750345706</v>
@@ -4489,7 +4489,7 @@
         <v>4.73795129722191</v>
       </c>
       <c r="E194" t="n">
-        <v>4.520701029361642</v>
+        <v>4.52178857704904</v>
       </c>
       <c r="F194" t="n">
         <v>4.71492104994721</v>
@@ -4520,7 +4520,7 @@
         <v>4.706823839714591</v>
       </c>
       <c r="E195" t="n">
-        <v>4.523960130562548</v>
+        <v>4.525044141508807</v>
       </c>
       <c r="F195" t="n">
         <v>4.725616339063959</v>
@@ -4553,7 +4553,7 @@
         <v>4.689511334421843</v>
       </c>
       <c r="E196" t="n">
-        <v>4.519612297626445</v>
+        <v>4.520701029361642</v>
       </c>
       <c r="F196" t="n">
         <v>4.692264892839025</v>
@@ -4584,7 +4584,7 @@
         <v>4.658710952916121</v>
       </c>
       <c r="E197" t="n">
-        <v>4.509760001183433</v>
+        <v>4.51085950651685</v>
       </c>
       <c r="F197" t="n">
         <v>4.691347882229143</v>
@@ -4615,7 +4615,7 @@
         <v>4.636668853047462</v>
       </c>
       <c r="E198" t="n">
-        <v>4.514150787600923</v>
+        <v>4.515245478460105</v>
       </c>
       <c r="F198" t="n">
         <v>4.719391330078114</v>
@@ -4648,7 +4648,7 @@
         <v>4.629862798578463</v>
       </c>
       <c r="E199" t="n">
-        <v>4.514150787600923</v>
+        <v>4.515245478460105</v>
       </c>
       <c r="F199" t="n">
         <v>4.71760561531788</v>
@@ -4679,7 +4679,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="E200" t="n">
-        <v>4.49423862528081</v>
+        <v>4.495355319980884</v>
       </c>
       <c r="F200" t="n">
         <v>4.705920089088234</v>
@@ -4710,7 +4710,7 @@
         <v>4.606169686321175</v>
       </c>
       <c r="E201" t="n">
-        <v>4.51852237926242</v>
+        <v>4.519612297626445</v>
       </c>
       <c r="F201" t="n">
         <v>4.719391330078114</v>
@@ -4743,7 +4743,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="E202" t="n">
-        <v>4.505349850705881</v>
+        <v>4.506454213048934</v>
       </c>
       <c r="F202" t="n">
         <v>4.710430696645584</v>
@@ -4774,7 +4774,7 @@
         <v>4.533674184283021</v>
       </c>
       <c r="E203" t="n">
-        <v>4.489759334476764</v>
+        <v>4.490881039585964</v>
       </c>
       <c r="F203" t="n">
         <v>4.724729421045731</v>
@@ -4805,7 +4805,7 @@
         <v>4.506454213048934</v>
       </c>
       <c r="E204" t="n">
-        <v>4.484131857611035</v>
+        <v>4.485259889315534</v>
       </c>
       <c r="F204" t="n">
         <v>4.71492104994721</v>
@@ -4838,7 +4838,7 @@
         <v>4.536891345234797</v>
       </c>
       <c r="E205" t="n">
-        <v>4.493120682179469</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="F205" t="n">
         <v>4.730039168033961</v>
@@ -4869,7 +4869,7 @@
         <v>4.564348191467836</v>
       </c>
       <c r="E206" t="n">
-        <v>4.493120682179469</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="F206" t="n">
         <v>4.71492104994721</v>
@@ -4900,7 +4900,7 @@
         <v>4.571613402459248</v>
       </c>
       <c r="E207" t="n">
-        <v>4.49423862528081</v>
+        <v>4.495355319980884</v>
       </c>
       <c r="F207" t="n">
         <v>4.727387818712341</v>
@@ -4933,7 +4933,7 @@
         <v>4.591071261608589</v>
       </c>
       <c r="E208" t="n">
-        <v>4.503137460422939</v>
+        <v>4.504244267398131</v>
       </c>
       <c r="F208" t="n">
         <v>4.724729421045731</v>
@@ -4964,7 +4964,7 @@
         <v>4.580877493419047</v>
       </c>
       <c r="E209" t="n">
-        <v>4.500920164614292</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="F209" t="n">
         <v>4.702296896718814</v>
@@ -4995,7 +4995,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="E210" t="n">
-        <v>4.505349850705881</v>
+        <v>4.506454213048934</v>
       </c>
       <c r="F210" t="n">
         <v>4.69866052907543</v>
@@ -5028,7 +5028,7 @@
         <v>4.56746831880408</v>
       </c>
       <c r="E211" t="n">
-        <v>4.509760001183433</v>
+        <v>4.511957804265912</v>
       </c>
       <c r="F211" t="n">
         <v>4.69866052907543</v>
@@ -5059,7 +5059,7 @@
         <v>4.554928969551344</v>
       </c>
       <c r="E212" t="n">
-        <v>4.502029427068578</v>
+        <v>4.503137460422939</v>
       </c>
       <c r="F212" t="n">
         <v>4.695010889987881</v>
@@ -5090,7 +5090,7 @@
         <v>4.529368472571809</v>
       </c>
       <c r="E213" t="n">
-        <v>4.506454213048934</v>
+        <v>4.507557357121091</v>
       </c>
       <c r="F213" t="n">
         <v>4.708628894356321</v>
@@ -5123,7 +5123,7 @@
         <v>4.547541073151455</v>
       </c>
       <c r="E214" t="n">
-        <v>4.51085950651685</v>
+        <v>4.511957804265912</v>
       </c>
       <c r="F214" t="n">
         <v>4.716711560720999</v>
@@ -5154,7 +5154,7 @@
         <v>4.529368472571809</v>
       </c>
       <c r="E215" t="n">
-        <v>4.506454213048934</v>
+        <v>4.507557357121091</v>
       </c>
       <c r="F215" t="n">
         <v>4.702296896718814</v>
@@ -5185,7 +5185,7 @@
         <v>4.52720864451838</v>
       </c>
       <c r="E216" t="n">
-        <v>4.509760001183433</v>
+        <v>4.51085950651685</v>
       </c>
       <c r="F216" t="n">
         <v>4.709530201312334</v>
@@ -5218,7 +5218,7 @@
         <v>4.515245478460105</v>
       </c>
       <c r="E217" t="n">
-        <v>4.495355319980884</v>
+        <v>4.49647076906475</v>
       </c>
       <c r="F217" t="n">
         <v>4.703203926259457</v>
@@ -5249,7 +5249,7 @@
         <v>4.522874943261261</v>
       </c>
       <c r="E218" t="n">
-        <v>4.509760001183433</v>
+        <v>4.51085950651685</v>
       </c>
       <c r="F218" t="n">
         <v>4.689511334421843</v>
@@ -5280,7 +5280,7 @@
         <v>4.526126978647638</v>
       </c>
       <c r="E219" t="n">
-        <v>4.513054897080286</v>
+        <v>4.514150787600923</v>
       </c>
       <c r="F219" t="n">
         <v>4.684905154006945</v>
@@ -5313,7 +5313,7 @@
         <v>4.507557357121091</v>
       </c>
       <c r="E220" t="n">
-        <v>4.505349850705881</v>
+        <v>4.506454213048934</v>
       </c>
       <c r="F220" t="n">
         <v>4.726502471155617</v>
@@ -5344,7 +5344,7 @@
         <v>4.514150787600923</v>
       </c>
       <c r="E221" t="n">
-        <v>4.509760001183433</v>
+        <v>4.51085950651685</v>
       </c>
       <c r="F221" t="n">
         <v>4.713127327493184</v>
@@ -5375,7 +5375,7 @@
         <v>4.51085950651685</v>
       </c>
       <c r="E222" t="n">
-        <v>4.492001487882454</v>
+        <v>4.493120682179469</v>
       </c>
       <c r="F222" t="n">
         <v>4.699570861409576</v>
@@ -5408,7 +5408,7 @@
         <v>4.52178857704904</v>
       </c>
       <c r="E223" t="n">
-        <v>4.493120682179469</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="F223" t="n">
         <v>4.715816706075155</v>
@@ -5439,7 +5439,7 @@
         <v>4.52720864451838</v>
       </c>
       <c r="E224" t="n">
-        <v>4.509760001183433</v>
+        <v>4.51085950651685</v>
       </c>
       <c r="F224" t="n">
         <v>4.712229258281499</v>
@@ -5470,7 +5470,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="E225" t="n">
-        <v>4.497584975308154</v>
+        <v>4.498697941477575</v>
       </c>
       <c r="F225" t="n">
         <v>4.683056724645162</v>
@@ -5503,7 +5503,7 @@
         <v>4.558078578454241</v>
       </c>
       <c r="E226" t="n">
-        <v>4.49423862528081</v>
+        <v>4.495355319980884</v>
       </c>
       <c r="F226" t="n">
         <v>4.700480365792417</v>
@@ -5534,7 +5534,7 @@
         <v>4.575741375297279</v>
       </c>
       <c r="E227" t="n">
-        <v>4.52178857704904</v>
+        <v>4.523960130562548</v>
       </c>
       <c r="F227" t="n">
         <v>4.696837374513915</v>
@@ -5565,7 +5565,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E228" t="n">
-        <v>4.519612297626445</v>
+        <v>4.52178857704904</v>
       </c>
       <c r="F228" t="n">
         <v>4.697749367281185</v>
@@ -5598,7 +5598,7 @@
         <v>4.591071261608589</v>
       </c>
       <c r="E229" t="n">
-        <v>4.519612297626445</v>
+        <v>4.520701029361642</v>
       </c>
       <c r="F229" t="n">
         <v>4.713127327493184</v>
@@ -5629,7 +5629,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="E230" t="n">
-        <v>4.517431271680085</v>
+        <v>4.51852237926242</v>
       </c>
       <c r="F230" t="n">
         <v>4.695010889987881</v>
@@ -5660,7 +5660,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="E231" t="n">
-        <v>4.526126978647638</v>
+        <v>4.52720864451838</v>
       </c>
       <c r="F231" t="n">
         <v>4.713127327493184</v>
@@ -5693,7 +5693,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E232" t="n">
-        <v>4.520701029361642</v>
+        <v>4.52178857704904</v>
       </c>
       <c r="F232" t="n">
         <v>4.706823839714591</v>
@@ -5724,7 +5724,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="E233" t="n">
-        <v>4.530446639792155</v>
+        <v>4.532599493153256</v>
       </c>
       <c r="F233" t="n">
         <v>4.700480365792417</v>
@@ -5755,7 +5755,7 @@
         <v>4.607168188650764</v>
       </c>
       <c r="E234" t="n">
-        <v>4.532599493153256</v>
+        <v>4.533674184283021</v>
       </c>
       <c r="F234" t="n">
         <v>4.696837374513915</v>
@@ -5788,7 +5788,7 @@
         <v>4.60816569496789</v>
       </c>
       <c r="E235" t="n">
-        <v>4.531523645819793</v>
+        <v>4.532599493153256</v>
       </c>
       <c r="F235" t="n">
         <v>4.69866052907543</v>
@@ -5819,7 +5819,7 @@
         <v>4.609162207257629</v>
       </c>
       <c r="E236" t="n">
-        <v>4.540098189244376</v>
+        <v>4.541164856012179</v>
       </c>
       <c r="F236" t="n">
         <v>4.697749367281185</v>
@@ -5850,7 +5850,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="E237" t="n">
-        <v>4.520701029361642</v>
+        <v>4.52178857704904</v>
       </c>
       <c r="F237" t="n">
         <v>4.676560182074764</v>
@@ -5883,7 +5883,7 @@
         <v>4.613138355637268</v>
       </c>
       <c r="E238" t="n">
-        <v>4.533674184283021</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F238" t="n">
         <v>4.695010889987881</v>
@@ -5914,7 +5914,7 @@
         <v>4.61512051684126</v>
       </c>
       <c r="E239" t="n">
-        <v>4.537961436294641</v>
+        <v>4.540098189244376</v>
       </c>
       <c r="F239" t="n">
         <v>4.701389043728634</v>
@@ -5945,7 +5945,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="E240" t="n">
-        <v>4.52720864451838</v>
+        <v>4.528289141652134</v>
       </c>
       <c r="F240" t="n">
         <v>4.699570861409576</v>
@@ -5978,7 +5978,7 @@
         <v>4.602165676967792</v>
       </c>
       <c r="E241" t="n">
-        <v>4.528289141652134</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="F241" t="n">
         <v>4.683981366412381</v>
@@ -6009,7 +6009,7 @@
         <v>4.611152257665639</v>
       </c>
       <c r="E242" t="n">
-        <v>4.537961436294641</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="F242" t="n">
         <v>4.709530201312334</v>
@@ -6040,7 +6040,7 @@
         <v>4.599152113662528</v>
       </c>
       <c r="E243" t="n">
-        <v>4.534747721691546</v>
+        <v>4.535820107853298</v>
       </c>
       <c r="F243" t="n">
         <v>4.685828089005546</v>
@@ -6073,7 +6073,7 @@
         <v>4.589040804058207</v>
       </c>
       <c r="E244" t="n">
-        <v>4.534747721691546</v>
+        <v>4.535820107853298</v>
       </c>
       <c r="F244" t="n">
         <v>4.684905154006945</v>
@@ -6104,7 +6104,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="E245" t="n">
-        <v>4.549657476057832</v>
+        <v>4.550714000192032</v>
       </c>
       <c r="F245" t="n">
         <v>4.706823839714591</v>
@@ -6135,7 +6135,7 @@
         <v>4.575741375297279</v>
       </c>
       <c r="E246" t="n">
-        <v>4.535820107853298</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="F246" t="n">
         <v>4.713127327493184</v>
@@ -6168,7 +6168,7 @@
         <v>4.578826210648489</v>
       </c>
       <c r="E247" t="n">
-        <v>4.545420181582317</v>
+        <v>4.546481189639412</v>
       </c>
       <c r="F247" t="n">
         <v>4.706823839714591</v>
@@ -6199,7 +6199,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="E248" t="n">
-        <v>4.550714000192032</v>
+        <v>4.551769409260976</v>
       </c>
       <c r="F248" t="n">
         <v>4.719391330078114</v>
@@ -6230,7 +6230,7 @@
         <v>4.604169685654508</v>
       </c>
       <c r="E249" t="n">
-        <v>4.537961436294641</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="F249" t="n">
         <v>4.719391330078114</v>
@@ -6263,7 +6263,7 @@
         <v>4.611152257665639</v>
       </c>
       <c r="E250" t="n">
-        <v>4.552823705615882</v>
+        <v>4.553876891600541</v>
       </c>
       <c r="F250" t="n">
         <v>4.722063937459591</v>
@@ -6294,7 +6294,7 @@
         <v>4.629862798578463</v>
       </c>
       <c r="E251" t="n">
-        <v>4.554928969551344</v>
+        <v>4.55597994179732</v>
       </c>
       <c r="F251" t="n">
         <v>4.719391330078114</v>
@@ -6325,7 +6325,7 @@
         <v>4.629862798578463</v>
       </c>
       <c r="E252" t="n">
-        <v>4.570578741218473</v>
+        <v>4.571613402459248</v>
       </c>
       <c r="F252" t="n">
         <v>4.716711560720999</v>
@@ -6358,7 +6358,7 @@
         <v>4.643428898105181</v>
       </c>
       <c r="E253" t="n">
-        <v>4.560172820057356</v>
+        <v>4.562262684976814</v>
       </c>
       <c r="F253" t="n">
         <v>4.71492104994721</v>
@@ -6389,7 +6389,7 @@
         <v>4.660604892876192</v>
       </c>
       <c r="E254" t="n">
-        <v>4.5685062016165</v>
+        <v>4.56954300834494</v>
       </c>
       <c r="F254" t="n">
         <v>4.708628894356321</v>
@@ -6420,7 +6420,7 @@
         <v>4.660604892876192</v>
       </c>
       <c r="E255" t="n">
-        <v>4.56746831880408</v>
+        <v>4.5685062016165</v>
       </c>
       <c r="F255" t="n">
         <v>4.713127327493184</v>
@@ -6453,7 +6453,7 @@
         <v>4.670021158307708</v>
       </c>
       <c r="E256" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="F256" t="n">
         <v>4.705920089088234</v>
@@ -6484,7 +6484,7 @@
         <v>4.686750172980514</v>
       </c>
       <c r="E257" t="n">
-        <v>4.576770711466393</v>
+        <v>4.578826210648489</v>
       </c>
       <c r="F257" t="n">
         <v>4.73356340075649</v>
@@ -6515,7 +6515,7 @@
         <v>4.690430029938915</v>
       </c>
       <c r="E258" t="n">
-        <v>4.591071261608589</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="F258" t="n">
         <v>4.73356340075649</v>
@@ -6548,7 +6548,7 @@
         <v>4.692264892839025</v>
       </c>
       <c r="E259" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="F259" t="n">
         <v>4.739701078945697</v>
@@ -6579,7 +6579,7 @@
         <v>4.695924549256556</v>
       </c>
       <c r="E260" t="n">
-        <v>4.590056548178043</v>
+        <v>4.591071261608589</v>
       </c>
       <c r="F260" t="n">
         <v>4.746669748261791</v>
@@ -6610,7 +6610,7 @@
         <v>4.700480365792417</v>
       </c>
       <c r="E261" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="F261" t="n">
         <v>4.745801315727837</v>
@@ -6643,7 +6643,7 @@
         <v>4.706823839714591</v>
       </c>
       <c r="E262" t="n">
-        <v>4.593097604753822</v>
+        <v>4.59511985013459</v>
       </c>
       <c r="F262" t="n">
         <v>4.746669748261791</v>
@@ -6674,7 +6674,7 @@
         <v>4.714024590900173</v>
       </c>
       <c r="E263" t="n">
-        <v>4.591071261608589</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="F263" t="n">
         <v>4.774912960575186</v>
@@ -6705,7 +6705,7 @@
         <v>4.715816706075155</v>
       </c>
       <c r="E264" t="n">
-        <v>4.600157644164547</v>
+        <v>4.601162164590552</v>
       </c>
       <c r="F264" t="n">
         <v>4.784988612563928</v>
@@ -6738,7 +6738,7 @@
         <v>4.727387818712341</v>
       </c>
       <c r="E265" t="n">
-        <v>4.61512051684126</v>
+        <v>4.616110126026426</v>
       </c>
       <c r="F265" t="n">
         <v>4.81380905109942</v>
@@ -6769,7 +6769,7 @@
         <v>4.711330381816482</v>
       </c>
       <c r="E266" t="n">
-        <v>4.611152257665639</v>
+        <v>4.612145799724517</v>
       </c>
       <c r="F266" t="n">
         <v>4.762173934797756</v>
@@ -6800,7 +6800,7 @@
         <v>4.715816706075155</v>
       </c>
       <c r="E267" t="n">
-        <v>4.616110126026426</v>
+        <v>4.617098756853365</v>
       </c>
       <c r="F267" t="n">
         <v>4.778282803696737</v>
@@ -6833,7 +6833,7 @@
         <v>4.720282993088596</v>
       </c>
       <c r="E268" t="n">
-        <v>4.623010104116422</v>
+        <v>4.623991940228679</v>
       </c>
       <c r="F268" t="n">
         <v>4.774912960575186</v>
@@ -6864,7 +6864,7 @@
         <v>4.721173861744398</v>
       </c>
       <c r="E269" t="n">
-        <v>4.609162207257629</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="F269" t="n">
         <v>4.776599301615622</v>
@@ -6895,7 +6895,7 @@
         <v>4.719391330078114</v>
       </c>
       <c r="E270" t="n">
-        <v>4.624972813284271</v>
+        <v>4.626931677769604</v>
       </c>
       <c r="F270" t="n">
         <v>4.768988271217486</v>
@@ -6928,7 +6928,7 @@
         <v>4.716711560720999</v>
       </c>
       <c r="E271" t="n">
-        <v>4.627909672957581</v>
+        <v>4.629862798578463</v>
       </c>
       <c r="F271" t="n">
         <v>4.765586907393996</v>
@@ -6959,7 +6959,7 @@
         <v>4.711330381816482</v>
       </c>
       <c r="E272" t="n">
-        <v>4.628886712605407</v>
+        <v>4.630837932736669</v>
       </c>
       <c r="F272" t="n">
         <v>4.771531723203316</v>
@@ -6990,7 +6990,7 @@
         <v>4.702296896718814</v>
       </c>
       <c r="E273" t="n">
-        <v>4.634728988229636</v>
+        <v>4.635699391022914</v>
       </c>
       <c r="F273" t="n">
         <v>4.769836807543325</v>
@@ -7023,7 +7023,7 @@
         <v>4.685828089005546</v>
       </c>
       <c r="E274" t="n">
-        <v>4.631812116934513</v>
+        <v>4.633757642840004</v>
       </c>
       <c r="F274" t="n">
         <v>4.769836807543325</v>
@@ -7054,7 +7054,7 @@
         <v>4.681204872264089</v>
       </c>
       <c r="E275" t="n">
-        <v>4.639571612705423</v>
+        <v>4.640537329825382</v>
       </c>
       <c r="F275" t="n">
         <v>4.770684624465665</v>
@@ -7085,7 +7085,7 @@
         <v>4.673762977453703</v>
       </c>
       <c r="E276" t="n">
-        <v>4.633757642840004</v>
+        <v>4.634728988229636</v>
       </c>
       <c r="F276" t="n">
         <v>4.763028270603671</v>
@@ -7118,7 +7118,7 @@
         <v>4.665324108807838</v>
       </c>
       <c r="E277" t="n">
-        <v>4.637637376125593</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F277" t="n">
         <v>4.768139014266231</v>
@@ -7149,7 +7149,7 @@
         <v>4.650143551630823</v>
       </c>
       <c r="E278" t="n">
-        <v>4.648229675448539</v>
+        <v>4.650143551630823</v>
       </c>
       <c r="F278" t="n">
         <v>4.789988622980633</v>
@@ -7180,7 +7180,7 @@
         <v>4.634728988229636</v>
       </c>
       <c r="E279" t="n">
-        <v>4.648229675448539</v>
+        <v>4.650143551630823</v>
       </c>
       <c r="F279" t="n">
         <v>4.794963757620747</v>
@@ -7213,7 +7213,7 @@
         <v>4.626931677769604</v>
       </c>
       <c r="E280" t="n">
-        <v>4.640537329825382</v>
+        <v>4.642465970731788</v>
       </c>
       <c r="F280" t="n">
         <v>4.787491742782046</v>
@@ -7244,7 +7244,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="E281" t="n">
-        <v>4.654912277882906</v>
+        <v>4.65681341913993</v>
       </c>
       <c r="F281" t="n">
         <v>4.763028270603671</v>
@@ -7275,7 +7275,7 @@
         <v>4.59511985013459</v>
       </c>
       <c r="E282" t="n">
-        <v>4.623010104116422</v>
+        <v>4.624972813284271</v>
       </c>
       <c r="F282" t="n">
         <v>4.753590191106364</v>
@@ -7308,7 +7308,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="E283" t="n">
-        <v>4.625952725170619</v>
+        <v>4.626931677769604</v>
       </c>
       <c r="F283" t="n">
         <v>4.753590191106364</v>
@@ -7339,7 +7339,7 @@
         <v>4.517431271680085</v>
       </c>
       <c r="E284" t="n">
-        <v>4.617098756853365</v>
+        <v>4.618086411254637</v>
       </c>
       <c r="F284" t="n">
         <v>4.74406218485471</v>
@@ -7370,7 +7370,7 @@
         <v>4.497584975308154</v>
       </c>
       <c r="E285" t="n">
-        <v>4.612145799724517</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="F285" t="n">
         <v>4.753590191106364</v>
@@ -7403,7 +7403,7 @@
         <v>4.486386649998124</v>
       </c>
       <c r="E286" t="n">
-        <v>4.604169685654508</v>
+        <v>4.606169686321175</v>
       </c>
       <c r="F286" t="n">
         <v>4.731802836921458</v>
@@ -7434,7 +7434,7 @@
         <v>4.410371107683024</v>
       </c>
       <c r="E287" t="n">
-        <v>4.581901559048737</v>
+        <v>4.583946549536464</v>
       </c>
       <c r="F287" t="n">
         <v>4.715816706075155</v>
@@ -7465,7 +7465,7 @@
         <v>4.342505876511598</v>
       </c>
       <c r="E288" t="n">
-        <v>4.545420181582317</v>
+        <v>4.546481189639412</v>
       </c>
       <c r="F288" t="n">
         <v>4.704110133842995</v>
@@ -7498,7 +7498,7 @@
         <v>4.251348311031766</v>
       </c>
       <c r="E289" t="n">
-        <v>4.504244267398131</v>
+        <v>4.505349850705881</v>
       </c>
       <c r="F289" t="n">
         <v>4.684905154006945</v>
@@ -7529,7 +7529,7 @@
         <v>4.255612709818223</v>
       </c>
       <c r="E290" t="n">
-        <v>4.460144413937834</v>
+        <v>4.461299815568389</v>
       </c>
       <c r="F290" t="n">
         <v>4.671893818030999</v>
@@ -7560,7 +7560,7 @@
         <v>4.220977213155467</v>
       </c>
       <c r="E291" t="n">
-        <v>4.437934266612178</v>
+        <v>4.439115601658009</v>
       </c>
       <c r="F291" t="n">
         <v>4.701389043728634</v>
@@ -7593,7 +7593,7 @@
         <v>4.207673247529104</v>
       </c>
       <c r="E292" t="n">
-        <v>4.42484663185681</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="F292" t="n">
         <v>4.693181063310805</v>
@@ -7624,7 +7624,7 @@
         <v>4.244200317766478</v>
       </c>
       <c r="E293" t="n">
-        <v>4.411585436915426</v>
+        <v>4.412798293340635</v>
       </c>
       <c r="F293" t="n">
         <v>4.685828089005546</v>
@@ -7655,7 +7655,7 @@
         <v>4.298645025734831</v>
       </c>
       <c r="E294" t="n">
-        <v>4.43438186500781</v>
+        <v>4.435567401601912</v>
       </c>
       <c r="F294" t="n">
         <v>4.679349584162343</v>
@@ -7688,7 +7688,7 @@
         <v>4.333361462692601</v>
       </c>
       <c r="E295" t="n">
-        <v>4.441474093317302</v>
+        <v>4.442651256490317</v>
       </c>
       <c r="F295" t="n">
         <v>4.680277658474897</v>
@@ -7719,7 +7719,7 @@
         <v>4.37197629882038</v>
       </c>
       <c r="E296" t="n">
-        <v>4.44500143383527</v>
+        <v>4.446174454497633</v>
       </c>
       <c r="F296" t="n">
         <v>4.670957926526095</v>
@@ -7750,7 +7750,7 @@
         <v>4.433194921248282</v>
       </c>
       <c r="E297" t="n">
-        <v>4.44500143383527</v>
+        <v>4.447346100794524</v>
       </c>
       <c r="F297" t="n">
         <v>4.669083511731744</v>
@@ -7783,7 +7783,7 @@
         <v>4.463606621666305</v>
       </c>
       <c r="E298" t="n">
-        <v>4.469350462845557</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="F298" t="n">
         <v>4.665324108807838</v>
@@ -7814,7 +7814,7 @@
         <v>4.489759334476764</v>
       </c>
       <c r="E299" t="n">
-        <v>4.464758032271346</v>
+        <v>4.467056883858457</v>
       </c>
       <c r="F299" t="n">
         <v>4.651099117876491</v>
@@ -7845,7 +7845,7 @@
         <v>4.503137460422939</v>
       </c>
       <c r="E300" t="n">
-        <v>4.469350462845557</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="F300" t="n">
         <v>4.654912277882906</v>
@@ -7878,7 +7878,7 @@
         <v>4.523960130562548</v>
       </c>
       <c r="E301" t="n">
-        <v>4.468204330914934</v>
+        <v>4.469350462845557</v>
       </c>
       <c r="F301" t="n">
         <v>4.624972813284271</v>
@@ -7909,7 +7909,7 @@
         <v>4.533674184283021</v>
       </c>
       <c r="E302" t="n">
-        <v>4.484131857611035</v>
+        <v>4.485259889315534</v>
       </c>
       <c r="F302" t="n">
         <v>4.611152257665639</v>
@@ -7940,7 +7940,7 @@
         <v>4.529368472571809</v>
       </c>
       <c r="E303" t="n">
-        <v>4.478472532942134</v>
+        <v>4.479606963012746</v>
       </c>
       <c r="F303" t="n">
         <v>4.598145571051127</v>
@@ -7973,7 +7973,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="E304" t="n">
-        <v>4.498697941477575</v>
+        <v>4.500920164614292</v>
       </c>
       <c r="F304" t="n">
         <v>4.640537329825382</v>
@@ -8004,7 +8004,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="E305" t="n">
-        <v>4.500920164614292</v>
+        <v>4.503137460422939</v>
       </c>
       <c r="F305" t="n">
         <v>4.623991940228679</v>
@@ -8035,7 +8035,7 @@
         <v>4.573679518896721</v>
       </c>
       <c r="E306" t="n">
-        <v>4.522874943261261</v>
+        <v>4.523960130562548</v>
       </c>
       <c r="F306" t="n">
         <v>4.621043535144381</v>
@@ -8068,7 +8068,7 @@
         <v>4.573679518896721</v>
       </c>
       <c r="E307" t="n">
-        <v>4.522874943261261</v>
+        <v>4.523960130562548</v>
       </c>
       <c r="F307" t="n">
         <v>4.696837374513915</v>
@@ -8099,7 +8099,7 @@
         <v>4.59511985013459</v>
       </c>
       <c r="E308" t="n">
-        <v>4.51852237926242</v>
+        <v>4.519612297626445</v>
       </c>
       <c r="F308" t="n">
         <v>4.591071261608589</v>
@@ -8130,7 +8130,7 @@
         <v>4.611152257665639</v>
       </c>
       <c r="E309" t="n">
-        <v>4.529368472571809</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="F309" t="n">
         <v>4.594109238628667</v>
@@ -8163,7 +8163,7 @@
         <v>4.621043535144381</v>
       </c>
       <c r="E310" t="n">
-        <v>4.528289141652134</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="F310" t="n">
         <v>4.600157644164547</v>
@@ -8194,7 +8194,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="E311" t="n">
-        <v>4.536891345234797</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="F311" t="n">
         <v>4.607168188650764</v>
@@ -8225,7 +8225,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="E312" t="n">
-        <v>4.546481189639412</v>
+        <v>4.547541073151455</v>
       </c>
       <c r="F312" t="n">
         <v>4.597138014290827</v>
@@ -8258,7 +8258,7 @@
         <v>4.638604962074329</v>
       </c>
       <c r="E313" t="n">
-        <v>4.554928969551344</v>
+        <v>4.55597994179732</v>
       </c>
       <c r="F313" t="n">
         <v>4.526126978647638</v>
@@ -8289,7 +8289,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E314" t="n">
-        <v>4.548599834499697</v>
+        <v>4.549657476057832</v>
       </c>
       <c r="F314" t="n">
         <v>4.604169685654508</v>
@@ -8320,7 +8320,7 @@
         <v>4.640537329825382</v>
       </c>
       <c r="E315" t="n">
-        <v>4.558078578454241</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="F315" t="n">
         <v>4.614129927359564</v>
@@ -8353,7 +8353,7 @@
         <v>4.637637376125593</v>
       </c>
       <c r="E316" t="n">
-        <v>4.558078578454241</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="F316" t="n">
         <v>4.600157644164547</v>
@@ -8384,7 +8384,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="E317" t="n">
-        <v>4.55597994179732</v>
+        <v>4.557029810660157</v>
       </c>
       <c r="F317" t="n">
         <v>4.600157644164547</v>
@@ -8415,7 +8415,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="E318" t="n">
-        <v>4.562262684976814</v>
+        <v>4.563305981889393</v>
       </c>
       <c r="F318" t="n">
         <v>4.60816569496789</v>
@@ -8448,7 +8448,7 @@
         <v>4.621043535144381</v>
       </c>
       <c r="E319" t="n">
-        <v>4.546481189639412</v>
+        <v>4.547541073151455</v>
       </c>
       <c r="F319" t="n">
         <v>4.581901559048737</v>
@@ -8479,7 +8479,7 @@
         <v>4.604169685654508</v>
       </c>
       <c r="E320" t="n">
-        <v>4.558078578454241</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="F320" t="n">
         <v>4.58700621536042</v>
@@ -8510,7 +8510,7 @@
         <v>4.574710978503383</v>
       </c>
       <c r="E321" t="n">
-        <v>4.558078578454241</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="F321" t="n">
         <v>4.589040804058207</v>
@@ -8543,7 +8543,7 @@
         <v>4.547541073151455</v>
       </c>
       <c r="E322" t="n">
-        <v>4.549657476057832</v>
+        <v>4.550714000192032</v>
       </c>
       <c r="F322" t="n">
         <v>4.588024027153121</v>
@@ -8574,7 +8574,7 @@
         <v>4.539030383483547</v>
       </c>
       <c r="E323" t="n">
-        <v>4.545420181582317</v>
+        <v>4.547541073151455</v>
       </c>
       <c r="F323" t="n">
         <v>4.565389315976247</v>
@@ -8605,7 +8605,7 @@
         <v>4.531523645819793</v>
       </c>
       <c r="E324" t="n">
-        <v>4.547541073151455</v>
+        <v>4.549657476057832</v>
       </c>
       <c r="F324" t="n">
         <v>4.59511985013459</v>
@@ -8638,7 +8638,7 @@
         <v>4.514150787600923</v>
       </c>
       <c r="E325" t="n">
-        <v>4.542230386214217</v>
+        <v>4.543294782270004</v>
       </c>
       <c r="F325" t="n">
         <v>4.576770711466393</v>
@@ -8669,7 +8669,7 @@
         <v>4.516338972281476</v>
       </c>
       <c r="E326" t="n">
-        <v>4.535820107853298</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="F326" t="n">
         <v>4.599152113662528</v>
@@ -8700,7 +8700,7 @@
         <v>4.520701029361642</v>
       </c>
       <c r="E327" t="n">
-        <v>4.543294782270004</v>
+        <v>4.544358046591334</v>
       </c>
       <c r="F327" t="n">
         <v>4.492001487882454</v>
@@ -8733,7 +8733,7 @@
         <v>4.52720864451838</v>
       </c>
       <c r="E328" t="n">
-        <v>4.541164856012179</v>
+        <v>4.542230386214217</v>
       </c>
       <c r="F328" t="n">
         <v>4.597138014290827</v>
@@ -8764,7 +8764,7 @@
         <v>4.51852237926242</v>
       </c>
       <c r="E329" t="n">
-        <v>4.533674184283021</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F329" t="n">
         <v>4.56746831880408</v>
@@ -8795,7 +8795,7 @@
         <v>4.498697941477575</v>
       </c>
       <c r="E330" t="n">
-        <v>4.542230386214217</v>
+        <v>4.543294782270004</v>
       </c>
       <c r="F330" t="n">
         <v>4.574710978503383</v>
@@ -8828,7 +8828,7 @@
         <v>4.49647076906475</v>
       </c>
       <c r="E331" t="n">
-        <v>4.533674184283021</v>
+        <v>4.535820107853298</v>
       </c>
       <c r="F331" t="n">
         <v>4.572646994282532</v>
@@ -8859,7 +8859,7 @@
         <v>4.476199804691132</v>
       </c>
       <c r="E332" t="n">
-        <v>4.536891345234797</v>
+        <v>4.537961436294641</v>
       </c>
       <c r="F332" t="n">
         <v>4.574710978503383</v>
@@ -8890,7 +8890,7 @@
         <v>4.467056883858457</v>
       </c>
       <c r="E333" t="n">
-        <v>4.543294782270004</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="F333" t="n">
         <v>4.585987366571318</v>
@@ -8923,7 +8923,7 @@
         <v>4.452019006493916</v>
       </c>
       <c r="E334" t="n">
-        <v>4.523960130562548</v>
+        <v>4.526126978647638</v>
       </c>
       <c r="F334" t="n">
         <v>4.563305981889393</v>
@@ -8954,7 +8954,7 @@
         <v>4.441474093317302</v>
       </c>
       <c r="E335" t="n">
-        <v>4.516338972281476</v>
+        <v>4.517431271680085</v>
       </c>
       <c r="F335" t="n">
         <v>4.56954300834494</v>
@@ -8985,7 +8985,7 @@
         <v>4.454347296253507</v>
       </c>
       <c r="E336" t="n">
-        <v>4.508659285607248</v>
+        <v>4.509760001183433</v>
       </c>
       <c r="F336" t="n">
         <v>4.564348191467836</v>
@@ -9018,7 +9018,7 @@
         <v>4.45898767581001</v>
       </c>
       <c r="E337" t="n">
-        <v>4.515245478460105</v>
+        <v>4.516338972281476</v>
       </c>
       <c r="F337" t="n">
         <v>4.546481189639412</v>
@@ -9049,7 +9049,7 @@
         <v>4.478472532942134</v>
       </c>
       <c r="E338" t="n">
-        <v>4.509760001183433</v>
+        <v>4.511957804265912</v>
       </c>
       <c r="F338" t="n">
         <v>4.516338972281476</v>
@@ -9080,7 +9080,7 @@
         <v>4.485259889315534</v>
       </c>
       <c r="E339" t="n">
-        <v>4.513054897080286</v>
+        <v>4.514150787600923</v>
       </c>
       <c r="F339" t="n">
         <v>4.51852237926242</v>
@@ -9113,7 +9113,7 @@
         <v>4.484131857611035</v>
       </c>
       <c r="E340" t="n">
-        <v>4.523960130562548</v>
+        <v>4.525044141508807</v>
       </c>
       <c r="F340" t="n">
         <v>4.504244267398131</v>
@@ -9144,7 +9144,7 @@
         <v>4.475061500641071</v>
       </c>
       <c r="E341" t="n">
-        <v>4.525044141508807</v>
+        <v>4.526126978647638</v>
       </c>
       <c r="F341" t="n">
         <v>4.543294782270004</v>
@@ -9175,7 +9175,7 @@
         <v>4.481871969643598</v>
       </c>
       <c r="E342" t="n">
-        <v>4.525044141508807</v>
+        <v>4.52720864451838</v>
       </c>
       <c r="F342" t="n">
         <v>4.543294782270004</v>
@@ -9208,7 +9208,7 @@
         <v>4.49647076906475</v>
       </c>
       <c r="E343" t="n">
-        <v>4.52720864451838</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="F343" t="n">
         <v>4.557029810660157</v>
@@ -9239,7 +9239,7 @@
         <v>4.505349850705881</v>
       </c>
       <c r="E344" t="n">
-        <v>4.517431271680085</v>
+        <v>4.519612297626445</v>
       </c>
       <c r="F344" t="n">
         <v>4.56746831880408</v>
@@ -9270,7 +9270,7 @@
         <v>4.533674184283021</v>
       </c>
       <c r="E345" t="n">
-        <v>4.522874943261261</v>
+        <v>4.525044141508807</v>
       </c>
       <c r="F345" t="n">
         <v>4.564348191467836</v>
@@ -9303,7 +9303,7 @@
         <v>4.561218298458908</v>
       </c>
       <c r="E346" t="n">
-        <v>4.526126978647638</v>
+        <v>4.528289141652134</v>
       </c>
       <c r="F346" t="n">
         <v>4.566429357671661</v>
@@ -9334,7 +9334,7 @@
         <v>4.561218298458908</v>
       </c>
       <c r="E347" t="n">
-        <v>4.520701029361642</v>
+        <v>4.522874943261261</v>
       </c>
       <c r="F347" t="n">
         <v>4.56954300834494</v>
@@ -9365,7 +9365,7 @@
         <v>4.573679518896721</v>
       </c>
       <c r="E348" t="n">
-        <v>4.532599493153256</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F348" t="n">
         <v>4.55597994179732</v>
@@ -9398,7 +9398,7 @@
         <v>4.581901559048737</v>
       </c>
       <c r="E349" t="n">
-        <v>4.531523645819793</v>
+        <v>4.533674184283021</v>
       </c>
       <c r="F349" t="n">
         <v>4.5685062016165</v>
@@ -9429,7 +9429,7 @@
         <v>4.591071261608589</v>
       </c>
       <c r="E350" t="n">
-        <v>4.528289141652134</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="F350" t="n">
         <v>4.572646994282532</v>
@@ -9460,7 +9460,7 @@
         <v>4.59511985013459</v>
       </c>
       <c r="E351" t="n">
-        <v>4.534747721691546</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="F351" t="n">
         <v>4.565389315976247</v>
@@ -9493,7 +9493,7 @@
         <v>4.606169686321175</v>
       </c>
       <c r="E352" t="n">
-        <v>4.529368472571809</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="F352" t="n">
         <v>4.573679518896721</v>
@@ -9524,7 +9524,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="E353" t="n">
-        <v>4.545420181582317</v>
+        <v>4.546481189639412</v>
       </c>
       <c r="F353" t="n">
         <v>4.573679518896721</v>
@@ -9555,7 +9555,7 @@
         <v>4.601162164590552</v>
       </c>
       <c r="E354" t="n">
-        <v>4.537961436294641</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="F354" t="n">
         <v>4.546481189639412</v>
@@ -9588,7 +9588,7 @@
         <v>4.59511985013459</v>
       </c>
       <c r="E355" t="n">
-        <v>4.531523645819793</v>
+        <v>4.532599493153256</v>
       </c>
       <c r="F355" t="n">
         <v>4.552823705615882</v>
@@ -9619,7 +9619,7 @@
         <v>4.594109238628667</v>
       </c>
       <c r="E356" t="n">
-        <v>4.540098189244376</v>
+        <v>4.542230386214217</v>
       </c>
       <c r="F356" t="n">
         <v>4.551769409260976</v>
@@ -9650,7 +9650,7 @@
         <v>4.581901559048737</v>
       </c>
       <c r="E357" t="n">
-        <v>4.52178857704904</v>
+        <v>4.522874943261261</v>
       </c>
       <c r="F357" t="n">
         <v>4.553876891600541</v>
@@ -9683,7 +9683,7 @@
         <v>4.574710978503383</v>
       </c>
       <c r="E358" t="n">
-        <v>4.533674184283021</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="F358" t="n">
         <v>4.545420181582317</v>
@@ -9714,7 +9714,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="E359" t="n">
-        <v>4.531523645819793</v>
+        <v>4.532599493153256</v>
       </c>
       <c r="F359" t="n">
         <v>4.559126247486684</v>
@@ -9745,7 +9745,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="E360" t="n">
-        <v>4.529368472571809</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="F360" t="n">
         <v>4.539030383483547</v>
@@ -9778,7 +9778,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="E361" t="n">
-        <v>4.542230386214217</v>
+        <v>4.543294782270004</v>
       </c>
       <c r="F361" t="n">
         <v>4.552823705615882</v>
@@ -9809,7 +9809,7 @@
         <v>4.599152113662528</v>
       </c>
       <c r="E362" t="n">
-        <v>4.534747721691546</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="F362" t="n">
         <v>4.551769409260976</v>
@@ -9840,7 +9840,7 @@
         <v>4.617098756853365</v>
       </c>
       <c r="E363" t="n">
-        <v>4.560172820057356</v>
+        <v>4.561218298458908</v>
       </c>
       <c r="F363" t="n">
         <v>4.528289141652134</v>
@@ -9873,7 +9873,7 @@
         <v>4.638604962074329</v>
       </c>
       <c r="E364" t="n">
-        <v>4.562262684976814</v>
+        <v>4.563305981889393</v>
       </c>
       <c r="F364" t="n">
         <v>4.553876891600541</v>
@@ -9904,7 +9904,7 @@
         <v>4.638604962074329</v>
       </c>
       <c r="E365" t="n">
-        <v>4.554928969551344</v>
+        <v>4.55597994179732</v>
       </c>
       <c r="F365" t="n">
         <v>4.545420181582317</v>
@@ -9935,7 +9935,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E366" t="n">
-        <v>4.561218298458908</v>
+        <v>4.563305981889393</v>
       </c>
       <c r="F366" t="n">
         <v>4.548599834499697</v>
@@ -9968,7 +9968,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E367" t="n">
-        <v>4.564348191467836</v>
+        <v>4.565389315976247</v>
       </c>
       <c r="F367" t="n">
         <v>4.548599834499697</v>
@@ -9999,7 +9999,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E368" t="n">
-        <v>4.570578741218473</v>
+        <v>4.571613402459248</v>
       </c>
       <c r="F368" t="n">
         <v>4.541164856012179</v>
@@ -10030,7 +10030,7 @@
         <v>4.638604962074329</v>
       </c>
       <c r="E369" t="n">
-        <v>4.55597994179732</v>
+        <v>4.558078578454241</v>
       </c>
       <c r="F369" t="n">
         <v>4.542230386214217</v>
@@ -10063,7 +10063,7 @@
         <v>4.649187071404866</v>
       </c>
       <c r="E370" t="n">
-        <v>4.561218298458908</v>
+        <v>4.562262684976814</v>
       </c>
       <c r="F370" t="n">
         <v>4.545420181582317</v>
@@ -10094,7 +10094,7 @@
         <v>4.651099117876491</v>
       </c>
       <c r="E371" t="n">
-        <v>4.563305981889393</v>
+        <v>4.565389315976247</v>
       </c>
       <c r="F371" t="n">
         <v>4.546481189639412</v>
@@ -10125,7 +10125,7 @@
         <v>4.654912277882906</v>
       </c>
       <c r="E372" t="n">
-        <v>4.558078578454241</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="F372" t="n">
         <v>4.559126247486684</v>
@@ -10158,7 +10158,7 @@
         <v>4.65681341913993</v>
       </c>
       <c r="E373" t="n">
-        <v>4.558078578454241</v>
+        <v>4.559126247486684</v>
       </c>
       <c r="F373" t="n">
         <v>4.55597994179732</v>
@@ -10189,7 +10189,7 @@
         <v>4.653007515402251</v>
       </c>
       <c r="E374" t="n">
-        <v>4.576770711466393</v>
+        <v>4.578826210648489</v>
       </c>
       <c r="F374" t="n">
         <v>4.575741375297279</v>
@@ -10220,7 +10220,7 @@
         <v>4.645351975620923</v>
       </c>
       <c r="E375" t="n">
-        <v>4.563305981889393</v>
+        <v>4.564348191467836</v>
       </c>
       <c r="F375" t="n">
         <v>4.559126247486684</v>
@@ -10253,7 +10253,7 @@
         <v>4.641502115235482</v>
       </c>
       <c r="E376" t="n">
-        <v>4.558078578454241</v>
+        <v>4.559126247486684</v>
       </c>
       <c r="F376" t="n">
         <v>4.560172820057356</v>
@@ -10284,7 +10284,7 @@
         <v>4.647271362006727</v>
       </c>
       <c r="E377" t="n">
-        <v>4.572646994282532</v>
+        <v>4.573679518896721</v>
       </c>
       <c r="F377" t="n">
         <v>4.563305981889393</v>
@@ -10315,7 +10315,7 @@
         <v>4.645351975620923</v>
       </c>
       <c r="E378" t="n">
-        <v>4.557029810660157</v>
+        <v>4.558078578454241</v>
       </c>
       <c r="F378" t="n">
         <v>4.563305981889393</v>
@@ -10348,7 +10348,7 @@
         <v>4.646312129319266</v>
       </c>
       <c r="E379" t="n">
-        <v>4.565389315976247</v>
+        <v>4.56746831880408</v>
       </c>
       <c r="F379" t="n">
         <v>4.566429357671661</v>
@@ -10379,7 +10379,7 @@
         <v>4.644390899141372</v>
       </c>
       <c r="E380" t="n">
-        <v>4.564348191467836</v>
+        <v>4.565389315976247</v>
       </c>
       <c r="F380" t="n">
         <v>4.573679518896721</v>
@@ -10410,7 +10410,7 @@
         <v>4.639571612705423</v>
       </c>
       <c r="E381" t="n">
-        <v>4.564348191467836</v>
+        <v>4.566429357671661</v>
       </c>
       <c r="F381" t="n">
         <v>4.592084946439436</v>
@@ -10443,7 +10443,7 @@
         <v>4.648229675448539</v>
       </c>
       <c r="E382" t="n">
-        <v>4.56746831880408</v>
+        <v>4.56954300834494</v>
       </c>
       <c r="F382" t="n">
         <v>4.578826210648489</v>
@@ -10474,7 +10474,7 @@
         <v>4.663439094112067</v>
       </c>
       <c r="E383" t="n">
-        <v>4.574710978503383</v>
+        <v>4.576770711466393</v>
       </c>
       <c r="F383" t="n">
         <v>4.578826210648489</v>
@@ -10505,7 +10505,7 @@
         <v>4.666265285347902</v>
       </c>
       <c r="E384" t="n">
-        <v>4.578826210648489</v>
+        <v>4.580877493419047</v>
       </c>
       <c r="F384" t="n">
         <v>4.589040804058207</v>
@@ -10538,7 +10538,7 @@
         <v>4.678420647727684</v>
       </c>
       <c r="E385" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="F385" t="n">
         <v>4.591071261608589</v>
@@ -10569,7 +10569,7 @@
         <v>4.684905154006945</v>
       </c>
       <c r="E386" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="F386" t="n">
         <v>4.566429357671661</v>
@@ -10600,7 +10600,7 @@
         <v>4.684905154006945</v>
       </c>
       <c r="E387" t="n">
-        <v>4.580877493419047</v>
+        <v>4.582924577040772</v>
       </c>
       <c r="F387" t="n">
         <v>4.603168183317418</v>
@@ -10633,7 +10633,7 @@
         <v>4.690430029938915</v>
       </c>
       <c r="E388" t="n">
-        <v>4.579852378003801</v>
+        <v>4.580877493419047</v>
       </c>
       <c r="F388" t="n">
         <v>4.612145799724517</v>
@@ -10664,7 +10664,7 @@
         <v>4.700480365792417</v>
       </c>
       <c r="E389" t="n">
-        <v>4.588024027153121</v>
+        <v>4.589040804058207</v>
       </c>
       <c r="F389" t="n">
         <v>4.612145799724517</v>
@@ -10695,7 +10695,7 @@
         <v>4.699570861409576</v>
       </c>
       <c r="E390" t="n">
-        <v>4.592084946439436</v>
+        <v>4.594109238628667</v>
       </c>
       <c r="F390" t="n">
         <v>4.618086411254637</v>
@@ -10728,7 +10728,7 @@
         <v>4.710430696645584</v>
       </c>
       <c r="E391" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="F391" t="n">
         <v>4.614129927359564</v>
@@ -10759,7 +10759,7 @@
         <v>4.71760561531788</v>
       </c>
       <c r="E392" t="n">
-        <v>4.602165676967792</v>
+        <v>4.603168183317418</v>
       </c>
       <c r="F392" t="n">
         <v>4.613138355637268</v>
@@ -10790,7 +10790,7 @@
         <v>4.71760561531788</v>
       </c>
       <c r="E393" t="n">
-        <v>4.61015772749913</v>
+        <v>4.612145799724517</v>
       </c>
       <c r="F393" t="n">
         <v>4.621043535144381</v>
@@ -10823,7 +10823,7 @@
         <v>4.727387818712341</v>
       </c>
       <c r="E394" t="n">
-        <v>4.606169686321175</v>
+        <v>4.60816569496789</v>
       </c>
       <c r="F394" t="n">
         <v>4.611152257665639</v>
@@ -10854,7 +10854,7 @@
         <v>4.738826570800765</v>
       </c>
       <c r="E395" t="n">
-        <v>4.607168188650764</v>
+        <v>4.60816569496789</v>
       </c>
       <c r="F395" t="n">
         <v>4.625952725170619</v>
@@ -10885,7 +10885,7 @@
         <v>4.741447804280639</v>
       </c>
       <c r="E396" t="n">
-        <v>4.632785353021065</v>
+        <v>4.634728988229636</v>
       </c>
       <c r="F396" t="n">
         <v>4.624972813284271</v>
@@ -10918,7 +10918,7 @@
         <v>4.751864565138895</v>
       </c>
       <c r="E397" t="n">
-        <v>4.632785353021065</v>
+        <v>4.633757642840004</v>
       </c>
       <c r="F397" t="n">
         <v>4.631812116934513</v>
@@ -10949,7 +10949,7 @@
         <v>4.746669748261791</v>
       </c>
       <c r="E398" t="n">
-        <v>4.612145799724517</v>
+        <v>4.614129927359564</v>
       </c>
       <c r="F398" t="n">
         <v>4.611152257665639</v>
@@ -10980,7 +10980,7 @@
         <v>4.739701078945697</v>
       </c>
       <c r="E399" t="n">
-        <v>4.604169685654508</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="F399" t="n">
         <v>4.58700621536042</v>
@@ -11013,7 +11013,7 @@
         <v>4.724729421045731</v>
       </c>
       <c r="E400" t="n">
-        <v>4.609162207257629</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="F400" t="n">
         <v>4.580877493419047</v>
@@ -11044,7 +11044,7 @@
         <v>4.731802836921458</v>
       </c>
       <c r="E401" t="n">
-        <v>4.605170185988092</v>
+        <v>4.606169686321175</v>
       </c>
       <c r="F401" t="n">
         <v>4.613138355637268</v>
@@ -11075,7 +11075,7 @@
         <v>4.716711560720999</v>
       </c>
       <c r="E402" t="n">
-        <v>4.618086411254637</v>
+        <v>4.619073091157083</v>
       </c>
       <c r="F402" t="n">
         <v>4.607168188650764</v>
@@ -11108,7 +11108,7 @@
         <v>4.719391330078114</v>
       </c>
       <c r="E403" t="n">
-        <v>4.617098756853365</v>
+        <v>4.618086411254637</v>
       </c>
       <c r="F403" t="n">
         <v>4.619073091157083</v>
@@ -11139,7 +11139,7 @@
         <v>4.711330381816482</v>
       </c>
       <c r="E404" t="n">
-        <v>4.603168183317418</v>
+        <v>4.604169685654508</v>
       </c>
       <c r="F404" t="n">
         <v>4.623010104116422</v>
@@ -11170,7 +11170,7 @@
         <v>4.709530201312334</v>
       </c>
       <c r="E405" t="n">
-        <v>4.616110126026426</v>
+        <v>4.617098756853365</v>
       </c>
       <c r="F405" t="n">
         <v>4.623991940228679</v>
@@ -11203,7 +11203,7 @@
         <v>4.708628894356321</v>
       </c>
       <c r="E406" t="n">
-        <v>4.60816569496789</v>
+        <v>4.609162207257629</v>
       </c>
       <c r="F406" t="n">
         <v>4.630837932736669</v>
@@ -11234,7 +11234,7 @@
         <v>4.705920089088234</v>
       </c>
       <c r="E407" t="n">
-        <v>4.611152257665639</v>
+        <v>4.612145799724517</v>
       </c>
       <c r="F407" t="n">
         <v>4.623991940228679</v>
@@ -11265,7 +11265,7 @@
         <v>4.705920089088234</v>
       </c>
       <c r="E408" t="n">
-        <v>4.597138014290827</v>
+        <v>4.598145571051127</v>
       </c>
       <c r="F408" t="n">
         <v>4.625952725170619</v>
@@ -11298,7 +11298,7 @@
         <v>4.691347882229143</v>
       </c>
       <c r="E409" t="n">
-        <v>4.598145571051127</v>
+        <v>4.600157644164547</v>
       </c>
       <c r="F409" t="n">
         <v>4.643428898105181</v>
@@ -11329,7 +11329,7 @@
         <v>4.677490847567717</v>
       </c>
       <c r="E410" t="n">
-        <v>4.609162207257629</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="F410" t="n">
         <v>4.611152257665639</v>
@@ -11360,7 +11360,7 @@
         <v>4.672828834461906</v>
       </c>
       <c r="E411" t="n">
-        <v>4.603168183317418</v>
+        <v>4.604169685654508</v>
       </c>
       <c r="F411" t="n">
         <v>4.641502115235482</v>
@@ -11393,7 +11393,7 @@
         <v>4.666265285347902</v>
       </c>
       <c r="E412" t="n">
-        <v>4.604169685654508</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="F412" t="n">
         <v>4.643428898105181</v>
@@ -11424,7 +11424,7 @@
         <v>4.652053771886941</v>
       </c>
       <c r="E413" t="n">
-        <v>4.603168183317418</v>
+        <v>4.604169685654508</v>
       </c>
       <c r="F413" t="n">
         <v>4.640537329825382</v>
@@ -11455,7 +11455,7 @@
         <v>4.661550519424199</v>
       </c>
       <c r="E414" t="n">
-        <v>4.60816569496789</v>
+        <v>4.609162207257629</v>
       </c>
       <c r="F414" t="n">
         <v>4.632785353021065</v>
@@ -11519,7 +11519,7 @@
         <v>4.630837932736669</v>
       </c>
       <c r="E416" t="n">
-        <v>4.594109238628667</v>
+        <v>4.59511985013459</v>
       </c>
       <c r="F416" t="n">
         <v>4.633757642840004</v>
@@ -11550,7 +11550,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E417" t="n">
-        <v>4.599152113662528</v>
+        <v>4.600157644164547</v>
       </c>
       <c r="F417" t="n">
         <v>4.630837932736669</v>
@@ -11583,7 +11583,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="E418" t="n">
-        <v>4.597138014290827</v>
+        <v>4.598145571051127</v>
       </c>
       <c r="F418" t="n">
         <v>4.637637376125593</v>
@@ -11614,7 +11614,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="E419" t="n">
-        <v>4.604169685654508</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="F419" t="n">
         <v>4.629862798578463</v>
@@ -11645,7 +11645,7 @@
         <v>4.633757642840004</v>
       </c>
       <c r="E420" t="n">
-        <v>4.590056548178043</v>
+        <v>4.591071261608589</v>
       </c>
       <c r="F420" t="n">
         <v>4.631812116934513</v>
@@ -11678,7 +11678,7 @@
         <v>4.639571612705423</v>
       </c>
       <c r="E421" t="n">
-        <v>4.571613402459248</v>
+        <v>4.572646994282532</v>
       </c>
       <c r="F421" t="n">
         <v>4.627909672957581</v>
@@ -11709,7 +11709,7 @@
         <v>4.65586330030361</v>
       </c>
       <c r="E422" t="n">
-        <v>4.597138014290827</v>
+        <v>4.599152113662528</v>
       </c>
       <c r="F422" t="n">
         <v>4.652053771886941</v>
@@ -11740,7 +11740,7 @@
         <v>4.658710952916121</v>
       </c>
       <c r="E423" t="n">
-        <v>4.591071261608589</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="F423" t="n">
         <v>4.638604962074329</v>
@@ -11804,7 +11804,7 @@
         <v>4.056988775678332</v>
       </c>
       <c r="E425" t="n">
-        <v>4.26689632742025</v>
+        <v>4.26549281841793</v>
       </c>
       <c r="F425" t="n">
         <v>4.26549281841793</v>
@@ -11868,7 +11868,7 @@
         <v>4.314817884980432</v>
       </c>
       <c r="E427" t="n">
-        <v>4.485259889315534</v>
+        <v>4.486386649998124</v>
       </c>
       <c r="F427" t="n">
         <v>4.579852378003801</v>
@@ -11963,7 +11963,7 @@
         <v>4.549657476057832</v>
       </c>
       <c r="E430" t="n">
-        <v>4.543294782270004</v>
+        <v>4.544358046591334</v>
       </c>
       <c r="F430" t="n">
         <v>4.599152113662528</v>
@@ -12089,7 +12089,7 @@
         <v>4.565389315976247</v>
       </c>
       <c r="E434" t="n">
-        <v>4.606169686321175</v>
+        <v>4.607168188650764</v>
       </c>
       <c r="F434" t="n">
         <v>4.589040804058207</v>
@@ -12248,7 +12248,7 @@
         <v>4.763028270603671</v>
       </c>
       <c r="E439" t="n">
-        <v>4.605170185988092</v>
+        <v>4.604169685654508</v>
       </c>
       <c r="F439" t="n">
         <v>4.611152257665639</v>
@@ -12374,7 +12374,7 @@
         <v>4.785823685681349</v>
       </c>
       <c r="E443" t="n">
-        <v>4.599152113662528</v>
+        <v>4.598145571051127</v>
       </c>
       <c r="F443" t="n">
         <v>4.619073091157083</v>
@@ -12438,7 +12438,7 @@
         <v>4.751000634199631</v>
       </c>
       <c r="E445" t="n">
-        <v>4.625952725170619</v>
+        <v>4.624972813284271</v>
       </c>
       <c r="F445" t="n">
         <v>4.60816569496789</v>
@@ -12849,7 +12849,7 @@
         <v>4.597138014290827</v>
       </c>
       <c r="E458" t="n">
-        <v>4.628886712605407</v>
+        <v>4.627909672957581</v>
       </c>
       <c r="F458" t="n">
         <v>4.638604962074329</v>
@@ -12880,7 +12880,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="E459" t="n">
-        <v>4.639571612705423</v>
+        <v>4.638604962074329</v>
       </c>
       <c r="F459" t="n">
         <v>4.65681341913993</v>
@@ -13165,7 +13165,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="E468" t="n">
-        <v>4.593097604753822</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="F468" t="n">
         <v>4.639571612705423</v>
@@ -13198,7 +13198,7 @@
         <v>4.571613402459248</v>
       </c>
       <c r="E469" t="n">
-        <v>4.590056548178043</v>
+        <v>4.591071261608589</v>
       </c>
       <c r="F469" t="n">
         <v>4.643428898105181</v>
@@ -13229,7 +13229,7 @@
         <v>4.560172820057356</v>
       </c>
       <c r="E470" t="n">
-        <v>4.579852378003801</v>
+        <v>4.578826210648489</v>
       </c>
       <c r="F470" t="n">
         <v>4.640537329825382</v>
@@ -13293,7 +13293,7 @@
         <v>4.566429357671661</v>
       </c>
       <c r="E472" t="n">
-        <v>4.576770711466393</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="F472" t="n">
         <v>4.634728988229636</v>
@@ -13450,7 +13450,7 @@
         <v>4.570578741218473</v>
       </c>
       <c r="E477" t="n">
-        <v>4.580877493419047</v>
+        <v>4.579852378003801</v>
       </c>
       <c r="F477" t="n">
         <v>4.625952725170619</v>
@@ -13609,7 +13609,7 @@
         <v>4.55597994179732</v>
       </c>
       <c r="E482" t="n">
-        <v>4.584967478670572</v>
+        <v>4.585987366571318</v>
       </c>
       <c r="F482" t="n">
         <v>4.672828834461906</v>
@@ -13640,7 +13640,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="E483" t="n">
-        <v>4.593097604753822</v>
+        <v>4.594109238628667</v>
       </c>
       <c r="F483" t="n">
         <v>4.661550519424199</v>
@@ -13673,7 +13673,7 @@
         <v>4.560172820057356</v>
       </c>
       <c r="E484" t="n">
-        <v>4.619073091157083</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="F484" t="n">
         <v>4.652053771886941</v>
@@ -13704,7 +13704,7 @@
         <v>4.552823705615882</v>
       </c>
       <c r="E485" t="n">
-        <v>4.583946549536464</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="F485" t="n">
         <v>4.653007515402251</v>
@@ -13799,7 +13799,7 @@
         <v>4.564348191467836</v>
       </c>
       <c r="E488" t="n">
-        <v>4.591071261608589</v>
+        <v>4.590056548178043</v>
       </c>
       <c r="F488" t="n">
         <v>4.653960350157523</v>
@@ -13830,7 +13830,7 @@
         <v>4.558078578454241</v>
       </c>
       <c r="E489" t="n">
-        <v>4.589040804058207</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="F489" t="n">
         <v>4.647271362006727</v>
@@ -13989,7 +13989,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E494" t="n">
-        <v>4.578826210648489</v>
+        <v>4.576770711466393</v>
       </c>
       <c r="F494" t="n">
         <v>4.633757642840004</v>
@@ -14020,7 +14020,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="E495" t="n">
-        <v>4.581901559048737</v>
+        <v>4.580877493419047</v>
       </c>
       <c r="F495" t="n">
         <v>4.628886712605407</v>
@@ -14053,7 +14053,7 @@
         <v>4.572646994282532</v>
       </c>
       <c r="E496" t="n">
-        <v>4.585987366571318</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="F496" t="n">
         <v>4.647271362006727</v>
@@ -14084,7 +14084,7 @@
         <v>4.540098189244376</v>
       </c>
       <c r="E497" t="n">
-        <v>4.589040804058207</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="F497" t="n">
         <v>4.646312129319266</v>
@@ -14115,7 +14115,7 @@
         <v>4.545420181582317</v>
       </c>
       <c r="E498" t="n">
-        <v>4.592084946439436</v>
+        <v>4.590056548178043</v>
       </c>
       <c r="F498" t="n">
         <v>4.648229675448539</v>
@@ -14148,7 +14148,7 @@
         <v>4.560172820057356</v>
       </c>
       <c r="E499" t="n">
-        <v>4.592084946439436</v>
+        <v>4.589040804058207</v>
       </c>
       <c r="F499" t="n">
         <v>4.634728988229636</v>
@@ -14178,7 +14178,9 @@
       <c r="D500" t="n">
         <v>4.575741375297279</v>
       </c>
-      <c r="E500" t="inlineStr"/>
+      <c r="E500" t="n">
+        <v>4.588024027153121</v>
+      </c>
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="n">
         <v>4.646312129319266</v>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14212,7 +14212,7 @@
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
-        <v>4.641502115235482</v>
+        <v>4.641405678570186</v>
       </c>
       <c r="J501" t="n">
         <v>4.363913651397029</v>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -3282,7 +3282,7 @@
         <v>4.382026634673881</v>
       </c>
       <c r="F148" t="n">
-        <v>4.674696248636701</v>
+        <v>4.675628649636653</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
         <v>4.407938016458383</v>
       </c>
       <c r="F152" t="n">
-        <v>4.683056724645162</v>
+        <v>4.683981366412381</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
         <v>4.429625613473161</v>
       </c>
       <c r="F171" t="n">
-        <v>4.620058798481842</v>
+        <v>4.621043535144381</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
         <v>4.436751534363128</v>
       </c>
       <c r="F173" t="n">
-        <v>4.691347882229143</v>
+        <v>4.692264892839025</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
         <v>4.522874943261261</v>
       </c>
       <c r="F192" t="n">
-        <v>4.711330381816482</v>
+        <v>4.710430696645584</v>
       </c>
       <c r="G192" t="n">
         <v>4.423648309364701</v>
@@ -6423,7 +6423,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="F255" t="n">
-        <v>4.713127327493184</v>
+        <v>4.714024590900173</v>
       </c>
       <c r="G255" t="n">
         <v>4.48863636973214</v>
@@ -8736,7 +8736,7 @@
         <v>4.542230386214217</v>
       </c>
       <c r="F328" t="n">
-        <v>4.597138014290827</v>
+        <v>4.598145571051127</v>
       </c>
       <c r="G328" t="n">
         <v>4.472780997942346</v>
@@ -12092,7 +12092,7 @@
         <v>4.607168188650764</v>
       </c>
       <c r="F434" t="n">
-        <v>4.589040804058207</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="G434" t="n">
         <v>4.528289141652134</v>
@@ -12282,7 +12282,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="F440" t="n">
-        <v>4.607168188650764</v>
+        <v>4.60816569496789</v>
       </c>
       <c r="G440" t="n">
         <v>4.617098756853365</v>
@@ -12598,7 +12598,7 @@
         <v>4.628886712605407</v>
       </c>
       <c r="F450" t="n">
-        <v>4.628886712605407</v>
+        <v>4.627909672957581</v>
       </c>
       <c r="G450" t="n">
         <v>4.625952725170619</v>
@@ -12693,7 +12693,7 @@
         <v>4.630837932736669</v>
       </c>
       <c r="F453" t="n">
-        <v>4.623991940228679</v>
+        <v>4.623010104116422</v>
       </c>
       <c r="G453" t="n">
         <v>4.61512051684126</v>
@@ -13137,7 +13137,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="F467" t="n">
-        <v>4.642465970731788</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="G467" t="n">
         <v>4.598145571051127</v>
@@ -13453,7 +13453,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="F477" t="n">
-        <v>4.625952725170619</v>
+        <v>4.626931677769604</v>
       </c>
       <c r="G477" t="n">
         <v>4.621043535144381</v>
@@ -13612,7 +13612,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="F482" t="n">
-        <v>4.672828834461906</v>
+        <v>4.673762977453703</v>
       </c>
       <c r="G482" t="n">
         <v>4.624972813284271</v>
@@ -13643,7 +13643,7 @@
         <v>4.594109238628667</v>
       </c>
       <c r="F483" t="n">
-        <v>4.661550519424199</v>
+        <v>4.662495252607361</v>
       </c>
       <c r="G483" t="n">
         <v>4.628886712605407</v>
@@ -13676,7 +13676,7 @@
         <v>4.620058798481842</v>
       </c>
       <c r="F484" t="n">
-        <v>4.652053771886941</v>
+        <v>4.653007515402251</v>
       </c>
       <c r="G484" t="n">
         <v>4.628886712605407</v>
@@ -13738,7 +13738,7 @@
         <v>4.594109238628667</v>
       </c>
       <c r="F486" t="n">
-        <v>4.644390899141372</v>
+        <v>4.645351975620923</v>
       </c>
       <c r="G486" t="n">
         <v>4.631812116934513</v>
@@ -13771,7 +13771,7 @@
         <v>4.591071261608589</v>
       </c>
       <c r="F487" t="n">
-        <v>4.647271362006727</v>
+        <v>4.649187071404866</v>
       </c>
       <c r="G487" t="n">
         <v>4.639571612705423</v>
@@ -13802,7 +13802,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F488" t="n">
-        <v>4.653960350157523</v>
+        <v>4.654912277882906</v>
       </c>
       <c r="G488" t="n">
         <v>4.638604962074329</v>
@@ -13866,7 +13866,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="F490" t="n">
-        <v>4.642465970731788</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="G490" t="n">
         <v>4.639571612705423</v>
@@ -13961,7 +13961,7 @@
         <v>4.589040804058207</v>
       </c>
       <c r="F493" t="n">
-        <v>4.644390899141372</v>
+        <v>4.645351975620923</v>
       </c>
       <c r="G493" t="n">
         <v>4.644390899141372</v>
@@ -14023,7 +14023,7 @@
         <v>4.580877493419047</v>
       </c>
       <c r="F495" t="n">
-        <v>4.628886712605407</v>
+        <v>4.627909672957581</v>
       </c>
       <c r="G495" t="n">
         <v>4.642465970731788</v>
@@ -14056,7 +14056,7 @@
         <v>4.584967478670572</v>
       </c>
       <c r="F496" t="n">
-        <v>4.647271362006727</v>
+        <v>4.646312129319266</v>
       </c>
       <c r="G496" t="n">
         <v>4.651099117876491</v>
@@ -14118,7 +14118,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F498" t="n">
-        <v>4.648229675448539</v>
+        <v>4.647271362006727</v>
       </c>
       <c r="G498" t="n">
         <v>4.650143551630823</v>
@@ -14151,7 +14151,7 @@
         <v>4.589040804058207</v>
       </c>
       <c r="F499" t="n">
-        <v>4.634728988229636</v>
+        <v>4.631812116934513</v>
       </c>
       <c r="G499" t="n">
         <v>4.652053771886941</v>
@@ -14181,7 +14181,9 @@
       <c r="E500" t="n">
         <v>4.588024027153121</v>
       </c>
-      <c r="F500" t="inlineStr"/>
+      <c r="F500" t="n">
+        <v>4.631812116934513</v>
+      </c>
       <c r="G500" t="n">
         <v>4.646312129319266</v>
       </c>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,7 +770,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>4.58700621536042</v>
+        <v>4.585987366571318</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>4.730039168033961</v>
+        <v>4.729156165769083</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>4.302712827954156</v>
+        <v>4.30406509320417</v>
       </c>
       <c r="E96" t="n">
         <v>4.305415532302042</v>
@@ -2492,7 +2492,7 @@
         <v>6.24</v>
       </c>
       <c r="D114" t="n">
-        <v>4.553876891600541</v>
+        <v>4.552823705615882</v>
       </c>
       <c r="E114" t="n">
         <v>4.314817884980432</v>
@@ -3086,7 +3086,7 @@
         <v>5.06</v>
       </c>
       <c r="D140" t="n">
-        <v>4.530446639792155</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="E140" t="n">
         <v>4.34639945703073</v>
@@ -3583,7 +3583,7 @@
         <v>4.09</v>
       </c>
       <c r="D161" t="n">
-        <v>4.710430696645584</v>
+        <v>4.709530201312334</v>
       </c>
       <c r="E161" t="n">
         <v>4.436751534363128</v>
@@ -4612,7 +4612,7 @@
         <v>4.6366818</v>
       </c>
       <c r="D198" t="n">
-        <v>4.636668853047462</v>
+        <v>4.635699391022914</v>
       </c>
       <c r="E198" t="n">
         <v>4.515245478460105</v>
@@ -5182,7 +5182,7 @@
         <v>3.1241429</v>
       </c>
       <c r="D216" t="n">
-        <v>4.52720864451838</v>
+        <v>4.528289141652134</v>
       </c>
       <c r="E216" t="n">
         <v>4.51085950651685</v>
@@ -5785,7 +5785,7 @@
         <v>2.1126818</v>
       </c>
       <c r="D235" t="n">
-        <v>4.60816569496789</v>
+        <v>4.607168188650764</v>
       </c>
       <c r="E235" t="n">
         <v>4.532599493153256</v>
@@ -5911,7 +5911,7 @@
         <v>2.1473333</v>
       </c>
       <c r="D239" t="n">
-        <v>4.61512051684126</v>
+        <v>4.616110126026426</v>
       </c>
       <c r="E239" t="n">
         <v>4.540098189244376</v>
@@ -6322,7 +6322,7 @@
         <v>2.3608636</v>
       </c>
       <c r="D252" t="n">
-        <v>4.629862798578463</v>
+        <v>4.630837932736669</v>
       </c>
       <c r="E252" t="n">
         <v>4.571613402459248</v>
@@ -6640,7 +6640,7 @@
         <v>3.335381</v>
       </c>
       <c r="D262" t="n">
-        <v>4.706823839714591</v>
+        <v>4.707726774313183</v>
       </c>
       <c r="E262" t="n">
         <v>4.59511985013459</v>
@@ -7336,7 +7336,7 @@
         <v>4.961</v>
       </c>
       <c r="D284" t="n">
-        <v>4.517431271680085</v>
+        <v>4.516338972281476</v>
       </c>
       <c r="E284" t="n">
         <v>4.618086411254637</v>
@@ -7747,7 +7747,7 @@
         <v>0.8604762</v>
       </c>
       <c r="D297" t="n">
-        <v>4.433194921248282</v>
+        <v>4.432006566978902</v>
       </c>
       <c r="E297" t="n">
         <v>4.447346100794524</v>
@@ -8065,7 +8065,7 @@
         <v>0.7275909</v>
       </c>
       <c r="D307" t="n">
-        <v>4.573679518896721</v>
+        <v>4.572646994282532</v>
       </c>
       <c r="E307" t="n">
         <v>4.523960130562548</v>
@@ -8286,7 +8286,7 @@
         <v>1.0172381</v>
       </c>
       <c r="D314" t="n">
-        <v>4.635699391022914</v>
+        <v>4.636668853047462</v>
       </c>
       <c r="E314" t="n">
         <v>4.549657476057832</v>
@@ -8317,7 +8317,7 @@
         <v>1.08675</v>
       </c>
       <c r="D315" t="n">
-        <v>4.640537329825382</v>
+        <v>4.641502115235482</v>
       </c>
       <c r="E315" t="n">
         <v>4.560172820057356</v>
@@ -8540,7 +8540,7 @@
         <v>1.5364545</v>
       </c>
       <c r="D322" t="n">
-        <v>4.547541073151455</v>
+        <v>4.548599834499697</v>
       </c>
       <c r="E322" t="n">
         <v>4.550714000192032</v>
@@ -8856,7 +8856,7 @@
         <v>0.4970455</v>
       </c>
       <c r="D332" t="n">
-        <v>4.476199804691132</v>
+        <v>4.475061500641071</v>
       </c>
       <c r="E332" t="n">
         <v>4.537961436294641</v>
@@ -9300,7 +9300,7 @@
         <v>0.2232381</v>
       </c>
       <c r="D346" t="n">
-        <v>4.561218298458908</v>
+        <v>4.562262684976814</v>
       </c>
       <c r="E346" t="n">
         <v>4.528289141652134</v>
@@ -9616,7 +9616,7 @@
         <v>0.2050435</v>
       </c>
       <c r="D356" t="n">
-        <v>4.594109238628667</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="E356" t="n">
         <v>4.542230386214217</v>
@@ -9932,7 +9932,7 @@
         <v>-0.0103684</v>
       </c>
       <c r="D366" t="n">
-        <v>4.635699391022914</v>
+        <v>4.634728988229636</v>
       </c>
       <c r="E366" t="n">
         <v>4.563305981889393</v>
@@ -10440,7 +10440,7 @@
         <v>-0.3016364</v>
       </c>
       <c r="D382" t="n">
-        <v>4.648229675448539</v>
+        <v>4.649187071404866</v>
       </c>
       <c r="E382" t="n">
         <v>4.56954300834494</v>
@@ -10820,7 +10820,7 @@
         <v>-0.329381</v>
       </c>
       <c r="D394" t="n">
-        <v>4.727387818712341</v>
+        <v>4.728272383122075</v>
       </c>
       <c r="E394" t="n">
         <v>4.60816569496789</v>
@@ -13131,7 +13131,7 @@
         <v>3.9676364</v>
       </c>
       <c r="D467" t="n">
-        <v>4.540098189244376</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="E467" t="n">
         <v>4.583946549536464</v>
@@ -13195,7 +13195,7 @@
         <v>3.9348947</v>
       </c>
       <c r="D469" t="n">
-        <v>4.571613402459248</v>
+        <v>4.570578741218473</v>
       </c>
       <c r="E469" t="n">
         <v>4.591071261608589</v>
@@ -13352,7 +13352,7 @@
         <v>3.8126818</v>
       </c>
       <c r="D474" t="n">
-        <v>4.56954300834494</v>
+        <v>4.570578741218473</v>
       </c>
       <c r="E474" t="n">
         <v>4.564348191467836</v>
@@ -13480,7 +13480,7 @@
         <v>3.4337143</v>
       </c>
       <c r="D478" t="n">
-        <v>4.565389315976247</v>
+        <v>4.564348191467836</v>
       </c>
       <c r="E478" t="n">
         <v>4.571613402459248</v>
@@ -13575,7 +13575,7 @@
         <v>2.8246</v>
       </c>
       <c r="D481" t="n">
-        <v>4.541164856012179</v>
+        <v>4.540098189244376</v>
       </c>
       <c r="E481" t="n">
         <v>4.56954300834494</v>
@@ -13637,7 +13637,7 @@
         <v>2.52495</v>
       </c>
       <c r="D483" t="n">
-        <v>4.5685062016165</v>
+        <v>4.56746831880408</v>
       </c>
       <c r="E483" t="n">
         <v>4.594109238628667</v>
@@ -13827,7 +13827,7 @@
         <v>2.0210952</v>
       </c>
       <c r="D489" t="n">
-        <v>4.558078578454241</v>
+        <v>4.559126247486684</v>
       </c>
       <c r="E489" t="n">
         <v>4.588024027153121</v>
@@ -13891,7 +13891,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.575741375297279</v>
+        <v>4.574710978503383</v>
       </c>
       <c r="E491" t="n">
         <v>4.589040804058207</v>
@@ -13922,7 +13922,7 @@
         <v>2.04165</v>
       </c>
       <c r="D492" t="n">
-        <v>4.576770711466393</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="E492" t="n">
         <v>4.592084946439436</v>
@@ -14112,7 +14112,7 @@
         <v>2.2261</v>
       </c>
       <c r="D498" t="n">
-        <v>4.545420181582317</v>
+        <v>4.546481189639412</v>
       </c>
       <c r="E498" t="n">
         <v>4.590056548178043</v>
@@ -14221,6 +14221,23 @@
       </c>
       <c r="K501" t="inlineStr"/>
     </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="n">
+        <v>4.583946549536464</v>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14226,7 +14226,9 @@
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>2.6350455</v>
+      </c>
       <c r="D502" t="n">
         <v>4.583946549536464</v>
       </c>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -8932,7 +8932,7 @@
         <v>4.454347296253507</v>
       </c>
       <c r="H334" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="I334" t="n">
         <v>4.339119133662605</v>
@@ -10357,7 +10357,7 @@
         <v>4.495355319980884</v>
       </c>
       <c r="H379" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I379" t="n">
         <v>4.359141762136423</v>
@@ -11687,7 +11687,7 @@
         <v>4.572646994282532</v>
       </c>
       <c r="H421" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I421" t="n">
         <v>4.404521712501253</v>
@@ -11908,7 +11908,7 @@
         <v>4.573679518896721</v>
       </c>
       <c r="H428" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I428" t="n">
         <v>4.403421131528038</v>
@@ -12193,7 +12193,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="H437" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I437" t="n">
         <v>4.420525933824491</v>
@@ -12288,7 +12288,7 @@
         <v>4.617098756853365</v>
       </c>
       <c r="H440" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I440" t="n">
         <v>4.424966385165138</v>
@@ -12447,7 +12447,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="H445" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I445" t="n">
         <v>4.450385972187225</v>
@@ -12858,7 +12858,7 @@
         <v>4.605170185988092</v>
       </c>
       <c r="H458" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I458" t="n">
         <v>4.536891345234797</v>
@@ -14124,7 +14124,7 @@
         <v>4.650143551630823</v>
       </c>
       <c r="H498" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I498" t="n">
         <v>4.635990328327978</v>
@@ -14212,7 +14212,9 @@
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr"/>
-      <c r="H501" t="inlineStr"/>
+      <c r="H501" t="n">
+        <v>6.4</v>
+      </c>
       <c r="I501" t="n">
         <v>4.641405678570186</v>
       </c>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14238,7 +14238,9 @@
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
+      <c r="I502" t="n">
+        <v>4.64736723468788</v>
+      </c>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
     </row>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -3807,9 +3807,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="n">
-        <v>2.258753410709026</v>
-      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
@@ -3832,9 +3830,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="n">
-        <v>2.215215536081905</v>
-      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
@@ -3859,9 +3855,7 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="n">
-        <v>2.441915473829036</v>
-      </c>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -3884,9 +3878,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="n">
-        <v>2.659128391771512</v>
-      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -3909,9 +3901,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="n">
-        <v>2.662351270988468</v>
-      </c>
+      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
@@ -3936,9 +3926,7 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="n">
-        <v>2.726740928159767</v>
-      </c>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -3961,9 +3949,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="n">
-        <v>2.913980159998923</v>
-      </c>
+      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
@@ -3986,9 +3972,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="n">
-        <v>2.948068884549391</v>
-      </c>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -4013,9 +3997,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="n">
-        <v>3.066427754076416</v>
-      </c>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -4038,9 +4020,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="n">
-        <v>3.022792079676902</v>
-      </c>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
@@ -4063,9 +4043,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="n">
-        <v>3.168669786393216</v>
-      </c>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -4092,9 +4070,7 @@
       <c r="I181" t="n">
         <v>4.06009812349351</v>
       </c>
-      <c r="J181" t="n">
-        <v>3.226547861048346</v>
-      </c>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -4123,9 +4099,7 @@
       <c r="I182" t="n">
         <v>4.060443010546419</v>
       </c>
-      <c r="J182" t="n">
-        <v>3.225468226306924</v>
-      </c>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -4154,9 +4128,7 @@
       <c r="I183" t="n">
         <v>4.063713518668578</v>
       </c>
-      <c r="J183" t="n">
-        <v>3.34103145018999</v>
-      </c>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -4187,9 +4159,7 @@
       <c r="I184" t="n">
         <v>4.067315889834181</v>
       </c>
-      <c r="J184" t="n">
-        <v>3.350130044760491</v>
-      </c>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -4218,9 +4188,7 @@
       <c r="I185" t="n">
         <v>4.0683427596831</v>
       </c>
-      <c r="J185" t="n">
-        <v>3.179513594758523</v>
-      </c>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -4249,9 +4217,7 @@
       <c r="I186" t="n">
         <v>4.069539443303129</v>
       </c>
-      <c r="J186" t="n">
-        <v>3.421626507848504</v>
-      </c>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
@@ -4282,9 +4248,7 @@
       <c r="I187" t="n">
         <v>4.072950669534428</v>
       </c>
-      <c r="J187" t="n">
-        <v>3.446668091826526</v>
-      </c>
+      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -4313,9 +4277,7 @@
       <c r="I188" t="n">
         <v>4.073971772414164</v>
       </c>
-      <c r="J188" t="n">
-        <v>3.418440227625302</v>
-      </c>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -4344,9 +4306,7 @@
       <c r="I189" t="n">
         <v>4.074821895733237</v>
       </c>
-      <c r="J189" t="n">
-        <v>3.508705320877654</v>
-      </c>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -4377,9 +4337,7 @@
       <c r="I190" t="n">
         <v>4.079230924412053</v>
       </c>
-      <c r="J190" t="n">
-        <v>3.637575814060428</v>
-      </c>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
@@ -4408,9 +4366,7 @@
       <c r="I191" t="n">
         <v>4.079738409832738</v>
       </c>
-      <c r="J191" t="n">
-        <v>3.589163804837296</v>
-      </c>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -4439,9 +4395,7 @@
       <c r="I192" t="n">
         <v>4.081934542145419</v>
       </c>
-      <c r="J192" t="n">
-        <v>3.637811013938663</v>
-      </c>
+      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -4472,9 +4426,7 @@
       <c r="I193" t="n">
         <v>4.085640121591954</v>
       </c>
-      <c r="J193" t="n">
-        <v>3.353280787370819</v>
-      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -4503,9 +4455,7 @@
       <c r="I194" t="n">
         <v>4.081596989399598</v>
       </c>
-      <c r="J194" t="n">
-        <v>3.307078225746494</v>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -4534,9 +4484,7 @@
       <c r="I195" t="n">
         <v>4.08446256236765</v>
       </c>
-      <c r="J195" t="n">
-        <v>3.39571606791116</v>
-      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -4567,9 +4515,7 @@
       <c r="I196" t="n">
         <v>4.089834406744215</v>
       </c>
-      <c r="J196" t="n">
-        <v>3.293508410131825</v>
-      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -4598,9 +4544,7 @@
       <c r="I197" t="n">
         <v>4.095843438345836</v>
       </c>
-      <c r="J197" t="n">
-        <v>3.359222505589618</v>
-      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -4629,9 +4573,7 @@
       <c r="I198" t="n">
         <v>4.100657924278693</v>
       </c>
-      <c r="J198" t="n">
-        <v>3.477702793014549</v>
-      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -4662,9 +4604,7 @@
       <c r="I199" t="n">
         <v>4.102147374285122</v>
       </c>
-      <c r="J199" t="n">
-        <v>3.485633328125863</v>
-      </c>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
@@ -4693,9 +4633,7 @@
       <c r="I200" t="n">
         <v>4.09982949245267</v>
       </c>
-      <c r="J200" t="n">
-        <v>3.353204381531675</v>
-      </c>
+      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -4724,9 +4662,7 @@
       <c r="I201" t="n">
         <v>4.099000373758295</v>
       </c>
-      <c r="J201" t="n">
-        <v>3.350536906316416</v>
-      </c>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
@@ -4757,9 +4693,7 @@
       <c r="I202" t="n">
         <v>4.101816577060802</v>
       </c>
-      <c r="J202" t="n">
-        <v>3.336481402617774</v>
-      </c>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -4788,9 +4722,7 @@
       <c r="I203" t="n">
         <v>4.102643365036796</v>
       </c>
-      <c r="J203" t="n">
-        <v>3.121238955182699</v>
-      </c>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -4819,9 +4751,7 @@
       <c r="I204" t="n">
         <v>4.101981989351312</v>
       </c>
-      <c r="J204" t="n">
-        <v>3.052292391041955</v>
-      </c>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
@@ -4852,9 +4782,7 @@
       <c r="I205" t="n">
         <v>4.106437809909484</v>
       </c>
-      <c r="J205" t="n">
-        <v>3.042930084242399</v>
-      </c>
+      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -4883,9 +4811,7 @@
       <c r="I206" t="n">
         <v>4.107754249132018</v>
       </c>
-      <c r="J206" t="n">
-        <v>3.090409286188716</v>
-      </c>
+      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -4914,9 +4840,7 @@
       <c r="I207" t="n">
         <v>4.109397364848393</v>
       </c>
-      <c r="J207" t="n">
-        <v>3.148857016980633</v>
-      </c>
+      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -4947,9 +4871,7 @@
       <c r="I208" t="n">
         <v>4.114963849424837</v>
       </c>
-      <c r="J208" t="n">
-        <v>3.298092572755924</v>
-      </c>
+      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
@@ -4978,9 +4900,7 @@
       <c r="I209" t="n">
         <v>4.119524860752399</v>
       </c>
-      <c r="J209" t="n">
-        <v>3.36887333254243</v>
-      </c>
+      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
@@ -5009,9 +4929,7 @@
       <c r="I210" t="n">
         <v>4.121311010451915</v>
       </c>
-      <c r="J210" t="n">
-        <v>3.319426536762864</v>
-      </c>
+      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -5042,9 +4960,7 @@
       <c r="I211" t="n">
         <v>4.120824195026479</v>
       </c>
-      <c r="J211" t="n">
-        <v>3.226964932062586</v>
-      </c>
+      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -5073,9 +4989,7 @@
       <c r="I212" t="n">
         <v>4.119849852630463</v>
       </c>
-      <c r="J212" t="n">
-        <v>3.255894309459665</v>
-      </c>
+      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -5104,9 +5018,7 @@
       <c r="I213" t="n">
         <v>4.120499519698952</v>
       </c>
-      <c r="J213" t="n">
-        <v>3.305281118216779</v>
-      </c>
+      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -5137,9 +5049,7 @@
       <c r="I214" t="n">
         <v>4.123093975508087</v>
       </c>
-      <c r="J214" t="n">
-        <v>3.365780714102301</v>
-      </c>
+      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -5168,9 +5078,7 @@
       <c r="I215" t="n">
         <v>4.12535861575127</v>
       </c>
-      <c r="J215" t="n">
-        <v>3.33471151798654</v>
-      </c>
+      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -5199,9 +5107,7 @@
       <c r="I216" t="n">
         <v>4.124712098838497</v>
       </c>
-      <c r="J216" t="n">
-        <v>3.190760109348617</v>
-      </c>
+      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
@@ -5232,9 +5138,7 @@
       <c r="I217" t="n">
         <v>4.129389903964901</v>
       </c>
-      <c r="J217" t="n">
-        <v>3.325830935922631</v>
-      </c>
+      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -5263,9 +5167,7 @@
       <c r="I218" t="n">
         <v>4.129067998280486</v>
       </c>
-      <c r="J218" t="n">
-        <v>3.379447472555244</v>
-      </c>
+      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
@@ -5294,9 +5196,7 @@
       <c r="I219" t="n">
         <v>4.132924044189576</v>
       </c>
-      <c r="J219" t="n">
-        <v>3.415060193036195</v>
-      </c>
+      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
@@ -5327,9 +5227,7 @@
       <c r="I220" t="n">
         <v>4.138839802108651</v>
       </c>
-      <c r="J220" t="n">
-        <v>3.343761837752438</v>
-      </c>
+      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
@@ -5358,9 +5256,7 @@
       <c r="I221" t="n">
         <v>4.140273494110501</v>
       </c>
-      <c r="J221" t="n">
-        <v>3.137517060500381</v>
-      </c>
+      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
@@ -5389,9 +5285,7 @@
       <c r="I222" t="n">
         <v>4.139636551413807</v>
       </c>
-      <c r="J222" t="n">
-        <v>3.105846743550071</v>
-      </c>
+      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
@@ -5422,9 +5316,7 @@
       <c r="I223" t="n">
         <v>4.140910031369422</v>
       </c>
-      <c r="J223" t="n">
-        <v>3.16580571505022</v>
-      </c>
+      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
@@ -5453,9 +5345,7 @@
       <c r="I224" t="n">
         <v>4.13947725232944</v>
       </c>
-      <c r="J224" t="n">
-        <v>3.216073222588062</v>
-      </c>
+      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -5484,9 +5374,7 @@
       <c r="I225" t="n">
         <v>4.140910031369422</v>
       </c>
-      <c r="J225" t="n">
-        <v>3.289686530763098</v>
-      </c>
+      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -5517,9 +5405,7 @@
       <c r="I226" t="n">
         <v>4.144562278382718</v>
       </c>
-      <c r="J226" t="n">
-        <v>3.184635922382673</v>
-      </c>
+      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
@@ -5548,9 +5434,7 @@
       <c r="I227" t="n">
         <v>4.145987795373939</v>
       </c>
-      <c r="J227" t="n">
-        <v>3.231799825152881</v>
-      </c>
+      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
@@ -5579,9 +5463,7 @@
       <c r="I228" t="n">
         <v>4.146462516484207</v>
       </c>
-      <c r="J228" t="n">
-        <v>3.201467365654374</v>
-      </c>
+      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -5612,9 +5494,7 @@
       <c r="I229" t="n">
         <v>4.14946386144318</v>
       </c>
-      <c r="J229" t="n">
-        <v>3.188999605453866</v>
-      </c>
+      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
@@ -5643,9 +5523,7 @@
       <c r="I230" t="n">
         <v>4.147411283158793</v>
       </c>
-      <c r="J230" t="n">
-        <v>3.210820879103183</v>
-      </c>
+      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
@@ -5674,9 +5552,7 @@
       <c r="I231" t="n">
         <v>4.149779269110201</v>
       </c>
-      <c r="J231" t="n">
-        <v>3.194669396551242</v>
-      </c>
+      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
@@ -5707,9 +5583,7 @@
       <c r="I232" t="n">
         <v>4.156066620850098</v>
       </c>
-      <c r="J232" t="n">
-        <v>3.311526935987064</v>
-      </c>
+      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
@@ -5738,9 +5612,7 @@
       <c r="I233" t="n">
         <v>4.161068194265009</v>
       </c>
-      <c r="J233" t="n">
-        <v>3.333124254236686</v>
-      </c>
+      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -5769,9 +5641,7 @@
       <c r="I234" t="n">
         <v>4.164336934042136</v>
       </c>
-      <c r="J234" t="n">
-        <v>3.443281310025442</v>
-      </c>
+      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
@@ -5802,9 +5672,7 @@
       <c r="I235" t="n">
         <v>4.164803025870662</v>
       </c>
-      <c r="J235" t="n">
-        <v>3.366695591539349</v>
-      </c>
+      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
@@ -5833,9 +5701,7 @@
       <c r="I236" t="n">
         <v>4.162781723775329</v>
       </c>
-      <c r="J236" t="n">
-        <v>3.439123941869134</v>
-      </c>
+      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -5864,9 +5730,7 @@
       <c r="I237" t="n">
         <v>4.164647686064525</v>
       </c>
-      <c r="J237" t="n">
-        <v>3.558257274898917</v>
-      </c>
+      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
@@ -5897,9 +5761,7 @@
       <c r="I238" t="n">
         <v>4.165889729385197</v>
       </c>
-      <c r="J238" t="n">
-        <v>3.565530195301103</v>
-      </c>
+      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
@@ -5928,9 +5790,7 @@
       <c r="I239" t="n">
         <v>4.169761201506855</v>
       </c>
-      <c r="J239" t="n">
-        <v>3.68529675416919</v>
-      </c>
+      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
@@ -5959,9 +5819,7 @@
       <c r="I240" t="n">
         <v>4.168988105217867</v>
       </c>
-      <c r="J240" t="n">
-        <v>3.502055280724579</v>
-      </c>
+      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -5992,9 +5850,7 @@
       <c r="I241" t="n">
         <v>4.172847623710044</v>
       </c>
-      <c r="J241" t="n">
-        <v>3.385591852334123</v>
-      </c>
+      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -6023,9 +5879,7 @@
       <c r="I242" t="n">
         <v>4.166665223801727</v>
       </c>
-      <c r="J242" t="n">
-        <v>3.524215636496602</v>
-      </c>
+      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -6054,9 +5908,7 @@
       <c r="I243" t="n">
         <v>4.170379248498098</v>
       </c>
-      <c r="J243" t="n">
-        <v>3.553812850906649</v>
-      </c>
+      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
@@ -6087,9 +5939,7 @@
       <c r="I244" t="n">
         <v>4.177766170361173</v>
       </c>
-      <c r="J244" t="n">
-        <v>3.69449468787442</v>
-      </c>
+      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
@@ -6118,9 +5968,7 @@
       <c r="I245" t="n">
         <v>4.181897459229962</v>
       </c>
-      <c r="J245" t="n">
-        <v>3.691357095961748</v>
-      </c>
+      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -6149,9 +5997,7 @@
       <c r="I246" t="n">
         <v>4.184032908485631</v>
       </c>
-      <c r="J246" t="n">
-        <v>3.646111041537936</v>
-      </c>
+      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -6182,9 +6028,7 @@
       <c r="I247" t="n">
         <v>4.185251120909776</v>
       </c>
-      <c r="J247" t="n">
-        <v>3.799474203357482</v>
-      </c>
+      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -6213,9 +6057,7 @@
       <c r="I248" t="n">
         <v>4.18418526622189</v>
       </c>
-      <c r="J248" t="n">
-        <v>3.866716742909966</v>
-      </c>
+      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
@@ -6244,9 +6086,7 @@
       <c r="I249" t="n">
         <v>4.186467851097906</v>
       </c>
-      <c r="J249" t="n">
-        <v>3.952171612687482</v>
-      </c>
+      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
@@ -6277,9 +6117,7 @@
       <c r="I250" t="n">
         <v>4.191773707553646</v>
       </c>
-      <c r="J250" t="n">
-        <v>3.938241235307378</v>
-      </c>
+      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -6308,9 +6146,7 @@
       <c r="I251" t="n">
         <v>4.194340715380776</v>
       </c>
-      <c r="J251" t="n">
-        <v>3.88617913885318</v>
-      </c>
+      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
@@ -6339,9 +6175,7 @@
       <c r="I252" t="n">
         <v>4.192227188023968</v>
       </c>
-      <c r="J252" t="n">
-        <v>3.847383175322071</v>
-      </c>
+      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -6372,9 +6206,7 @@
       <c r="I253" t="n">
         <v>4.195546442731068</v>
       </c>
-      <c r="J253" t="n">
-        <v>3.870335097792682</v>
-      </c>
+      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -6403,9 +6235,7 @@
       <c r="I254" t="n">
         <v>4.191168746857641</v>
       </c>
-      <c r="J254" t="n">
-        <v>3.952096454006358</v>
-      </c>
+      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
@@ -6434,9 +6264,7 @@
       <c r="I255" t="n">
         <v>4.1940390562533</v>
       </c>
-      <c r="J255" t="n">
-        <v>3.92066763700997</v>
-      </c>
+      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -6467,9 +6295,7 @@
       <c r="I256" t="n">
         <v>4.199755076629969</v>
       </c>
-      <c r="J256" t="n">
-        <v>3.944114822907218</v>
-      </c>
+      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -6498,9 +6324,7 @@
       <c r="I257" t="n">
         <v>4.206482062158951</v>
       </c>
-      <c r="J257" t="n">
-        <v>4.047535402771049</v>
-      </c>
+      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -6529,9 +6353,7 @@
       <c r="I258" t="n">
         <v>4.209308814022622</v>
       </c>
-      <c r="J258" t="n">
-        <v>4.00086589453139</v>
-      </c>
+      <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
@@ -6562,9 +6384,7 @@
       <c r="I259" t="n">
         <v>4.210051369934071</v>
       </c>
-      <c r="J259" t="n">
-        <v>3.992640745361161</v>
-      </c>
+      <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -6593,9 +6413,7 @@
       <c r="I260" t="n">
         <v>4.208714372037514</v>
       </c>
-      <c r="J260" t="n">
-        <v>4.061865677185565</v>
-      </c>
+      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -6624,9 +6442,7 @@
       <c r="I261" t="n">
         <v>4.20960590255719</v>
       </c>
-      <c r="J261" t="n">
-        <v>4.045862332716973</v>
-      </c>
+      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
@@ -6657,9 +6473,7 @@
       <c r="I262" t="n">
         <v>4.20960590255719</v>
       </c>
-      <c r="J262" t="n">
-        <v>3.885314713908755</v>
-      </c>
+      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -6688,9 +6502,7 @@
       <c r="I263" t="n">
         <v>4.210496638958126</v>
       </c>
-      <c r="J263" t="n">
-        <v>3.825173810764278</v>
-      </c>
+      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
@@ -6719,9 +6531,7 @@
       <c r="I264" t="n">
         <v>4.210941709805915</v>
       </c>
-      <c r="J264" t="n">
-        <v>3.820261328139329</v>
-      </c>
+      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
@@ -6752,9 +6562,7 @@
       <c r="I265" t="n">
         <v>4.214790715297968</v>
       </c>
-      <c r="J265" t="n">
-        <v>3.856086274465855</v>
-      </c>
+      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
@@ -6783,9 +6591,7 @@
       <c r="I266" t="n">
         <v>4.209754413732928</v>
       </c>
-      <c r="J266" t="n">
-        <v>3.720781128802734</v>
-      </c>
+      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -6814,9 +6620,7 @@
       <c r="I267" t="n">
         <v>4.212720014957422</v>
       </c>
-      <c r="J267" t="n">
-        <v>3.784772152402585</v>
-      </c>
+      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
@@ -6847,9 +6651,7 @@
       <c r="I268" t="n">
         <v>4.219360635538369</v>
       </c>
-      <c r="J268" t="n">
-        <v>3.847142306007747</v>
-      </c>
+      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
@@ -6878,9 +6680,7 @@
       <c r="I269" t="n">
         <v>4.225665179549459</v>
       </c>
-      <c r="J269" t="n">
-        <v>3.910678680904513</v>
-      </c>
+      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
@@ -6909,9 +6709,7 @@
       <c r="I270" t="n">
         <v>4.228000947034774</v>
       </c>
-      <c r="J270" t="n">
-        <v>3.90687942094059</v>
-      </c>
+      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -6942,9 +6740,7 @@
       <c r="I271" t="n">
         <v>4.229021132213981</v>
       </c>
-      <c r="J271" t="n">
-        <v>3.969329272586076</v>
-      </c>
+      <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -6973,9 +6769,7 @@
       <c r="I272" t="n">
         <v>4.226687749209813</v>
       </c>
-      <c r="J272" t="n">
-        <v>4.026947802126235</v>
-      </c>
+      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -7004,9 +6798,7 @@
       <c r="I273" t="n">
         <v>4.227563406008323</v>
       </c>
-      <c r="J273" t="n">
-        <v>3.950157720637076</v>
-      </c>
+      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -7037,9 +6829,7 @@
       <c r="I274" t="n">
         <v>4.231349083214389</v>
       </c>
-      <c r="J274" t="n">
-        <v>4.016962461629396</v>
-      </c>
+      <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
@@ -7068,9 +6858,7 @@
       <c r="I275" t="n">
         <v>4.236278058110767</v>
       </c>
-      <c r="J275" t="n">
-        <v>4.05826692580739</v>
-      </c>
+      <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
@@ -7099,9 +6887,7 @@
       <c r="I276" t="n">
         <v>4.241758314110927</v>
       </c>
-      <c r="J276" t="n">
-        <v>4.142086589687808</v>
-      </c>
+      <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
@@ -7132,9 +6918,7 @@
       <c r="I277" t="n">
         <v>4.24577726598231</v>
       </c>
-      <c r="J277" t="n">
-        <v>4.133685166567645</v>
-      </c>
+      <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
@@ -7163,9 +6947,7 @@
       <c r="I278" t="n">
         <v>4.24233343993555</v>
       </c>
-      <c r="J278" t="n">
-        <v>4.137263222529641</v>
-      </c>
+      <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -7194,9 +6976,7 @@
       <c r="I279" t="n">
         <v>4.24592050167689</v>
       </c>
-      <c r="J279" t="n">
-        <v>4.165223405075301</v>
-      </c>
+      <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
@@ -7227,9 +7007,7 @@
       <c r="I280" t="n">
         <v>4.255612709818223</v>
       </c>
-      <c r="J280" t="n">
-        <v>4.200958512284499</v>
-      </c>
+      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
@@ -7258,9 +7036,7 @@
       <c r="I281" t="n">
         <v>4.259011183777335</v>
       </c>
-      <c r="J281" t="n">
-        <v>4.237702860135204</v>
-      </c>
+      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -7289,9 +7065,7 @@
       <c r="I282" t="n">
         <v>4.265211880082047</v>
       </c>
-      <c r="J282" t="n">
-        <v>4.368631410602103</v>
-      </c>
+      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -7322,9 +7096,7 @@
       <c r="I283" t="n">
         <v>4.269137852595263</v>
       </c>
-      <c r="J283" t="n">
-        <v>4.443570086961615</v>
-      </c>
+      <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -7353,9 +7125,7 @@
       <c r="I284" t="n">
         <v>4.267737488271754</v>
       </c>
-      <c r="J284" t="n">
-        <v>4.432736637252135</v>
-      </c>
+      <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -7384,9 +7154,7 @@
       <c r="I285" t="n">
         <v>4.26633516017769</v>
       </c>
-      <c r="J285" t="n">
-        <v>4.325686970335696</v>
-      </c>
+      <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -7417,9 +7185,7 @@
       <c r="I286" t="n">
         <v>4.268297869345539</v>
       </c>
-      <c r="J286" t="n">
-        <v>4.214556494041232</v>
-      </c>
+      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
@@ -7448,9 +7214,7 @@
       <c r="I287" t="n">
         <v>4.268577942166303</v>
       </c>
-      <c r="J287" t="n">
-        <v>3.983977467074896</v>
-      </c>
+      <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
@@ -7479,9 +7243,7 @@
       <c r="I288" t="n">
         <v>4.263806003286451</v>
       </c>
-      <c r="J288" t="n">
-        <v>3.718315137147545</v>
-      </c>
+      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -7512,9 +7274,7 @@
       <c r="I289" t="n">
         <v>4.262398147218351</v>
       </c>
-      <c r="J289" t="n">
-        <v>3.391277145456625</v>
-      </c>
+      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
@@ -7543,9 +7303,7 @@
       <c r="I290" t="n">
         <v>4.254477313726906</v>
       </c>
-      <c r="J290" t="n">
-        <v>3.490823928116463</v>
-      </c>
+      <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
@@ -7574,9 +7332,7 @@
       <c r="I291" t="n">
         <v>4.25858700561615</v>
       </c>
-      <c r="J291" t="n">
-        <v>3.522950371657037</v>
-      </c>
+      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -7607,9 +7363,7 @@
       <c r="I292" t="n">
         <v>4.262257252536892</v>
       </c>
-      <c r="J292" t="n">
-        <v>3.574123049624286</v>
-      </c>
+      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -7638,9 +7392,7 @@
       <c r="I293" t="n">
         <v>4.265773677849632</v>
       </c>
-      <c r="J293" t="n">
-        <v>3.63871992295834</v>
-      </c>
+      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
@@ -7669,9 +7421,7 @@
       <c r="I294" t="n">
         <v>4.26633516017769</v>
       </c>
-      <c r="J294" t="n">
-        <v>3.737113228594204</v>
-      </c>
+      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
@@ -7702,9 +7452,7 @@
       <c r="I295" t="n">
         <v>4.268297869345539</v>
       </c>
-      <c r="J295" t="n">
-        <v>3.890791425559559</v>
-      </c>
+      <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -7733,9 +7481,7 @@
       <c r="I296" t="n">
         <v>4.261693475213995</v>
       </c>
-      <c r="J296" t="n">
-        <v>3.823017883680288</v>
-      </c>
+      <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -7764,9 +7510,7 @@
       <c r="I297" t="n">
         <v>4.26507138131118</v>
       </c>
-      <c r="J297" t="n">
-        <v>3.928290308880902</v>
-      </c>
+      <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -7797,9 +7541,7 @@
       <c r="I298" t="n">
         <v>4.265211880082047</v>
       </c>
-      <c r="J298" t="n">
-        <v>3.838542023544955</v>
-      </c>
+      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -7828,9 +7570,7 @@
       <c r="I299" t="n">
         <v>4.267457179930745</v>
       </c>
-      <c r="J299" t="n">
-        <v>3.894156654259313</v>
-      </c>
+      <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
@@ -7859,9 +7599,7 @@
       <c r="I300" t="n">
         <v>4.268577942166303</v>
       </c>
-      <c r="J300" t="n">
-        <v>3.939632855242714</v>
-      </c>
+      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
@@ -7892,9 +7630,7 @@
       <c r="I301" t="n">
         <v>4.271653577192511</v>
       </c>
-      <c r="J301" t="n">
-        <v>3.930895181543996</v>
-      </c>
+      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -7923,9 +7659,7 @@
       <c r="I302" t="n">
         <v>4.263665306838804</v>
       </c>
-      <c r="J302" t="n">
-        <v>3.977246194839179</v>
-      </c>
+      <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -7954,9 +7688,7 @@
       <c r="I303" t="n">
         <v>4.266756065129537</v>
       </c>
-      <c r="J303" t="n">
-        <v>3.986914596134354</v>
-      </c>
+      <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -7987,9 +7719,7 @@
       <c r="I304" t="n">
         <v>4.277776613300082</v>
       </c>
-      <c r="J304" t="n">
-        <v>4.062126196105137</v>
-      </c>
+      <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
@@ -8018,9 +7748,7 @@
       <c r="I305" t="n">
         <v>4.281791848878036</v>
       </c>
-      <c r="J305" t="n">
-        <v>4.1474364673948</v>
-      </c>
+      <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
@@ -8049,9 +7777,7 @@
       <c r="I306" t="n">
         <v>4.282896668766692</v>
       </c>
-      <c r="J306" t="n">
-        <v>4.101718622674842</v>
-      </c>
+      <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
@@ -8082,9 +7808,7 @@
       <c r="I307" t="n">
         <v>4.283034685466931</v>
       </c>
-      <c r="J307" t="n">
-        <v>4.114735645128339</v>
-      </c>
+      <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -8113,9 +7837,7 @@
       <c r="I308" t="n">
         <v>4.27874728521988</v>
       </c>
-      <c r="J308" t="n">
-        <v>4.080678120870941</v>
-      </c>
+      <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -8144,9 +7866,7 @@
       <c r="I309" t="n">
         <v>4.280685807012206</v>
       </c>
-      <c r="J309" t="n">
-        <v>4.090133672703592</v>
-      </c>
+      <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
@@ -8177,9 +7897,7 @@
       <c r="I310" t="n">
         <v>4.283724483383502</v>
       </c>
-      <c r="J310" t="n">
-        <v>4.087150562864786</v>
-      </c>
+      <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
@@ -8208,9 +7926,7 @@
       <c r="I311" t="n">
         <v>4.286753954166449</v>
       </c>
-      <c r="J311" t="n">
-        <v>4.085710632755419</v>
-      </c>
+      <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
@@ -8239,9 +7955,7 @@
       <c r="I312" t="n">
         <v>4.28771595520264</v>
       </c>
-      <c r="J312" t="n">
-        <v>4.133983322833704</v>
-      </c>
+      <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
@@ -8272,9 +7986,7 @@
       <c r="I313" t="n">
         <v>4.293741719806309</v>
       </c>
-      <c r="J313" t="n">
-        <v>4.236636766982302</v>
-      </c>
+      <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -8303,9 +8015,7 @@
       <c r="I314" t="n">
         <v>4.286753954166449</v>
       </c>
-      <c r="J314" t="n">
-        <v>4.280095116053412</v>
-      </c>
+      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
@@ -8334,9 +8044,7 @@
       <c r="I315" t="n">
         <v>4.290870315632018</v>
       </c>
-      <c r="J315" t="n">
-        <v>4.330617458069195</v>
-      </c>
+      <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -8367,9 +8075,7 @@
       <c r="I316" t="n">
         <v>4.304200219209375</v>
       </c>
-      <c r="J316" t="n">
-        <v>4.405383554850853</v>
-      </c>
+      <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
@@ -8398,9 +8104,7 @@
       <c r="I317" t="n">
         <v>4.309859086371819</v>
       </c>
-      <c r="J317" t="n">
-        <v>4.446754987971143</v>
-      </c>
+      <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
@@ -8429,9 +8133,7 @@
       <c r="I318" t="n">
         <v>4.309859086371819</v>
       </c>
-      <c r="J318" t="n">
-        <v>4.383775350288654</v>
-      </c>
+      <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
@@ -8462,9 +8164,7 @@
       <c r="I319" t="n">
         <v>4.309859086371819</v>
       </c>
-      <c r="J319" t="n">
-        <v>4.370868242117107</v>
-      </c>
+      <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
@@ -8493,9 +8193,7 @@
       <c r="I320" t="n">
         <v>4.304200219209375</v>
       </c>
-      <c r="J320" t="n">
-        <v>4.40674367385013</v>
-      </c>
+      <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
@@ -8524,9 +8222,7 @@
       <c r="I321" t="n">
         <v>4.305955197722586</v>
       </c>
-      <c r="J321" t="n">
-        <v>4.341786286638659</v>
-      </c>
+      <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
@@ -8557,9 +8253,7 @@
       <c r="I322" t="n">
         <v>4.313212318673522</v>
       </c>
-      <c r="J322" t="n">
-        <v>4.405975041403837</v>
-      </c>
+      <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
@@ -8588,9 +8282,7 @@
       <c r="I323" t="n">
         <v>4.316687793365541</v>
       </c>
-      <c r="J323" t="n">
-        <v>4.381108145918606</v>
-      </c>
+      <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
@@ -8619,9 +8311,7 @@
       <c r="I324" t="n">
         <v>4.31748811353631</v>
       </c>
-      <c r="J324" t="n">
-        <v>4.403231937545895</v>
-      </c>
+      <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
@@ -8652,9 +8342,7 @@
       <c r="I325" t="n">
         <v>4.320815903628985</v>
       </c>
-      <c r="J325" t="n">
-        <v>4.404883624474167</v>
-      </c>
+      <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
@@ -8683,9 +8371,7 @@
       <c r="I326" t="n">
         <v>4.312810523985199</v>
       </c>
-      <c r="J326" t="n">
-        <v>4.451714328005695</v>
-      </c>
+      <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -8714,9 +8400,7 @@
       <c r="I327" t="n">
         <v>4.317754744653741</v>
       </c>
-      <c r="J327" t="n">
-        <v>4.502437294970011</v>
-      </c>
+      <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -8747,9 +8431,7 @@
       <c r="I328" t="n">
         <v>4.330601752681694</v>
       </c>
-      <c r="J328" t="n">
-        <v>4.554199781507855</v>
-      </c>
+      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
@@ -8778,9 +8460,7 @@
       <c r="I329" t="n">
         <v>4.335197047317084</v>
       </c>
-      <c r="J329" t="n">
-        <v>4.510677433212988</v>
-      </c>
+      <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
@@ -8809,9 +8489,7 @@
       <c r="I330" t="n">
         <v>4.334017415487521</v>
       </c>
-      <c r="J330" t="n">
-        <v>4.457573282793912</v>
-      </c>
+      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
@@ -8842,9 +8520,7 @@
       <c r="I331" t="n">
         <v>4.333230220484919</v>
       </c>
-      <c r="J331" t="n">
-        <v>4.330315484887012</v>
-      </c>
+      <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
@@ -8873,9 +8549,7 @@
       <c r="I332" t="n">
         <v>4.327966357823938</v>
       </c>
-      <c r="J332" t="n">
-        <v>4.424957771782873</v>
-      </c>
+      <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
@@ -8904,9 +8578,7 @@
       <c r="I333" t="n">
         <v>4.331916850188431</v>
       </c>
-      <c r="J333" t="n">
-        <v>4.515460722082998</v>
-      </c>
+      <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
@@ -8937,9 +8609,7 @@
       <c r="I334" t="n">
         <v>4.339119133662605</v>
       </c>
-      <c r="J334" t="n">
-        <v>4.474945912779694</v>
-      </c>
+      <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
@@ -8968,9 +8638,7 @@
       <c r="I335" t="n">
         <v>4.341465022917759</v>
       </c>
-      <c r="J335" t="n">
-        <v>4.455530561139925</v>
-      </c>
+      <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -8999,9 +8667,7 @@
       <c r="I336" t="n">
         <v>4.339380059952409</v>
       </c>
-      <c r="J336" t="n">
-        <v>4.442874261198329</v>
-      </c>
+      <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
@@ -9032,9 +8698,7 @@
       <c r="I337" t="n">
         <v>4.342895917470844</v>
       </c>
-      <c r="J337" t="n">
-        <v>4.42432867016139</v>
-      </c>
+      <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
@@ -9063,9 +8727,7 @@
       <c r="I338" t="n">
         <v>4.332705079341171</v>
       </c>
-      <c r="J338" t="n">
-        <v>4.442754073712507</v>
-      </c>
+      <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
@@ -9094,9 +8756,7 @@
       <c r="I339" t="n">
         <v>4.336244442018754</v>
       </c>
-      <c r="J339" t="n">
-        <v>4.464412167918701</v>
-      </c>
+      <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
@@ -9127,9 +8787,7 @@
       <c r="I340" t="n">
         <v>4.347823313332383</v>
       </c>
-      <c r="J340" t="n">
-        <v>4.426913299917369</v>
-      </c>
+      <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
@@ -9158,9 +8816,7 @@
       <c r="I341" t="n">
         <v>4.347046915777855</v>
       </c>
-      <c r="J341" t="n">
-        <v>4.363058527792747</v>
-      </c>
+      <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
@@ -9189,9 +8845,7 @@
       <c r="I342" t="n">
         <v>4.348081978620944</v>
       </c>
-      <c r="J342" t="n">
-        <v>4.369465802209772</v>
-      </c>
+      <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
@@ -9222,9 +8876,7 @@
       <c r="I343" t="n">
         <v>4.349115971216622</v>
       </c>
-      <c r="J343" t="n">
-        <v>4.357172886933424</v>
-      </c>
+      <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
@@ -9253,9 +8905,7 @@
       <c r="I344" t="n">
         <v>4.343805421853684</v>
       </c>
-      <c r="J344" t="n">
-        <v>4.412973643773758</v>
-      </c>
+      <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -9284,9 +8934,7 @@
       <c r="I345" t="n">
         <v>4.345103280569283</v>
       </c>
-      <c r="J345" t="n">
-        <v>4.426156574647868</v>
-      </c>
+      <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
@@ -9317,9 +8965,7 @@
       <c r="I346" t="n">
         <v>4.349890764643811</v>
       </c>
-      <c r="J346" t="n">
-        <v>4.426146717086199</v>
-      </c>
+      <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
@@ -9348,9 +8994,7 @@
       <c r="I347" t="n">
         <v>4.348599108561364</v>
       </c>
-      <c r="J347" t="n">
-        <v>4.382029823403645</v>
-      </c>
+      <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -9379,9 +9023,7 @@
       <c r="I348" t="n">
         <v>4.347693955593376</v>
       </c>
-      <c r="J348" t="n">
-        <v>4.380606008697423</v>
-      </c>
+      <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
@@ -9412,9 +9054,7 @@
       <c r="I349" t="n">
         <v>4.351180754502781</v>
       </c>
-      <c r="J349" t="n">
-        <v>4.392292219259067</v>
-      </c>
+      <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
@@ -9443,9 +9083,7 @@
       <c r="I350" t="n">
         <v>4.340162430575183</v>
       </c>
-      <c r="J350" t="n">
-        <v>4.375005298927058</v>
-      </c>
+      <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -9474,9 +9112,7 @@
       <c r="I351" t="n">
         <v>4.343155860284888</v>
       </c>
-      <c r="J351" t="n">
-        <v>4.37865308448309</v>
-      </c>
+      <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -9507,9 +9143,7 @@
       <c r="I352" t="n">
         <v>4.352340324303521</v>
       </c>
-      <c r="J352" t="n">
-        <v>4.353590454993498</v>
-      </c>
+      <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -9538,9 +9172,7 @@
       <c r="I353" t="n">
         <v>4.353884328727601</v>
       </c>
-      <c r="J353" t="n">
-        <v>4.356917645818182</v>
-      </c>
+      <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
@@ -9569,9 +9201,7 @@
       <c r="I354" t="n">
         <v>4.352855257373601</v>
       </c>
-      <c r="J354" t="n">
-        <v>4.379135593579115</v>
-      </c>
+      <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
@@ -9602,9 +9232,7 @@
       <c r="I355" t="n">
         <v>4.353884328727601</v>
       </c>
-      <c r="J355" t="n">
-        <v>4.40978724204682</v>
-      </c>
+      <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
@@ -9633,9 +9261,7 @@
       <c r="I356" t="n">
         <v>4.347435189904263</v>
       </c>
-      <c r="J356" t="n">
-        <v>4.367674826414911</v>
-      </c>
+      <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
@@ -9664,9 +9290,7 @@
       <c r="I357" t="n">
         <v>4.348599108561364</v>
       </c>
-      <c r="J357" t="n">
-        <v>4.334753576649708</v>
-      </c>
+      <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
@@ -9697,9 +9321,7 @@
       <c r="I358" t="n">
         <v>4.352983949221151</v>
       </c>
-      <c r="J358" t="n">
-        <v>4.320890462349924</v>
-      </c>
+      <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
@@ -9728,9 +9350,7 @@
       <c r="I359" t="n">
         <v>4.352340324303521</v>
       </c>
-      <c r="J359" t="n">
-        <v>4.233970404972107</v>
-      </c>
+      <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
@@ -9759,9 +9379,7 @@
       <c r="I360" t="n">
         <v>4.35040696029342</v>
       </c>
-      <c r="J360" t="n">
-        <v>4.1540849451836</v>
-      </c>
+      <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -9792,9 +9410,7 @@
       <c r="I361" t="n">
         <v>4.349503442968322</v>
       </c>
-      <c r="J361" t="n">
-        <v>3.923044918669016</v>
-      </c>
+      <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
@@ -9823,9 +9439,7 @@
       <c r="I362" t="n">
         <v>4.334017415487521</v>
       </c>
-      <c r="J362" t="n">
-        <v>3.715931072544266</v>
-      </c>
+      <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
@@ -9854,9 +9468,7 @@
       <c r="I363" t="n">
         <v>4.340162430575183</v>
       </c>
-      <c r="J363" t="n">
-        <v>3.935563850404375</v>
-      </c>
+      <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
@@ -9887,9 +9499,7 @@
       <c r="I364" t="n">
         <v>4.351696284866048</v>
       </c>
-      <c r="J364" t="n">
-        <v>3.942941447545522</v>
-      </c>
+      <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
@@ -9918,9 +9528,7 @@
       <c r="I365" t="n">
         <v>4.355939299910563</v>
       </c>
-      <c r="J365" t="n">
-        <v>4.011269855211339</v>
-      </c>
+      <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
@@ -9949,9 +9557,7 @@
       <c r="I366" t="n">
         <v>4.358758007734528</v>
       </c>
-      <c r="J366" t="n">
-        <v>4.051318257406852</v>
-      </c>
+      <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
@@ -9982,9 +9588,7 @@
       <c r="I367" t="n">
         <v>4.358885942232239</v>
       </c>
-      <c r="J367" t="n">
-        <v>4.004202923709484</v>
-      </c>
+      <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
@@ -10013,9 +9617,7 @@
       <c r="I368" t="n">
         <v>4.352855257373601</v>
       </c>
-      <c r="J368" t="n">
-        <v>3.940375314509715</v>
-      </c>
+      <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
@@ -10044,9 +9646,7 @@
       <c r="I369" t="n">
         <v>4.352855257373601</v>
       </c>
-      <c r="J369" t="n">
-        <v>3.732010681806484</v>
-      </c>
+      <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
@@ -10077,9 +9677,7 @@
       <c r="I370" t="n">
         <v>4.35491234218231</v>
       </c>
-      <c r="J370" t="n">
-        <v>3.748034708116403</v>
-      </c>
+      <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
@@ -10108,9 +9706,7 @@
       <c r="I371" t="n">
         <v>4.356067595503785</v>
       </c>
-      <c r="J371" t="n">
-        <v>3.763662552207743</v>
-      </c>
+      <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
@@ -10139,9 +9735,7 @@
       <c r="I372" t="n">
         <v>4.351696284866048</v>
       </c>
-      <c r="J372" t="n">
-        <v>3.719289759508769</v>
-      </c>
+      <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
@@ -10172,9 +9766,7 @@
       <c r="I373" t="n">
         <v>4.35182512594076</v>
       </c>
-      <c r="J373" t="n">
-        <v>3.553767192184088</v>
-      </c>
+      <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
@@ -10203,9 +9795,7 @@
       <c r="I374" t="n">
         <v>4.337160013333775</v>
       </c>
-      <c r="J374" t="n">
-        <v>3.34179366196171</v>
-      </c>
+      <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
@@ -10234,9 +9824,7 @@
       <c r="I375" t="n">
         <v>4.33872761652873</v>
       </c>
-      <c r="J375" t="n">
-        <v>3.367620248522414</v>
-      </c>
+      <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -10267,9 +9855,7 @@
       <c r="I376" t="n">
         <v>4.351051830374451</v>
       </c>
-      <c r="J376" t="n">
-        <v>3.538767276615476</v>
-      </c>
+      <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
@@ -10298,9 +9884,7 @@
       <c r="I377" t="n">
         <v>4.353241283242128</v>
       </c>
-      <c r="J377" t="n">
-        <v>3.601939466251815</v>
-      </c>
+      <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
@@ -10329,9 +9913,7 @@
       <c r="I378" t="n">
         <v>4.357349646961441</v>
       </c>
-      <c r="J378" t="n">
-        <v>3.721401681359362</v>
-      </c>
+      <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
@@ -10362,9 +9944,7 @@
       <c r="I379" t="n">
         <v>4.359141762136423</v>
       </c>
-      <c r="J379" t="n">
-        <v>3.760489299141885</v>
-      </c>
+      <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
@@ -10393,9 +9973,7 @@
       <c r="I380" t="n">
         <v>4.354269957628839</v>
       </c>
-      <c r="J380" t="n">
-        <v>3.704030466622941</v>
-      </c>
+      <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
@@ -10424,9 +10002,7 @@
       <c r="I381" t="n">
         <v>4.35491234218231</v>
       </c>
-      <c r="J381" t="n">
-        <v>3.710780799365191</v>
-      </c>
+      <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
@@ -10457,9 +10033,7 @@
       <c r="I382" t="n">
         <v>4.358630056867486</v>
       </c>
-      <c r="J382" t="n">
-        <v>3.726548908522889</v>
-      </c>
+      <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
@@ -10488,9 +10062,7 @@
       <c r="I383" t="n">
         <v>4.360930671379148</v>
       </c>
-      <c r="J383" t="n">
-        <v>3.804701282415921</v>
-      </c>
+      <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
@@ -10519,9 +10091,7 @@
       <c r="I384" t="n">
         <v>4.357477761752469</v>
       </c>
-      <c r="J384" t="n">
-        <v>3.72378018234094</v>
-      </c>
+      <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
@@ -10552,9 +10122,7 @@
       <c r="I385" t="n">
         <v>4.362716386139382</v>
       </c>
-      <c r="J385" t="n">
-        <v>3.923255924575946</v>
-      </c>
+      <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
@@ -10583,9 +10151,7 @@
       <c r="I386" t="n">
         <v>4.354141431184346</v>
       </c>
-      <c r="J386" t="n">
-        <v>3.94004018203459</v>
-      </c>
+      <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
@@ -10614,9 +10180,7 @@
       <c r="I387" t="n">
         <v>4.358118089622206</v>
       </c>
-      <c r="J387" t="n">
-        <v>3.942682331011386</v>
-      </c>
+      <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
@@ -10647,9 +10211,7 @@
       <c r="I388" t="n">
         <v>4.366278277705742</v>
       </c>
-      <c r="J388" t="n">
-        <v>3.87710054353757</v>
-      </c>
+      <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
@@ -10678,9 +10240,7 @@
       <c r="I389" t="n">
         <v>4.371850028222321</v>
       </c>
-      <c r="J389" t="n">
-        <v>3.887412769449671</v>
-      </c>
+      <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
@@ -10709,9 +10269,7 @@
       <c r="I390" t="n">
         <v>4.371092069621102</v>
       </c>
-      <c r="J390" t="n">
-        <v>3.81807748302197</v>
-      </c>
+      <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
@@ -10742,9 +10300,7 @@
       <c r="I391" t="n">
         <v>4.37197629882038</v>
       </c>
-      <c r="J391" t="n">
-        <v>3.720697595023922</v>
-      </c>
+      <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
@@ -10773,9 +10329,7 @@
       <c r="I392" t="n">
         <v>4.367547313409047</v>
       </c>
-      <c r="J392" t="n">
-        <v>3.740420924409831</v>
-      </c>
+      <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
@@ -10804,9 +10358,7 @@
       <c r="I393" t="n">
         <v>4.37020705786854</v>
       </c>
-      <c r="J393" t="n">
-        <v>3.779372393310901</v>
-      </c>
+      <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -10837,9 +10389,7 @@
       <c r="I394" t="n">
         <v>4.374120463102784</v>
       </c>
-      <c r="J394" t="n">
-        <v>3.852849633341334</v>
-      </c>
+      <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
@@ -10868,9 +10418,7 @@
       <c r="I395" t="n">
         <v>4.37462430490712</v>
       </c>
-      <c r="J395" t="n">
-        <v>3.890191789722997</v>
-      </c>
+      <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -10899,9 +10447,7 @@
       <c r="I396" t="n">
         <v>4.37260741275739</v>
       </c>
-      <c r="J396" t="n">
-        <v>3.978274575412832</v>
-      </c>
+      <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
@@ -10932,9 +10478,7 @@
       <c r="I397" t="n">
         <v>4.376008562348319</v>
       </c>
-      <c r="J397" t="n">
-        <v>3.996069257730837</v>
-      </c>
+      <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
@@ -10963,9 +10507,7 @@
       <c r="I398" t="n">
         <v>4.367039892365558</v>
       </c>
-      <c r="J398" t="n">
-        <v>4.036455378979721</v>
-      </c>
+      <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -10994,9 +10536,7 @@
       <c r="I399" t="n">
         <v>4.369194655858504</v>
       </c>
-      <c r="J399" t="n">
-        <v>3.968405451542542</v>
-      </c>
+      <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
@@ -11027,9 +10567,7 @@
       <c r="I400" t="n">
         <v>4.380149874661021</v>
       </c>
-      <c r="J400" t="n">
-        <v>3.980005562040444</v>
-      </c>
+      <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
@@ -11058,9 +10596,7 @@
       <c r="I401" t="n">
         <v>4.38414938005486</v>
       </c>
-      <c r="J401" t="n">
-        <v>4.073107249536162</v>
-      </c>
+      <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
@@ -11089,9 +10625,7 @@
       <c r="I402" t="n">
         <v>4.390366758948883</v>
       </c>
-      <c r="J402" t="n">
-        <v>4.176995536319429</v>
-      </c>
+      <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
@@ -11122,9 +10656,7 @@
       <c r="I403" t="n">
         <v>4.391605609454205</v>
       </c>
-      <c r="J403" t="n">
-        <v>4.154444238812214</v>
-      </c>
+      <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
@@ -11153,9 +10685,7 @@
       <c r="I404" t="n">
         <v>4.38937457233642</v>
       </c>
-      <c r="J404" t="n">
-        <v>4.151654664766028</v>
-      </c>
+      <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
@@ -11184,9 +10714,7 @@
       <c r="I405" t="n">
         <v>4.390862483336281</v>
       </c>
-      <c r="J405" t="n">
-        <v>4.13999027392105</v>
-      </c>
+      <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
@@ -11217,9 +10745,7 @@
       <c r="I406" t="n">
         <v>4.394819456472634</v>
       </c>
-      <c r="J406" t="n">
-        <v>4.214586887675727</v>
-      </c>
+      <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
@@ -11248,9 +10774,7 @@
       <c r="I407" t="n">
         <v>4.397161522258152</v>
       </c>
-      <c r="J407" t="n">
-        <v>4.256446001229222</v>
-      </c>
+      <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
@@ -11279,9 +10803,7 @@
       <c r="I408" t="n">
         <v>4.391729410135267</v>
       </c>
-      <c r="J408" t="n">
-        <v>4.042416369390097</v>
-      </c>
+      <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
@@ -11312,9 +10834,7 @@
       <c r="I409" t="n">
         <v>4.391234115424795</v>
       </c>
-      <c r="J409" t="n">
-        <v>3.91970493549282</v>
-      </c>
+      <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
@@ -11343,9 +10863,7 @@
       <c r="I410" t="n">
         <v>4.380901001386372</v>
       </c>
-      <c r="J410" t="n">
-        <v>3.951995940956316</v>
-      </c>
+      <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
@@ -11374,9 +10892,7 @@
       <c r="I411" t="n">
         <v>4.384024637336554</v>
       </c>
-      <c r="J411" t="n">
-        <v>4.031523920579169</v>
-      </c>
+      <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
@@ -11407,9 +10923,7 @@
       <c r="I412" t="n">
         <v>4.394078715698023</v>
       </c>
-      <c r="J412" t="n">
-        <v>4.069336966934754</v>
-      </c>
+      <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
@@ -11438,9 +10952,7 @@
       <c r="I413" t="n">
         <v>4.401216329067023</v>
       </c>
-      <c r="J413" t="n">
-        <v>4.149176032590502</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
@@ -11469,9 +10981,7 @@
       <c r="I414" t="n">
         <v>4.40256428589143</v>
       </c>
-      <c r="J414" t="n">
-        <v>4.15522486667411</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
@@ -11502,9 +11012,7 @@
       <c r="I415" t="n">
         <v>4.404154986746883</v>
       </c>
-      <c r="J415" t="n">
-        <v>4.040681297369372</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
@@ -11533,9 +11041,7 @@
       <c r="I416" t="n">
         <v>4.399620943074833</v>
       </c>
-      <c r="J416" t="n">
-        <v>4.042662882146143</v>
-      </c>
+      <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
@@ -11564,9 +11070,7 @@
       <c r="I417" t="n">
         <v>4.400971050674819</v>
       </c>
-      <c r="J417" t="n">
-        <v>3.971495134668775</v>
-      </c>
+      <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
@@ -11597,9 +11101,7 @@
       <c r="I418" t="n">
         <v>4.403054001865957</v>
       </c>
-      <c r="J418" t="n">
-        <v>4.044767571245441</v>
-      </c>
+      <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
@@ -11628,9 +11130,7 @@
       <c r="I419" t="n">
         <v>4.404521712501253</v>
       </c>
-      <c r="J419" t="n">
-        <v>3.989422056160758</v>
-      </c>
+      <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
@@ -11659,9 +11159,7 @@
       <c r="I420" t="n">
         <v>4.401338945706255</v>
       </c>
-      <c r="J420" t="n">
-        <v>4.046530996907043</v>
-      </c>
+      <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
@@ -11692,9 +11190,7 @@
       <c r="I421" t="n">
         <v>4.404521712501253</v>
       </c>
-      <c r="J421" t="n">
-        <v>4.103737820516812</v>
-      </c>
+      <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
@@ -11723,9 +11219,7 @@
       <c r="I422" t="n">
         <v>4.3945726038424</v>
       </c>
-      <c r="J422" t="n">
-        <v>4.049006550182978</v>
-      </c>
+      <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
@@ -11754,9 +11248,7 @@
       <c r="I423" t="n">
         <v>4.396299293960601</v>
       </c>
-      <c r="J423" t="n">
-        <v>3.932625449438198</v>
-      </c>
+      <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
@@ -11787,9 +11279,7 @@
       <c r="I424" t="n">
         <v>4.401584133889412</v>
       </c>
-      <c r="J424" t="n">
-        <v>3.364990262308884</v>
-      </c>
+      <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
@@ -11818,9 +11308,7 @@
       <c r="I425" t="n">
         <v>4.404399485525607</v>
       </c>
-      <c r="J425" t="n">
-        <v>2.828586956758972</v>
-      </c>
+      <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
@@ -11849,9 +11337,7 @@
       <c r="I426" t="n">
         <v>4.403421131528038</v>
       </c>
-      <c r="J426" t="n">
-        <v>3.293966764135656</v>
-      </c>
+      <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
@@ -11882,9 +11368,7 @@
       <c r="I427" t="n">
         <v>4.40684119104832</v>
       </c>
-      <c r="J427" t="n">
-        <v>3.577415741641218</v>
-      </c>
+      <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
@@ -11913,9 +11397,7 @@
       <c r="I428" t="n">
         <v>4.403421131528038</v>
       </c>
-      <c r="J428" t="n">
-        <v>3.630192492919949</v>
-      </c>
+      <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
@@ -11944,9 +11426,7 @@
       <c r="I429" t="n">
         <v>4.399252415338951</v>
       </c>
-      <c r="J429" t="n">
-        <v>3.632975395179463</v>
-      </c>
+      <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
@@ -11977,9 +11457,7 @@
       <c r="I430" t="n">
         <v>4.399989335048054</v>
       </c>
-      <c r="J430" t="n">
-        <v>3.546503597848869</v>
-      </c>
+      <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
@@ -12008,9 +11486,7 @@
       <c r="I431" t="n">
         <v>4.401829261970061</v>
       </c>
-      <c r="J431" t="n">
-        <v>3.530209220637321</v>
-      </c>
+      <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
@@ -12039,9 +11515,7 @@
       <c r="I432" t="n">
         <v>4.398514952178684</v>
       </c>
-      <c r="J432" t="n">
-        <v>3.585243142644741</v>
-      </c>
+      <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
@@ -12072,9 +11546,7 @@
       <c r="I433" t="n">
         <v>4.401706705440709</v>
       </c>
-      <c r="J433" t="n">
-        <v>3.715456581471767</v>
-      </c>
+      <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
@@ -12103,9 +11575,7 @@
       <c r="I434" t="n">
         <v>4.403421131528038</v>
       </c>
-      <c r="J434" t="n">
-        <v>3.806683943350821</v>
-      </c>
+      <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
@@ -12134,9 +11604,7 @@
       <c r="I435" t="n">
         <v>4.405498990859024</v>
       </c>
-      <c r="J435" t="n">
-        <v>3.941193556138346</v>
-      </c>
+      <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
@@ -12167,9 +11635,7 @@
       <c r="I436" t="n">
         <v>4.414856779264584</v>
       </c>
-      <c r="J436" t="n">
-        <v>4.006798574135988</v>
-      </c>
+      <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -12198,9 +11664,7 @@
       <c r="I437" t="n">
         <v>4.420525933824491</v>
       </c>
-      <c r="J437" t="n">
-        <v>3.990881540777088</v>
-      </c>
+      <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
@@ -12229,9 +11693,7 @@
       <c r="I438" t="n">
         <v>4.423168578005057</v>
       </c>
-      <c r="J438" t="n">
-        <v>4.032864642254908</v>
-      </c>
+      <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -12262,9 +11724,7 @@
       <c r="I439" t="n">
         <v>4.425684604013345</v>
       </c>
-      <c r="J439" t="n">
-        <v>4.10641070405884</v>
-      </c>
+      <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
@@ -12293,9 +11753,7 @@
       <c r="I440" t="n">
         <v>4.424966385165138</v>
       </c>
-      <c r="J440" t="n">
-        <v>4.152390485546104</v>
-      </c>
+      <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -12324,9 +11782,7 @@
       <c r="I441" t="n">
         <v>4.428433007488037</v>
       </c>
-      <c r="J441" t="n">
-        <v>4.09602924423503</v>
-      </c>
+      <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
@@ -12357,9 +11813,7 @@
       <c r="I442" t="n">
         <v>4.433076149349573</v>
       </c>
-      <c r="J442" t="n">
-        <v>4.147669026985889</v>
-      </c>
+      <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
@@ -12388,9 +11842,7 @@
       <c r="I443" t="n">
         <v>4.441591872011272</v>
       </c>
-      <c r="J443" t="n">
-        <v>4.276778304247688</v>
-      </c>
+      <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -12419,9 +11871,7 @@
       <c r="I444" t="n">
         <v>4.446057214331018</v>
       </c>
-      <c r="J444" t="n">
-        <v>4.26280668671896</v>
-      </c>
+      <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
@@ -12452,9 +11902,7 @@
       <c r="I445" t="n">
         <v>4.450385972187225</v>
       </c>
-      <c r="J445" t="n">
-        <v>4.183807434906146</v>
-      </c>
+      <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
@@ -12483,9 +11931,7 @@
       <c r="I446" t="n">
         <v>4.453416630760555</v>
       </c>
-      <c r="J446" t="n">
-        <v>4.336762122546151</v>
-      </c>
+      <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
@@ -12514,9 +11960,7 @@
       <c r="I447" t="n">
         <v>4.462799844696365</v>
       </c>
-      <c r="J447" t="n">
-        <v>4.45013154764248</v>
-      </c>
+      <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -12547,9 +11991,7 @@
       <c r="I448" t="n">
         <v>4.486836999026226</v>
       </c>
-      <c r="J448" t="n">
-        <v>4.667276390576368</v>
-      </c>
+      <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
@@ -12578,9 +12020,7 @@
       <c r="I449" t="n">
         <v>4.492673154760945</v>
       </c>
-      <c r="J449" t="n">
-        <v>4.571257898024519</v>
-      </c>
+      <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
@@ -12609,9 +12049,7 @@
       <c r="I450" t="n">
         <v>4.501031146246946</v>
       </c>
-      <c r="J450" t="n">
-        <v>4.674153604294284</v>
-      </c>
+      <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
@@ -12642,9 +12080,7 @@
       <c r="I451" t="n">
         <v>4.50920979484218</v>
       </c>
-      <c r="J451" t="n">
-        <v>4.754784850242117</v>
-      </c>
+      <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
@@ -12673,9 +12109,7 @@
       <c r="I452" t="n">
         <v>4.510419849442281</v>
       </c>
-      <c r="J452" t="n">
-        <v>4.700141350799962</v>
-      </c>
+      <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
@@ -12704,9 +12138,7 @@
       <c r="I453" t="n">
         <v>4.516448255927287</v>
       </c>
-      <c r="J453" t="n">
-        <v>4.596898391001972</v>
-      </c>
+      <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -12737,9 +12169,7 @@
       <c r="I454" t="n">
         <v>4.528289141652134</v>
       </c>
-      <c r="J454" t="n">
-        <v>4.506808766658857</v>
-      </c>
+      <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
@@ -12768,9 +12198,7 @@
       <c r="I455" t="n">
         <v>4.542975582394973</v>
       </c>
-      <c r="J455" t="n">
-        <v>4.553728683004673</v>
-      </c>
+      <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
@@ -12799,9 +12227,7 @@
       <c r="I456" t="n">
         <v>4.542336876816522</v>
       </c>
-      <c r="J456" t="n">
-        <v>4.495536876207816</v>
-      </c>
+      <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
@@ -12832,9 +12258,7 @@
       <c r="I457" t="n">
         <v>4.538923540169165</v>
       </c>
-      <c r="J457" t="n">
-        <v>4.336248367125863</v>
-      </c>
+      <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
@@ -12863,9 +12287,7 @@
       <c r="I458" t="n">
         <v>4.536891345234797</v>
       </c>
-      <c r="J458" t="n">
-        <v>4.338711749987938</v>
-      </c>
+      <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
@@ -12894,9 +12316,7 @@
       <c r="I459" t="n">
         <v>4.544889255103161</v>
       </c>
-      <c r="J459" t="n">
-        <v>4.344819739223528</v>
-      </c>
+      <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
@@ -12927,9 +12347,7 @@
       <c r="I460" t="n">
         <v>4.553876891600541</v>
       </c>
-      <c r="J460" t="n">
-        <v>4.294003512825759</v>
-      </c>
+      <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
@@ -12958,9 +12376,7 @@
       <c r="I461" t="n">
         <v>4.560277417097355</v>
       </c>
-      <c r="J461" t="n">
-        <v>4.346035445366231</v>
-      </c>
+      <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
@@ -12989,9 +12405,7 @@
       <c r="I462" t="n">
         <v>4.560591142590124</v>
       </c>
-      <c r="J462" t="n">
-        <v>4.240543635410012</v>
-      </c>
+      <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
@@ -13022,9 +12436,7 @@
       <c r="I463" t="n">
         <v>4.563097409566184</v>
       </c>
-      <c r="J463" t="n">
-        <v>4.234707178138777</v>
-      </c>
+      <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
@@ -13053,9 +12465,7 @@
       <c r="I464" t="n">
         <v>4.562262684976814</v>
       </c>
-      <c r="J464" t="n">
-        <v>4.282818716493589</v>
-      </c>
+      <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
@@ -13084,9 +12494,7 @@
       <c r="I465" t="n">
         <v>4.567779796769532</v>
       </c>
-      <c r="J465" t="n">
-        <v>4.369098876045259</v>
-      </c>
+      <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
@@ -13117,9 +12525,7 @@
       <c r="I466" t="n">
         <v>4.570889252011217</v>
       </c>
-      <c r="J466" t="n">
-        <v>4.474167239716883</v>
-      </c>
+      <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
@@ -13148,9 +12554,7 @@
       <c r="I467" t="n">
         <v>4.571716809728872</v>
       </c>
-      <c r="J467" t="n">
-        <v>4.451725009980071</v>
-      </c>
+      <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
@@ -13179,9 +12583,7 @@
       <c r="I468" t="n">
         <v>4.566221435849517</v>
       </c>
-      <c r="J468" t="n">
-        <v>4.340394919180895</v>
-      </c>
+      <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
@@ -13212,9 +12614,7 @@
       <c r="I469" t="n">
         <v>4.567883601202075</v>
       </c>
-      <c r="J469" t="n">
-        <v>4.265496235442415</v>
-      </c>
+      <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
@@ -13243,9 +12643,7 @@
       <c r="I470" t="n">
         <v>4.564348191467836</v>
       </c>
-      <c r="J470" t="n">
-        <v>4.296876699527028</v>
-      </c>
+      <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
@@ -13274,9 +12672,7 @@
       <c r="I471" t="n">
         <v>4.570475216191205</v>
       </c>
-      <c r="J471" t="n">
-        <v>4.348135578866391</v>
-      </c>
+      <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
@@ -13307,9 +12703,7 @@
       <c r="I472" t="n">
         <v>4.578004517915322</v>
       </c>
-      <c r="J472" t="n">
-        <v>4.363839210393138</v>
-      </c>
+      <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
@@ -13338,9 +12732,7 @@
       <c r="I473" t="n">
         <v>4.583742238574471</v>
       </c>
-      <c r="J473" t="n">
-        <v>4.428892922417647</v>
-      </c>
+      <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
@@ -13369,9 +12761,7 @@
       <c r="I474" t="n">
         <v>4.585885424576224</v>
       </c>
-      <c r="J474" t="n">
-        <v>4.325573254163131</v>
-      </c>
+      <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
@@ -13402,9 +12792,7 @@
       <c r="I475" t="n">
         <v>4.588024027153121</v>
       </c>
-      <c r="J475" t="n">
-        <v>4.336605869027755</v>
-      </c>
+      <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
@@ -13433,9 +12821,7 @@
       <c r="I476" t="n">
         <v>4.587820547652979</v>
       </c>
-      <c r="J476" t="n">
-        <v>4.363379549638092</v>
-      </c>
+      <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
@@ -13464,9 +12850,7 @@
       <c r="I477" t="n">
         <v>4.589142424910894</v>
       </c>
-      <c r="J477" t="n">
-        <v>4.290099534882992</v>
-      </c>
+      <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
@@ -13497,9 +12881,7 @@
       <c r="I478" t="n">
         <v>4.588125751378833</v>
       </c>
-      <c r="J478" t="n">
-        <v>4.19943491713264</v>
-      </c>
+      <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
@@ -13528,9 +12910,7 @@
       <c r="I479" t="n">
         <v>4.591578232468624</v>
       </c>
-      <c r="J479" t="n">
-        <v>4.239276530032364</v>
-      </c>
+      <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
@@ -13559,9 +12939,7 @@
       <c r="I480" t="n">
         <v>4.588430861983793</v>
       </c>
-      <c r="J480" t="n">
-        <v>4.247675134582752</v>
-      </c>
+      <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
@@ -13592,9 +12970,7 @@
       <c r="I481" t="n">
         <v>4.591882291661156</v>
       </c>
-      <c r="J481" t="n">
-        <v>4.255407105448533</v>
-      </c>
+      <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
@@ -13623,9 +12999,7 @@
       <c r="I482" t="n">
         <v>4.58934563564112</v>
       </c>
-      <c r="J482" t="n">
-        <v>4.338098261991652</v>
-      </c>
+      <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
@@ -13654,9 +13028,7 @@
       <c r="I483" t="n">
         <v>4.593603549616626</v>
       </c>
-      <c r="J483" t="n">
-        <v>4.282915723826287</v>
-      </c>
+      <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
@@ -13687,9 +13059,7 @@
       <c r="I484" t="n">
         <v>4.599655005299981</v>
       </c>
-      <c r="J484" t="n">
-        <v>4.209162600255272</v>
-      </c>
+      <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
@@ -13718,9 +13088,7 @@
       <c r="I485" t="n">
         <v>4.605170185988092</v>
       </c>
-      <c r="J485" t="n">
-        <v>4.106844198800405</v>
-      </c>
+      <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
@@ -13749,9 +13117,7 @@
       <c r="I486" t="n">
         <v>4.604670060946409</v>
       </c>
-      <c r="J486" t="n">
-        <v>4.045616674707757</v>
-      </c>
+      <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
@@ -13782,9 +13148,7 @@
       <c r="I487" t="n">
         <v>4.607667066186679</v>
       </c>
-      <c r="J487" t="n">
-        <v>4.127689116814509</v>
-      </c>
+      <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
@@ -13813,9 +13177,7 @@
       <c r="I488" t="n">
         <v>4.608065989100117</v>
       </c>
-      <c r="J488" t="n">
-        <v>4.108218266877361</v>
-      </c>
+      <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
@@ -13844,9 +13206,7 @@
       <c r="I489" t="n">
         <v>4.609560534289384</v>
       </c>
-      <c r="J489" t="n">
-        <v>4.066468409690192</v>
-      </c>
+      <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
@@ -13877,9 +13237,7 @@
       <c r="I490" t="n">
         <v>4.610356712675391</v>
       </c>
-      <c r="J490" t="n">
-        <v>4.059606205568766</v>
-      </c>
+      <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
@@ -13908,9 +13266,7 @@
       <c r="I491" t="n">
         <v>4.612542940317504</v>
       </c>
-      <c r="J491" t="n">
-        <v>4.01624492921095</v>
-      </c>
+      <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
@@ -13939,9 +13295,7 @@
       <c r="I492" t="n">
         <v>4.609660091260944</v>
       </c>
-      <c r="J492" t="n">
-        <v>4.010770119212157</v>
-      </c>
+      <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
@@ -13972,9 +13326,7 @@
       <c r="I493" t="n">
         <v>4.611450423945242</v>
       </c>
-      <c r="J493" t="n">
-        <v>3.978058069709093</v>
-      </c>
+      <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
@@ -14003,9 +13355,7 @@
       <c r="I494" t="n">
         <v>4.605869941102364</v>
       </c>
-      <c r="J494" t="n">
-        <v>4.03843794446973</v>
-      </c>
+      <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
@@ -14034,9 +13384,7 @@
       <c r="I495" t="n">
         <v>4.612344389736092</v>
       </c>
-      <c r="J495" t="n">
-        <v>4.093587337351482</v>
-      </c>
+      <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
@@ -14067,9 +13415,7 @@
       <c r="I496" t="n">
         <v>4.624874769262426</v>
       </c>
-      <c r="J496" t="n">
-        <v>4.491170054663795</v>
-      </c>
+      <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
@@ -14098,9 +13444,7 @@
       <c r="I497" t="n">
         <v>4.635117262356044</v>
       </c>
-      <c r="J497" t="n">
-        <v>4.60709889273138</v>
-      </c>
+      <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
@@ -14129,9 +13473,7 @@
       <c r="I498" t="n">
         <v>4.635990328327978</v>
       </c>
-      <c r="J498" t="n">
-        <v>4.519425867367042</v>
-      </c>
+      <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
@@ -14162,9 +13504,7 @@
       <c r="I499" t="n">
         <v>4.635020207956977</v>
       </c>
-      <c r="J499" t="n">
-        <v>4.30602016470409</v>
-      </c>
+      <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
@@ -14193,9 +13533,7 @@
       <c r="I500" t="n">
         <v>4.637153231841142</v>
       </c>
-      <c r="J500" t="n">
-        <v>4.295395297499554</v>
-      </c>
+      <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
@@ -14218,9 +13556,7 @@
       <c r="I501" t="n">
         <v>4.641405678570186</v>
       </c>
-      <c r="J501" t="n">
-        <v>4.363913651397029</v>
-      </c>
+      <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -3807,7 +3807,9 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="n">
+        <v>2.258753410709026</v>
+      </c>
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
@@ -3830,7 +3832,9 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="n">
+        <v>2.215215536081905</v>
+      </c>
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
@@ -3855,7 +3859,9 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="n">
+        <v>2.441915473829036</v>
+      </c>
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -3878,7 +3884,9 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="n">
+        <v>2.659128391771512</v>
+      </c>
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -3901,7 +3909,9 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>2.662351270988468</v>
+      </c>
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
@@ -3926,7 +3936,9 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
+      <c r="J175" t="n">
+        <v>2.726740928159767</v>
+      </c>
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -3949,7 +3961,9 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
+      <c r="J176" t="n">
+        <v>2.913980159998923</v>
+      </c>
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
@@ -3972,7 +3986,9 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
+      <c r="J177" t="n">
+        <v>2.948068884549391</v>
+      </c>
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -3997,7 +4013,9 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+      <c r="J178" t="n">
+        <v>3.066427754076416</v>
+      </c>
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -4020,7 +4038,9 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="n">
+        <v>3.022792079676902</v>
+      </c>
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
@@ -4043,7 +4063,9 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+      <c r="J180" t="n">
+        <v>3.168669786393216</v>
+      </c>
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -4070,7 +4092,9 @@
       <c r="I181" t="n">
         <v>4.06009812349351</v>
       </c>
-      <c r="J181" t="inlineStr"/>
+      <c r="J181" t="n">
+        <v>3.226547861048346</v>
+      </c>
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -4099,7 +4123,9 @@
       <c r="I182" t="n">
         <v>4.060443010546419</v>
       </c>
-      <c r="J182" t="inlineStr"/>
+      <c r="J182" t="n">
+        <v>3.225468226306924</v>
+      </c>
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -4128,7 +4154,9 @@
       <c r="I183" t="n">
         <v>4.063713518668578</v>
       </c>
-      <c r="J183" t="inlineStr"/>
+      <c r="J183" t="n">
+        <v>3.34103145018999</v>
+      </c>
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -4159,7 +4187,9 @@
       <c r="I184" t="n">
         <v>4.067315889834181</v>
       </c>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="n">
+        <v>3.350130044760491</v>
+      </c>
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -4188,7 +4218,9 @@
       <c r="I185" t="n">
         <v>4.0683427596831</v>
       </c>
-      <c r="J185" t="inlineStr"/>
+      <c r="J185" t="n">
+        <v>3.179513594758523</v>
+      </c>
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -4217,7 +4249,9 @@
       <c r="I186" t="n">
         <v>4.069539443303129</v>
       </c>
-      <c r="J186" t="inlineStr"/>
+      <c r="J186" t="n">
+        <v>3.421626507848504</v>
+      </c>
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
@@ -4248,7 +4282,9 @@
       <c r="I187" t="n">
         <v>4.072950669534428</v>
       </c>
-      <c r="J187" t="inlineStr"/>
+      <c r="J187" t="n">
+        <v>3.446668091826526</v>
+      </c>
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -4277,7 +4313,9 @@
       <c r="I188" t="n">
         <v>4.073971772414164</v>
       </c>
-      <c r="J188" t="inlineStr"/>
+      <c r="J188" t="n">
+        <v>3.418440227625302</v>
+      </c>
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -4306,7 +4344,9 @@
       <c r="I189" t="n">
         <v>4.074821895733237</v>
       </c>
-      <c r="J189" t="inlineStr"/>
+      <c r="J189" t="n">
+        <v>3.508705320877654</v>
+      </c>
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -4337,7 +4377,9 @@
       <c r="I190" t="n">
         <v>4.079230924412053</v>
       </c>
-      <c r="J190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>3.637575814060428</v>
+      </c>
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
@@ -4366,7 +4408,9 @@
       <c r="I191" t="n">
         <v>4.079738409832738</v>
       </c>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>3.589163804837296</v>
+      </c>
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -4395,7 +4439,9 @@
       <c r="I192" t="n">
         <v>4.081934542145419</v>
       </c>
-      <c r="J192" t="inlineStr"/>
+      <c r="J192" t="n">
+        <v>3.637811013938663</v>
+      </c>
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -4426,7 +4472,9 @@
       <c r="I193" t="n">
         <v>4.085640121591954</v>
       </c>
-      <c r="J193" t="inlineStr"/>
+      <c r="J193" t="n">
+        <v>3.353280787370819</v>
+      </c>
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -4455,7 +4503,9 @@
       <c r="I194" t="n">
         <v>4.081596989399598</v>
       </c>
-      <c r="J194" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>3.307078225746494</v>
+      </c>
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -4484,7 +4534,9 @@
       <c r="I195" t="n">
         <v>4.08446256236765</v>
       </c>
-      <c r="J195" t="inlineStr"/>
+      <c r="J195" t="n">
+        <v>3.39571606791116</v>
+      </c>
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -4515,7 +4567,9 @@
       <c r="I196" t="n">
         <v>4.089834406744215</v>
       </c>
-      <c r="J196" t="inlineStr"/>
+      <c r="J196" t="n">
+        <v>3.293508410131825</v>
+      </c>
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -4544,7 +4598,9 @@
       <c r="I197" t="n">
         <v>4.095843438345836</v>
       </c>
-      <c r="J197" t="inlineStr"/>
+      <c r="J197" t="n">
+        <v>3.359222505589618</v>
+      </c>
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -4573,7 +4629,9 @@
       <c r="I198" t="n">
         <v>4.100657924278693</v>
       </c>
-      <c r="J198" t="inlineStr"/>
+      <c r="J198" t="n">
+        <v>3.477702793014549</v>
+      </c>
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -4604,7 +4662,9 @@
       <c r="I199" t="n">
         <v>4.102147374285122</v>
       </c>
-      <c r="J199" t="inlineStr"/>
+      <c r="J199" t="n">
+        <v>3.485633328125863</v>
+      </c>
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
@@ -4633,7 +4693,9 @@
       <c r="I200" t="n">
         <v>4.09982949245267</v>
       </c>
-      <c r="J200" t="inlineStr"/>
+      <c r="J200" t="n">
+        <v>3.353204381531675</v>
+      </c>
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -4662,7 +4724,9 @@
       <c r="I201" t="n">
         <v>4.099000373758295</v>
       </c>
-      <c r="J201" t="inlineStr"/>
+      <c r="J201" t="n">
+        <v>3.350536906316416</v>
+      </c>
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
@@ -4693,7 +4757,9 @@
       <c r="I202" t="n">
         <v>4.101816577060802</v>
       </c>
-      <c r="J202" t="inlineStr"/>
+      <c r="J202" t="n">
+        <v>3.336481402617774</v>
+      </c>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -4722,7 +4788,9 @@
       <c r="I203" t="n">
         <v>4.102643365036796</v>
       </c>
-      <c r="J203" t="inlineStr"/>
+      <c r="J203" t="n">
+        <v>3.121238955182699</v>
+      </c>
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -4751,7 +4819,9 @@
       <c r="I204" t="n">
         <v>4.101981989351312</v>
       </c>
-      <c r="J204" t="inlineStr"/>
+      <c r="J204" t="n">
+        <v>3.052292391041955</v>
+      </c>
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
@@ -4782,7 +4852,9 @@
       <c r="I205" t="n">
         <v>4.106437809909484</v>
       </c>
-      <c r="J205" t="inlineStr"/>
+      <c r="J205" t="n">
+        <v>3.042930084242399</v>
+      </c>
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -4811,7 +4883,9 @@
       <c r="I206" t="n">
         <v>4.107754249132018</v>
       </c>
-      <c r="J206" t="inlineStr"/>
+      <c r="J206" t="n">
+        <v>3.090409286188716</v>
+      </c>
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -4840,7 +4914,9 @@
       <c r="I207" t="n">
         <v>4.109397364848393</v>
       </c>
-      <c r="J207" t="inlineStr"/>
+      <c r="J207" t="n">
+        <v>3.148857016980633</v>
+      </c>
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -4871,7 +4947,9 @@
       <c r="I208" t="n">
         <v>4.114963849424837</v>
       </c>
-      <c r="J208" t="inlineStr"/>
+      <c r="J208" t="n">
+        <v>3.298092572755924</v>
+      </c>
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
@@ -4900,7 +4978,9 @@
       <c r="I209" t="n">
         <v>4.119524860752399</v>
       </c>
-      <c r="J209" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>3.36887333254243</v>
+      </c>
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
@@ -4929,7 +5009,9 @@
       <c r="I210" t="n">
         <v>4.121311010451915</v>
       </c>
-      <c r="J210" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>3.319426536762864</v>
+      </c>
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -4960,7 +5042,9 @@
       <c r="I211" t="n">
         <v>4.120824195026479</v>
       </c>
-      <c r="J211" t="inlineStr"/>
+      <c r="J211" t="n">
+        <v>3.226964932062586</v>
+      </c>
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -4989,7 +5073,9 @@
       <c r="I212" t="n">
         <v>4.119849852630463</v>
       </c>
-      <c r="J212" t="inlineStr"/>
+      <c r="J212" t="n">
+        <v>3.255894309459665</v>
+      </c>
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -5018,7 +5104,9 @@
       <c r="I213" t="n">
         <v>4.120499519698952</v>
       </c>
-      <c r="J213" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>3.305281118216779</v>
+      </c>
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -5049,7 +5137,9 @@
       <c r="I214" t="n">
         <v>4.123093975508087</v>
       </c>
-      <c r="J214" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>3.365780714102301</v>
+      </c>
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -5078,7 +5168,9 @@
       <c r="I215" t="n">
         <v>4.12535861575127</v>
       </c>
-      <c r="J215" t="inlineStr"/>
+      <c r="J215" t="n">
+        <v>3.33471151798654</v>
+      </c>
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -5107,7 +5199,9 @@
       <c r="I216" t="n">
         <v>4.124712098838497</v>
       </c>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>3.190760109348617</v>
+      </c>
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
@@ -5138,7 +5232,9 @@
       <c r="I217" t="n">
         <v>4.129389903964901</v>
       </c>
-      <c r="J217" t="inlineStr"/>
+      <c r="J217" t="n">
+        <v>3.325830935922631</v>
+      </c>
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -5167,7 +5263,9 @@
       <c r="I218" t="n">
         <v>4.129067998280486</v>
       </c>
-      <c r="J218" t="inlineStr"/>
+      <c r="J218" t="n">
+        <v>3.379447472555244</v>
+      </c>
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
@@ -5196,7 +5294,9 @@
       <c r="I219" t="n">
         <v>4.132924044189576</v>
       </c>
-      <c r="J219" t="inlineStr"/>
+      <c r="J219" t="n">
+        <v>3.415060193036195</v>
+      </c>
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
@@ -5227,7 +5327,9 @@
       <c r="I220" t="n">
         <v>4.138839802108651</v>
       </c>
-      <c r="J220" t="inlineStr"/>
+      <c r="J220" t="n">
+        <v>3.343761837752438</v>
+      </c>
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
@@ -5256,7 +5358,9 @@
       <c r="I221" t="n">
         <v>4.140273494110501</v>
       </c>
-      <c r="J221" t="inlineStr"/>
+      <c r="J221" t="n">
+        <v>3.137517060500381</v>
+      </c>
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
@@ -5285,7 +5389,9 @@
       <c r="I222" t="n">
         <v>4.139636551413807</v>
       </c>
-      <c r="J222" t="inlineStr"/>
+      <c r="J222" t="n">
+        <v>3.105846743550071</v>
+      </c>
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
@@ -5316,7 +5422,9 @@
       <c r="I223" t="n">
         <v>4.140910031369422</v>
       </c>
-      <c r="J223" t="inlineStr"/>
+      <c r="J223" t="n">
+        <v>3.16580571505022</v>
+      </c>
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
@@ -5345,7 +5453,9 @@
       <c r="I224" t="n">
         <v>4.13947725232944</v>
       </c>
-      <c r="J224" t="inlineStr"/>
+      <c r="J224" t="n">
+        <v>3.216073222588062</v>
+      </c>
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -5374,7 +5484,9 @@
       <c r="I225" t="n">
         <v>4.140910031369422</v>
       </c>
-      <c r="J225" t="inlineStr"/>
+      <c r="J225" t="n">
+        <v>3.289686530763098</v>
+      </c>
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -5405,7 +5517,9 @@
       <c r="I226" t="n">
         <v>4.144562278382718</v>
       </c>
-      <c r="J226" t="inlineStr"/>
+      <c r="J226" t="n">
+        <v>3.184635922382673</v>
+      </c>
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
@@ -5434,7 +5548,9 @@
       <c r="I227" t="n">
         <v>4.145987795373939</v>
       </c>
-      <c r="J227" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>3.231799825152881</v>
+      </c>
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
@@ -5463,7 +5579,9 @@
       <c r="I228" t="n">
         <v>4.146462516484207</v>
       </c>
-      <c r="J228" t="inlineStr"/>
+      <c r="J228" t="n">
+        <v>3.201467365654374</v>
+      </c>
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -5494,7 +5612,9 @@
       <c r="I229" t="n">
         <v>4.14946386144318</v>
       </c>
-      <c r="J229" t="inlineStr"/>
+      <c r="J229" t="n">
+        <v>3.188999605453866</v>
+      </c>
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
@@ -5523,7 +5643,9 @@
       <c r="I230" t="n">
         <v>4.147411283158793</v>
       </c>
-      <c r="J230" t="inlineStr"/>
+      <c r="J230" t="n">
+        <v>3.210820879103183</v>
+      </c>
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
@@ -5552,7 +5674,9 @@
       <c r="I231" t="n">
         <v>4.149779269110201</v>
       </c>
-      <c r="J231" t="inlineStr"/>
+      <c r="J231" t="n">
+        <v>3.194669396551242</v>
+      </c>
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
@@ -5583,7 +5707,9 @@
       <c r="I232" t="n">
         <v>4.156066620850098</v>
       </c>
-      <c r="J232" t="inlineStr"/>
+      <c r="J232" t="n">
+        <v>3.311526935987064</v>
+      </c>
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
@@ -5612,7 +5738,9 @@
       <c r="I233" t="n">
         <v>4.161068194265009</v>
       </c>
-      <c r="J233" t="inlineStr"/>
+      <c r="J233" t="n">
+        <v>3.333124254236686</v>
+      </c>
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -5641,7 +5769,9 @@
       <c r="I234" t="n">
         <v>4.164336934042136</v>
       </c>
-      <c r="J234" t="inlineStr"/>
+      <c r="J234" t="n">
+        <v>3.443281310025442</v>
+      </c>
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
@@ -5672,7 +5802,9 @@
       <c r="I235" t="n">
         <v>4.164803025870662</v>
       </c>
-      <c r="J235" t="inlineStr"/>
+      <c r="J235" t="n">
+        <v>3.366695591539349</v>
+      </c>
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
@@ -5701,7 +5833,9 @@
       <c r="I236" t="n">
         <v>4.162781723775329</v>
       </c>
-      <c r="J236" t="inlineStr"/>
+      <c r="J236" t="n">
+        <v>3.439123941869134</v>
+      </c>
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -5730,7 +5864,9 @@
       <c r="I237" t="n">
         <v>4.164647686064525</v>
       </c>
-      <c r="J237" t="inlineStr"/>
+      <c r="J237" t="n">
+        <v>3.558257274898917</v>
+      </c>
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
@@ -5761,7 +5897,9 @@
       <c r="I238" t="n">
         <v>4.165889729385197</v>
       </c>
-      <c r="J238" t="inlineStr"/>
+      <c r="J238" t="n">
+        <v>3.565530195301103</v>
+      </c>
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
@@ -5790,7 +5928,9 @@
       <c r="I239" t="n">
         <v>4.169761201506855</v>
       </c>
-      <c r="J239" t="inlineStr"/>
+      <c r="J239" t="n">
+        <v>3.68529675416919</v>
+      </c>
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
@@ -5819,7 +5959,9 @@
       <c r="I240" t="n">
         <v>4.168988105217867</v>
       </c>
-      <c r="J240" t="inlineStr"/>
+      <c r="J240" t="n">
+        <v>3.502055280724579</v>
+      </c>
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -5850,7 +5992,9 @@
       <c r="I241" t="n">
         <v>4.172847623710044</v>
       </c>
-      <c r="J241" t="inlineStr"/>
+      <c r="J241" t="n">
+        <v>3.385591852334123</v>
+      </c>
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -5879,7 +6023,9 @@
       <c r="I242" t="n">
         <v>4.166665223801727</v>
       </c>
-      <c r="J242" t="inlineStr"/>
+      <c r="J242" t="n">
+        <v>3.524215636496602</v>
+      </c>
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -5908,7 +6054,9 @@
       <c r="I243" t="n">
         <v>4.170379248498098</v>
       </c>
-      <c r="J243" t="inlineStr"/>
+      <c r="J243" t="n">
+        <v>3.553812850906649</v>
+      </c>
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
@@ -5939,7 +6087,9 @@
       <c r="I244" t="n">
         <v>4.177766170361173</v>
       </c>
-      <c r="J244" t="inlineStr"/>
+      <c r="J244" t="n">
+        <v>3.69449468787442</v>
+      </c>
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
@@ -5968,7 +6118,9 @@
       <c r="I245" t="n">
         <v>4.181897459229962</v>
       </c>
-      <c r="J245" t="inlineStr"/>
+      <c r="J245" t="n">
+        <v>3.691357095961748</v>
+      </c>
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -5997,7 +6149,9 @@
       <c r="I246" t="n">
         <v>4.184032908485631</v>
       </c>
-      <c r="J246" t="inlineStr"/>
+      <c r="J246" t="n">
+        <v>3.646111041537936</v>
+      </c>
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -6028,7 +6182,9 @@
       <c r="I247" t="n">
         <v>4.185251120909776</v>
       </c>
-      <c r="J247" t="inlineStr"/>
+      <c r="J247" t="n">
+        <v>3.799474203357482</v>
+      </c>
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -6057,7 +6213,9 @@
       <c r="I248" t="n">
         <v>4.18418526622189</v>
       </c>
-      <c r="J248" t="inlineStr"/>
+      <c r="J248" t="n">
+        <v>3.866716742909966</v>
+      </c>
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
@@ -6086,7 +6244,9 @@
       <c r="I249" t="n">
         <v>4.186467851097906</v>
       </c>
-      <c r="J249" t="inlineStr"/>
+      <c r="J249" t="n">
+        <v>3.952171612687482</v>
+      </c>
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
@@ -6117,7 +6277,9 @@
       <c r="I250" t="n">
         <v>4.191773707553646</v>
       </c>
-      <c r="J250" t="inlineStr"/>
+      <c r="J250" t="n">
+        <v>3.938241235307378</v>
+      </c>
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -6146,7 +6308,9 @@
       <c r="I251" t="n">
         <v>4.194340715380776</v>
       </c>
-      <c r="J251" t="inlineStr"/>
+      <c r="J251" t="n">
+        <v>3.88617913885318</v>
+      </c>
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
@@ -6175,7 +6339,9 @@
       <c r="I252" t="n">
         <v>4.192227188023968</v>
       </c>
-      <c r="J252" t="inlineStr"/>
+      <c r="J252" t="n">
+        <v>3.847383175322071</v>
+      </c>
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -6206,7 +6372,9 @@
       <c r="I253" t="n">
         <v>4.195546442731068</v>
       </c>
-      <c r="J253" t="inlineStr"/>
+      <c r="J253" t="n">
+        <v>3.870335097792682</v>
+      </c>
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -6235,7 +6403,9 @@
       <c r="I254" t="n">
         <v>4.191168746857641</v>
       </c>
-      <c r="J254" t="inlineStr"/>
+      <c r="J254" t="n">
+        <v>3.952096454006358</v>
+      </c>
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
@@ -6264,7 +6434,9 @@
       <c r="I255" t="n">
         <v>4.1940390562533</v>
       </c>
-      <c r="J255" t="inlineStr"/>
+      <c r="J255" t="n">
+        <v>3.92066763700997</v>
+      </c>
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -6295,7 +6467,9 @@
       <c r="I256" t="n">
         <v>4.199755076629969</v>
       </c>
-      <c r="J256" t="inlineStr"/>
+      <c r="J256" t="n">
+        <v>3.944114822907218</v>
+      </c>
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -6324,7 +6498,9 @@
       <c r="I257" t="n">
         <v>4.206482062158951</v>
       </c>
-      <c r="J257" t="inlineStr"/>
+      <c r="J257" t="n">
+        <v>4.047535402771049</v>
+      </c>
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -6353,7 +6529,9 @@
       <c r="I258" t="n">
         <v>4.209308814022622</v>
       </c>
-      <c r="J258" t="inlineStr"/>
+      <c r="J258" t="n">
+        <v>4.00086589453139</v>
+      </c>
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
@@ -6376,7 +6554,7 @@
         <v>4.739701078945697</v>
       </c>
       <c r="G259" t="n">
-        <v>4.499809670330265</v>
+        <v>4.498697941477575</v>
       </c>
       <c r="H259" t="n">
         <v>8.5</v>
@@ -6384,7 +6562,9 @@
       <c r="I259" t="n">
         <v>4.210051369934071</v>
       </c>
-      <c r="J259" t="inlineStr"/>
+      <c r="J259" t="n">
+        <v>3.992640745361161</v>
+      </c>
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -6413,7 +6593,9 @@
       <c r="I260" t="n">
         <v>4.208714372037514</v>
       </c>
-      <c r="J260" t="inlineStr"/>
+      <c r="J260" t="n">
+        <v>4.061865677185565</v>
+      </c>
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -6442,7 +6624,9 @@
       <c r="I261" t="n">
         <v>4.20960590255719</v>
       </c>
-      <c r="J261" t="inlineStr"/>
+      <c r="J261" t="n">
+        <v>4.045862332716973</v>
+      </c>
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
@@ -6473,7 +6657,9 @@
       <c r="I262" t="n">
         <v>4.20960590255719</v>
       </c>
-      <c r="J262" t="inlineStr"/>
+      <c r="J262" t="n">
+        <v>3.885314713908755</v>
+      </c>
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -6502,7 +6688,9 @@
       <c r="I263" t="n">
         <v>4.210496638958126</v>
       </c>
-      <c r="J263" t="inlineStr"/>
+      <c r="J263" t="n">
+        <v>3.825173810764278</v>
+      </c>
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
@@ -6531,7 +6719,9 @@
       <c r="I264" t="n">
         <v>4.210941709805915</v>
       </c>
-      <c r="J264" t="inlineStr"/>
+      <c r="J264" t="n">
+        <v>3.820261328139329</v>
+      </c>
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
@@ -6562,7 +6752,9 @@
       <c r="I265" t="n">
         <v>4.214790715297968</v>
       </c>
-      <c r="J265" t="inlineStr"/>
+      <c r="J265" t="n">
+        <v>3.856086274465855</v>
+      </c>
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
@@ -6591,7 +6783,9 @@
       <c r="I266" t="n">
         <v>4.209754413732928</v>
       </c>
-      <c r="J266" t="inlineStr"/>
+      <c r="J266" t="n">
+        <v>3.720781128802734</v>
+      </c>
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -6620,7 +6814,9 @@
       <c r="I267" t="n">
         <v>4.212720014957422</v>
       </c>
-      <c r="J267" t="inlineStr"/>
+      <c r="J267" t="n">
+        <v>3.784772152402585</v>
+      </c>
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
@@ -6651,7 +6847,9 @@
       <c r="I268" t="n">
         <v>4.219360635538369</v>
       </c>
-      <c r="J268" t="inlineStr"/>
+      <c r="J268" t="n">
+        <v>3.847142306007747</v>
+      </c>
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
@@ -6680,7 +6878,9 @@
       <c r="I269" t="n">
         <v>4.225665179549459</v>
       </c>
-      <c r="J269" t="inlineStr"/>
+      <c r="J269" t="n">
+        <v>3.910678680904513</v>
+      </c>
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
@@ -6709,7 +6909,9 @@
       <c r="I270" t="n">
         <v>4.228000947034774</v>
       </c>
-      <c r="J270" t="inlineStr"/>
+      <c r="J270" t="n">
+        <v>3.90687942094059</v>
+      </c>
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -6740,7 +6942,9 @@
       <c r="I271" t="n">
         <v>4.229021132213981</v>
       </c>
-      <c r="J271" t="inlineStr"/>
+      <c r="J271" t="n">
+        <v>3.969329272586076</v>
+      </c>
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -6769,7 +6973,9 @@
       <c r="I272" t="n">
         <v>4.226687749209813</v>
       </c>
-      <c r="J272" t="inlineStr"/>
+      <c r="J272" t="n">
+        <v>4.026947802126235</v>
+      </c>
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -6798,7 +7004,9 @@
       <c r="I273" t="n">
         <v>4.227563406008323</v>
       </c>
-      <c r="J273" t="inlineStr"/>
+      <c r="J273" t="n">
+        <v>3.950157720637076</v>
+      </c>
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -6829,7 +7037,9 @@
       <c r="I274" t="n">
         <v>4.231349083214389</v>
       </c>
-      <c r="J274" t="inlineStr"/>
+      <c r="J274" t="n">
+        <v>4.016962461629396</v>
+      </c>
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
@@ -6858,7 +7068,9 @@
       <c r="I275" t="n">
         <v>4.236278058110767</v>
       </c>
-      <c r="J275" t="inlineStr"/>
+      <c r="J275" t="n">
+        <v>4.05826692580739</v>
+      </c>
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
@@ -6887,7 +7099,9 @@
       <c r="I276" t="n">
         <v>4.241758314110927</v>
       </c>
-      <c r="J276" t="inlineStr"/>
+      <c r="J276" t="n">
+        <v>4.142086589687808</v>
+      </c>
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
@@ -6918,7 +7132,9 @@
       <c r="I277" t="n">
         <v>4.24577726598231</v>
       </c>
-      <c r="J277" t="inlineStr"/>
+      <c r="J277" t="n">
+        <v>4.133685166567645</v>
+      </c>
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
@@ -6947,7 +7163,9 @@
       <c r="I278" t="n">
         <v>4.24233343993555</v>
       </c>
-      <c r="J278" t="inlineStr"/>
+      <c r="J278" t="n">
+        <v>4.137263222529641</v>
+      </c>
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -6976,7 +7194,9 @@
       <c r="I279" t="n">
         <v>4.24592050167689</v>
       </c>
-      <c r="J279" t="inlineStr"/>
+      <c r="J279" t="n">
+        <v>4.165223405075301</v>
+      </c>
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
@@ -7007,7 +7227,9 @@
       <c r="I280" t="n">
         <v>4.255612709818223</v>
       </c>
-      <c r="J280" t="inlineStr"/>
+      <c r="J280" t="n">
+        <v>4.200958512284499</v>
+      </c>
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
@@ -7036,7 +7258,9 @@
       <c r="I281" t="n">
         <v>4.259011183777335</v>
       </c>
-      <c r="J281" t="inlineStr"/>
+      <c r="J281" t="n">
+        <v>4.237702860135204</v>
+      </c>
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -7065,7 +7289,9 @@
       <c r="I282" t="n">
         <v>4.265211880082047</v>
       </c>
-      <c r="J282" t="inlineStr"/>
+      <c r="J282" t="n">
+        <v>4.368631410602103</v>
+      </c>
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -7096,7 +7322,9 @@
       <c r="I283" t="n">
         <v>4.269137852595263</v>
       </c>
-      <c r="J283" t="inlineStr"/>
+      <c r="J283" t="n">
+        <v>4.443570086961615</v>
+      </c>
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -7125,7 +7353,9 @@
       <c r="I284" t="n">
         <v>4.267737488271754</v>
       </c>
-      <c r="J284" t="inlineStr"/>
+      <c r="J284" t="n">
+        <v>4.432736637252135</v>
+      </c>
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -7154,7 +7384,9 @@
       <c r="I285" t="n">
         <v>4.26633516017769</v>
       </c>
-      <c r="J285" t="inlineStr"/>
+      <c r="J285" t="n">
+        <v>4.325686970335696</v>
+      </c>
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -7185,7 +7417,9 @@
       <c r="I286" t="n">
         <v>4.268297869345539</v>
       </c>
-      <c r="J286" t="inlineStr"/>
+      <c r="J286" t="n">
+        <v>4.214556494041232</v>
+      </c>
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
@@ -7214,7 +7448,9 @@
       <c r="I287" t="n">
         <v>4.268577942166303</v>
       </c>
-      <c r="J287" t="inlineStr"/>
+      <c r="J287" t="n">
+        <v>3.983977467074896</v>
+      </c>
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
@@ -7243,7 +7479,9 @@
       <c r="I288" t="n">
         <v>4.263806003286451</v>
       </c>
-      <c r="J288" t="inlineStr"/>
+      <c r="J288" t="n">
+        <v>3.718315137147545</v>
+      </c>
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -7274,7 +7512,9 @@
       <c r="I289" t="n">
         <v>4.262398147218351</v>
       </c>
-      <c r="J289" t="inlineStr"/>
+      <c r="J289" t="n">
+        <v>3.391277145456625</v>
+      </c>
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
@@ -7303,7 +7543,9 @@
       <c r="I290" t="n">
         <v>4.254477313726906</v>
       </c>
-      <c r="J290" t="inlineStr"/>
+      <c r="J290" t="n">
+        <v>3.490823928116463</v>
+      </c>
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
@@ -7332,7 +7574,9 @@
       <c r="I291" t="n">
         <v>4.25858700561615</v>
       </c>
-      <c r="J291" t="inlineStr"/>
+      <c r="J291" t="n">
+        <v>3.522950371657037</v>
+      </c>
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -7363,7 +7607,9 @@
       <c r="I292" t="n">
         <v>4.262257252536892</v>
       </c>
-      <c r="J292" t="inlineStr"/>
+      <c r="J292" t="n">
+        <v>3.574123049624286</v>
+      </c>
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -7384,7 +7630,7 @@
         <v>4.685828089005546</v>
       </c>
       <c r="G293" t="n">
-        <v>4.480740107609915</v>
+        <v>4.481871969643598</v>
       </c>
       <c r="H293" t="n">
         <v>9.5</v>
@@ -7392,7 +7638,9 @@
       <c r="I293" t="n">
         <v>4.265773677849632</v>
       </c>
-      <c r="J293" t="inlineStr"/>
+      <c r="J293" t="n">
+        <v>3.63871992295834</v>
+      </c>
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
@@ -7421,7 +7669,9 @@
       <c r="I294" t="n">
         <v>4.26633516017769</v>
       </c>
-      <c r="J294" t="inlineStr"/>
+      <c r="J294" t="n">
+        <v>3.737113228594204</v>
+      </c>
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
@@ -7452,7 +7702,9 @@
       <c r="I295" t="n">
         <v>4.268297869345539</v>
       </c>
-      <c r="J295" t="inlineStr"/>
+      <c r="J295" t="n">
+        <v>3.890791425559559</v>
+      </c>
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -7481,7 +7733,9 @@
       <c r="I296" t="n">
         <v>4.261693475213995</v>
       </c>
-      <c r="J296" t="inlineStr"/>
+      <c r="J296" t="n">
+        <v>3.823017883680288</v>
+      </c>
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -7510,7 +7764,9 @@
       <c r="I297" t="n">
         <v>4.26507138131118</v>
       </c>
-      <c r="J297" t="inlineStr"/>
+      <c r="J297" t="n">
+        <v>3.928290308880902</v>
+      </c>
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -7541,7 +7797,9 @@
       <c r="I298" t="n">
         <v>4.265211880082047</v>
       </c>
-      <c r="J298" t="inlineStr"/>
+      <c r="J298" t="n">
+        <v>3.838542023544955</v>
+      </c>
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -7570,7 +7828,9 @@
       <c r="I299" t="n">
         <v>4.267457179930745</v>
       </c>
-      <c r="J299" t="inlineStr"/>
+      <c r="J299" t="n">
+        <v>3.894156654259313</v>
+      </c>
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
@@ -7599,7 +7859,9 @@
       <c r="I300" t="n">
         <v>4.268577942166303</v>
       </c>
-      <c r="J300" t="inlineStr"/>
+      <c r="J300" t="n">
+        <v>3.939632855242714</v>
+      </c>
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
@@ -7630,7 +7892,9 @@
       <c r="I301" t="n">
         <v>4.271653577192511</v>
       </c>
-      <c r="J301" t="inlineStr"/>
+      <c r="J301" t="n">
+        <v>3.930895181543996</v>
+      </c>
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -7659,7 +7923,9 @@
       <c r="I302" t="n">
         <v>4.263665306838804</v>
       </c>
-      <c r="J302" t="inlineStr"/>
+      <c r="J302" t="n">
+        <v>3.977246194839179</v>
+      </c>
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -7688,7 +7954,9 @@
       <c r="I303" t="n">
         <v>4.266756065129537</v>
       </c>
-      <c r="J303" t="inlineStr"/>
+      <c r="J303" t="n">
+        <v>3.986914596134354</v>
+      </c>
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -7719,7 +7987,9 @@
       <c r="I304" t="n">
         <v>4.277776613300082</v>
       </c>
-      <c r="J304" t="inlineStr"/>
+      <c r="J304" t="n">
+        <v>4.062126196105137</v>
+      </c>
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
@@ -7748,7 +8018,9 @@
       <c r="I305" t="n">
         <v>4.281791848878036</v>
       </c>
-      <c r="J305" t="inlineStr"/>
+      <c r="J305" t="n">
+        <v>4.1474364673948</v>
+      </c>
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
@@ -7777,7 +8049,9 @@
       <c r="I306" t="n">
         <v>4.282896668766692</v>
       </c>
-      <c r="J306" t="inlineStr"/>
+      <c r="J306" t="n">
+        <v>4.101718622674842</v>
+      </c>
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
@@ -7808,7 +8082,9 @@
       <c r="I307" t="n">
         <v>4.283034685466931</v>
       </c>
-      <c r="J307" t="inlineStr"/>
+      <c r="J307" t="n">
+        <v>4.114735645128339</v>
+      </c>
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -7837,7 +8113,9 @@
       <c r="I308" t="n">
         <v>4.27874728521988</v>
       </c>
-      <c r="J308" t="inlineStr"/>
+      <c r="J308" t="n">
+        <v>4.080678120870941</v>
+      </c>
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -7866,7 +8144,9 @@
       <c r="I309" t="n">
         <v>4.280685807012206</v>
       </c>
-      <c r="J309" t="inlineStr"/>
+      <c r="J309" t="n">
+        <v>4.090133672703592</v>
+      </c>
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
@@ -7897,7 +8177,9 @@
       <c r="I310" t="n">
         <v>4.283724483383502</v>
       </c>
-      <c r="J310" t="inlineStr"/>
+      <c r="J310" t="n">
+        <v>4.087150562864786</v>
+      </c>
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
@@ -7926,7 +8208,9 @@
       <c r="I311" t="n">
         <v>4.286753954166449</v>
       </c>
-      <c r="J311" t="inlineStr"/>
+      <c r="J311" t="n">
+        <v>4.085710632755419</v>
+      </c>
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
@@ -7955,7 +8239,9 @@
       <c r="I312" t="n">
         <v>4.28771595520264</v>
       </c>
-      <c r="J312" t="inlineStr"/>
+      <c r="J312" t="n">
+        <v>4.133983322833704</v>
+      </c>
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
@@ -7978,7 +8264,7 @@
         <v>4.526126978647638</v>
       </c>
       <c r="G313" t="n">
-        <v>4.481871969643598</v>
+        <v>4.480740107609915</v>
       </c>
       <c r="H313" t="n">
         <v>10.2</v>
@@ -7986,7 +8272,9 @@
       <c r="I313" t="n">
         <v>4.293741719806309</v>
       </c>
-      <c r="J313" t="inlineStr"/>
+      <c r="J313" t="n">
+        <v>4.236636766982302</v>
+      </c>
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -8015,7 +8303,9 @@
       <c r="I314" t="n">
         <v>4.286753954166449</v>
       </c>
-      <c r="J314" t="inlineStr"/>
+      <c r="J314" t="n">
+        <v>4.280095116053412</v>
+      </c>
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
@@ -8044,7 +8334,9 @@
       <c r="I315" t="n">
         <v>4.290870315632018</v>
       </c>
-      <c r="J315" t="inlineStr"/>
+      <c r="J315" t="n">
+        <v>4.330617458069195</v>
+      </c>
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -8075,7 +8367,9 @@
       <c r="I316" t="n">
         <v>4.304200219209375</v>
       </c>
-      <c r="J316" t="inlineStr"/>
+      <c r="J316" t="n">
+        <v>4.405383554850853</v>
+      </c>
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
@@ -8104,7 +8398,9 @@
       <c r="I317" t="n">
         <v>4.309859086371819</v>
       </c>
-      <c r="J317" t="inlineStr"/>
+      <c r="J317" t="n">
+        <v>4.446754987971143</v>
+      </c>
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
@@ -8133,7 +8429,9 @@
       <c r="I318" t="n">
         <v>4.309859086371819</v>
       </c>
-      <c r="J318" t="inlineStr"/>
+      <c r="J318" t="n">
+        <v>4.383775350288654</v>
+      </c>
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
@@ -8164,7 +8462,9 @@
       <c r="I319" t="n">
         <v>4.309859086371819</v>
       </c>
-      <c r="J319" t="inlineStr"/>
+      <c r="J319" t="n">
+        <v>4.370868242117107</v>
+      </c>
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
@@ -8193,7 +8493,9 @@
       <c r="I320" t="n">
         <v>4.304200219209375</v>
       </c>
-      <c r="J320" t="inlineStr"/>
+      <c r="J320" t="n">
+        <v>4.40674367385013</v>
+      </c>
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
@@ -8222,7 +8524,9 @@
       <c r="I321" t="n">
         <v>4.305955197722586</v>
       </c>
-      <c r="J321" t="inlineStr"/>
+      <c r="J321" t="n">
+        <v>4.341786286638659</v>
+      </c>
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
@@ -8253,7 +8557,9 @@
       <c r="I322" t="n">
         <v>4.313212318673522</v>
       </c>
-      <c r="J322" t="inlineStr"/>
+      <c r="J322" t="n">
+        <v>4.405975041403837</v>
+      </c>
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
@@ -8282,7 +8588,9 @@
       <c r="I323" t="n">
         <v>4.316687793365541</v>
       </c>
-      <c r="J323" t="inlineStr"/>
+      <c r="J323" t="n">
+        <v>4.381108145918606</v>
+      </c>
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
@@ -8311,7 +8619,9 @@
       <c r="I324" t="n">
         <v>4.31748811353631</v>
       </c>
-      <c r="J324" t="inlineStr"/>
+      <c r="J324" t="n">
+        <v>4.403231937545895</v>
+      </c>
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
@@ -8342,7 +8652,9 @@
       <c r="I325" t="n">
         <v>4.320815903628985</v>
       </c>
-      <c r="J325" t="inlineStr"/>
+      <c r="J325" t="n">
+        <v>4.404883624474167</v>
+      </c>
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
@@ -8371,7 +8683,9 @@
       <c r="I326" t="n">
         <v>4.312810523985199</v>
       </c>
-      <c r="J326" t="inlineStr"/>
+      <c r="J326" t="n">
+        <v>4.451714328005695</v>
+      </c>
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -8400,7 +8714,9 @@
       <c r="I327" t="n">
         <v>4.317754744653741</v>
       </c>
-      <c r="J327" t="inlineStr"/>
+      <c r="J327" t="n">
+        <v>4.502437294970011</v>
+      </c>
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -8431,7 +8747,9 @@
       <c r="I328" t="n">
         <v>4.330601752681694</v>
       </c>
-      <c r="J328" t="inlineStr"/>
+      <c r="J328" t="n">
+        <v>4.554199781507855</v>
+      </c>
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
@@ -8460,7 +8778,9 @@
       <c r="I329" t="n">
         <v>4.335197047317084</v>
       </c>
-      <c r="J329" t="inlineStr"/>
+      <c r="J329" t="n">
+        <v>4.510677433212988</v>
+      </c>
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
@@ -8489,7 +8809,9 @@
       <c r="I330" t="n">
         <v>4.334017415487521</v>
       </c>
-      <c r="J330" t="inlineStr"/>
+      <c r="J330" t="n">
+        <v>4.457573282793912</v>
+      </c>
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
@@ -8520,7 +8842,9 @@
       <c r="I331" t="n">
         <v>4.333230220484919</v>
       </c>
-      <c r="J331" t="inlineStr"/>
+      <c r="J331" t="n">
+        <v>4.330315484887012</v>
+      </c>
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
@@ -8549,7 +8873,9 @@
       <c r="I332" t="n">
         <v>4.327966357823938</v>
       </c>
-      <c r="J332" t="inlineStr"/>
+      <c r="J332" t="n">
+        <v>4.424957771782873</v>
+      </c>
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
@@ -8578,7 +8904,9 @@
       <c r="I333" t="n">
         <v>4.331916850188431</v>
       </c>
-      <c r="J333" t="inlineStr"/>
+      <c r="J333" t="n">
+        <v>4.515460722082998</v>
+      </c>
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
@@ -8609,7 +8937,9 @@
       <c r="I334" t="n">
         <v>4.339119133662605</v>
       </c>
-      <c r="J334" t="inlineStr"/>
+      <c r="J334" t="n">
+        <v>4.474945912779694</v>
+      </c>
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
@@ -8638,7 +8968,9 @@
       <c r="I335" t="n">
         <v>4.341465022917759</v>
       </c>
-      <c r="J335" t="inlineStr"/>
+      <c r="J335" t="n">
+        <v>4.455530561139925</v>
+      </c>
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -8667,7 +8999,9 @@
       <c r="I336" t="n">
         <v>4.339380059952409</v>
       </c>
-      <c r="J336" t="inlineStr"/>
+      <c r="J336" t="n">
+        <v>4.442874261198329</v>
+      </c>
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
@@ -8698,7 +9032,9 @@
       <c r="I337" t="n">
         <v>4.342895917470844</v>
       </c>
-      <c r="J337" t="inlineStr"/>
+      <c r="J337" t="n">
+        <v>4.42432867016139</v>
+      </c>
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
@@ -8727,7 +9063,9 @@
       <c r="I338" t="n">
         <v>4.332705079341171</v>
       </c>
-      <c r="J338" t="inlineStr"/>
+      <c r="J338" t="n">
+        <v>4.442754073712507</v>
+      </c>
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
@@ -8756,7 +9094,9 @@
       <c r="I339" t="n">
         <v>4.336244442018754</v>
       </c>
-      <c r="J339" t="inlineStr"/>
+      <c r="J339" t="n">
+        <v>4.464412167918701</v>
+      </c>
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
@@ -8787,7 +9127,9 @@
       <c r="I340" t="n">
         <v>4.347823313332383</v>
       </c>
-      <c r="J340" t="inlineStr"/>
+      <c r="J340" t="n">
+        <v>4.426913299917369</v>
+      </c>
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
@@ -8816,7 +9158,9 @@
       <c r="I341" t="n">
         <v>4.347046915777855</v>
       </c>
-      <c r="J341" t="inlineStr"/>
+      <c r="J341" t="n">
+        <v>4.363058527792747</v>
+      </c>
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
@@ -8845,7 +9189,9 @@
       <c r="I342" t="n">
         <v>4.348081978620944</v>
       </c>
-      <c r="J342" t="inlineStr"/>
+      <c r="J342" t="n">
+        <v>4.369465802209772</v>
+      </c>
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
@@ -8876,7 +9222,9 @@
       <c r="I343" t="n">
         <v>4.349115971216622</v>
       </c>
-      <c r="J343" t="inlineStr"/>
+      <c r="J343" t="n">
+        <v>4.357172886933424</v>
+      </c>
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
@@ -8905,7 +9253,9 @@
       <c r="I344" t="n">
         <v>4.343805421853684</v>
       </c>
-      <c r="J344" t="inlineStr"/>
+      <c r="J344" t="n">
+        <v>4.412973643773758</v>
+      </c>
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -8934,7 +9284,9 @@
       <c r="I345" t="n">
         <v>4.345103280569283</v>
       </c>
-      <c r="J345" t="inlineStr"/>
+      <c r="J345" t="n">
+        <v>4.426156574647868</v>
+      </c>
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
@@ -8965,7 +9317,9 @@
       <c r="I346" t="n">
         <v>4.349890764643811</v>
       </c>
-      <c r="J346" t="inlineStr"/>
+      <c r="J346" t="n">
+        <v>4.426146717086199</v>
+      </c>
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
@@ -8986,7 +9340,7 @@
         <v>4.56954300834494</v>
       </c>
       <c r="G347" t="n">
-        <v>4.45318382899021</v>
+        <v>4.454347296253507</v>
       </c>
       <c r="H347" t="n">
         <v>12.1</v>
@@ -8994,7 +9348,9 @@
       <c r="I347" t="n">
         <v>4.348599108561364</v>
       </c>
-      <c r="J347" t="inlineStr"/>
+      <c r="J347" t="n">
+        <v>4.382029823403645</v>
+      </c>
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -9023,7 +9379,9 @@
       <c r="I348" t="n">
         <v>4.347693955593376</v>
       </c>
-      <c r="J348" t="inlineStr"/>
+      <c r="J348" t="n">
+        <v>4.380606008697423</v>
+      </c>
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
@@ -9046,7 +9404,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="G349" t="n">
-        <v>4.456670177669648</v>
+        <v>4.455509411433685</v>
       </c>
       <c r="H349" t="n">
         <v>12.1</v>
@@ -9054,7 +9412,9 @@
       <c r="I349" t="n">
         <v>4.351180754502781</v>
       </c>
-      <c r="J349" t="inlineStr"/>
+      <c r="J349" t="n">
+        <v>4.392292219259067</v>
+      </c>
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
@@ -9083,7 +9443,9 @@
       <c r="I350" t="n">
         <v>4.340162430575183</v>
       </c>
-      <c r="J350" t="inlineStr"/>
+      <c r="J350" t="n">
+        <v>4.375005298927058</v>
+      </c>
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -9112,7 +9474,9 @@
       <c r="I351" t="n">
         <v>4.343155860284888</v>
       </c>
-      <c r="J351" t="inlineStr"/>
+      <c r="J351" t="n">
+        <v>4.37865308448309</v>
+      </c>
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -9143,7 +9507,9 @@
       <c r="I352" t="n">
         <v>4.352340324303521</v>
       </c>
-      <c r="J352" t="inlineStr"/>
+      <c r="J352" t="n">
+        <v>4.353590454993498</v>
+      </c>
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -9172,7 +9538,9 @@
       <c r="I353" t="n">
         <v>4.353884328727601</v>
       </c>
-      <c r="J353" t="inlineStr"/>
+      <c r="J353" t="n">
+        <v>4.356917645818182</v>
+      </c>
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
@@ -9201,7 +9569,9 @@
       <c r="I354" t="n">
         <v>4.352855257373601</v>
       </c>
-      <c r="J354" t="inlineStr"/>
+      <c r="J354" t="n">
+        <v>4.379135593579115</v>
+      </c>
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
@@ -9232,7 +9602,9 @@
       <c r="I355" t="n">
         <v>4.353884328727601</v>
       </c>
-      <c r="J355" t="inlineStr"/>
+      <c r="J355" t="n">
+        <v>4.40978724204682</v>
+      </c>
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
@@ -9261,7 +9633,9 @@
       <c r="I356" t="n">
         <v>4.347435189904263</v>
       </c>
-      <c r="J356" t="inlineStr"/>
+      <c r="J356" t="n">
+        <v>4.367674826414911</v>
+      </c>
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
@@ -9290,7 +9664,9 @@
       <c r="I357" t="n">
         <v>4.348599108561364</v>
       </c>
-      <c r="J357" t="inlineStr"/>
+      <c r="J357" t="n">
+        <v>4.334753576649708</v>
+      </c>
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
@@ -9321,7 +9697,9 @@
       <c r="I358" t="n">
         <v>4.352983949221151</v>
       </c>
-      <c r="J358" t="inlineStr"/>
+      <c r="J358" t="n">
+        <v>4.320890462349924</v>
+      </c>
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
@@ -9350,7 +9728,9 @@
       <c r="I359" t="n">
         <v>4.352340324303521</v>
       </c>
-      <c r="J359" t="inlineStr"/>
+      <c r="J359" t="n">
+        <v>4.233970404972107</v>
+      </c>
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
@@ -9379,7 +9759,9 @@
       <c r="I360" t="n">
         <v>4.35040696029342</v>
       </c>
-      <c r="J360" t="inlineStr"/>
+      <c r="J360" t="n">
+        <v>4.1540849451836</v>
+      </c>
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -9410,7 +9792,9 @@
       <c r="I361" t="n">
         <v>4.349503442968322</v>
       </c>
-      <c r="J361" t="inlineStr"/>
+      <c r="J361" t="n">
+        <v>3.923044918669016</v>
+      </c>
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
@@ -9439,7 +9823,9 @@
       <c r="I362" t="n">
         <v>4.334017415487521</v>
       </c>
-      <c r="J362" t="inlineStr"/>
+      <c r="J362" t="n">
+        <v>3.715931072544266</v>
+      </c>
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
@@ -9468,7 +9854,9 @@
       <c r="I363" t="n">
         <v>4.340162430575183</v>
       </c>
-      <c r="J363" t="inlineStr"/>
+      <c r="J363" t="n">
+        <v>3.935563850404375</v>
+      </c>
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
@@ -9499,7 +9887,9 @@
       <c r="I364" t="n">
         <v>4.351696284866048</v>
       </c>
-      <c r="J364" t="inlineStr"/>
+      <c r="J364" t="n">
+        <v>3.942941447545522</v>
+      </c>
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
@@ -9528,7 +9918,9 @@
       <c r="I365" t="n">
         <v>4.355939299910563</v>
       </c>
-      <c r="J365" t="inlineStr"/>
+      <c r="J365" t="n">
+        <v>4.011269855211339</v>
+      </c>
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
@@ -9557,7 +9949,9 @@
       <c r="I366" t="n">
         <v>4.358758007734528</v>
       </c>
-      <c r="J366" t="inlineStr"/>
+      <c r="J366" t="n">
+        <v>4.051318257406852</v>
+      </c>
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
@@ -9588,7 +9982,9 @@
       <c r="I367" t="n">
         <v>4.358885942232239</v>
       </c>
-      <c r="J367" t="inlineStr"/>
+      <c r="J367" t="n">
+        <v>4.004202923709484</v>
+      </c>
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
@@ -9617,7 +10013,9 @@
       <c r="I368" t="n">
         <v>4.352855257373601</v>
       </c>
-      <c r="J368" t="inlineStr"/>
+      <c r="J368" t="n">
+        <v>3.940375314509715</v>
+      </c>
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
@@ -9646,7 +10044,9 @@
       <c r="I369" t="n">
         <v>4.352855257373601</v>
       </c>
-      <c r="J369" t="inlineStr"/>
+      <c r="J369" t="n">
+        <v>3.732010681806484</v>
+      </c>
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
@@ -9677,7 +10077,9 @@
       <c r="I370" t="n">
         <v>4.35491234218231</v>
       </c>
-      <c r="J370" t="inlineStr"/>
+      <c r="J370" t="n">
+        <v>3.748034708116403</v>
+      </c>
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
@@ -9706,7 +10108,9 @@
       <c r="I371" t="n">
         <v>4.356067595503785</v>
       </c>
-      <c r="J371" t="inlineStr"/>
+      <c r="J371" t="n">
+        <v>3.763662552207743</v>
+      </c>
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
@@ -9735,7 +10139,9 @@
       <c r="I372" t="n">
         <v>4.351696284866048</v>
       </c>
-      <c r="J372" t="inlineStr"/>
+      <c r="J372" t="n">
+        <v>3.719289759508769</v>
+      </c>
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
@@ -9766,7 +10172,9 @@
       <c r="I373" t="n">
         <v>4.35182512594076</v>
       </c>
-      <c r="J373" t="inlineStr"/>
+      <c r="J373" t="n">
+        <v>3.553767192184088</v>
+      </c>
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
@@ -9795,7 +10203,9 @@
       <c r="I374" t="n">
         <v>4.337160013333775</v>
       </c>
-      <c r="J374" t="inlineStr"/>
+      <c r="J374" t="n">
+        <v>3.34179366196171</v>
+      </c>
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
@@ -9824,7 +10234,9 @@
       <c r="I375" t="n">
         <v>4.33872761652873</v>
       </c>
-      <c r="J375" t="inlineStr"/>
+      <c r="J375" t="n">
+        <v>3.367620248522414</v>
+      </c>
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -9855,7 +10267,9 @@
       <c r="I376" t="n">
         <v>4.351051830374451</v>
       </c>
-      <c r="J376" t="inlineStr"/>
+      <c r="J376" t="n">
+        <v>3.538767276615476</v>
+      </c>
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
@@ -9884,7 +10298,9 @@
       <c r="I377" t="n">
         <v>4.353241283242128</v>
       </c>
-      <c r="J377" t="inlineStr"/>
+      <c r="J377" t="n">
+        <v>3.601939466251815</v>
+      </c>
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
@@ -9913,7 +10329,9 @@
       <c r="I378" t="n">
         <v>4.357349646961441</v>
       </c>
-      <c r="J378" t="inlineStr"/>
+      <c r="J378" t="n">
+        <v>3.721401681359362</v>
+      </c>
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
@@ -9944,7 +10362,9 @@
       <c r="I379" t="n">
         <v>4.359141762136423</v>
       </c>
-      <c r="J379" t="inlineStr"/>
+      <c r="J379" t="n">
+        <v>3.760489299141885</v>
+      </c>
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
@@ -9973,7 +10393,9 @@
       <c r="I380" t="n">
         <v>4.354269957628839</v>
       </c>
-      <c r="J380" t="inlineStr"/>
+      <c r="J380" t="n">
+        <v>3.704030466622941</v>
+      </c>
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
@@ -10002,7 +10424,9 @@
       <c r="I381" t="n">
         <v>4.35491234218231</v>
       </c>
-      <c r="J381" t="inlineStr"/>
+      <c r="J381" t="n">
+        <v>3.710780799365191</v>
+      </c>
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
@@ -10033,7 +10457,9 @@
       <c r="I382" t="n">
         <v>4.358630056867486</v>
       </c>
-      <c r="J382" t="inlineStr"/>
+      <c r="J382" t="n">
+        <v>3.726548908522889</v>
+      </c>
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
@@ -10062,7 +10488,9 @@
       <c r="I383" t="n">
         <v>4.360930671379148</v>
       </c>
-      <c r="J383" t="inlineStr"/>
+      <c r="J383" t="n">
+        <v>3.804701282415921</v>
+      </c>
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
@@ -10091,7 +10519,9 @@
       <c r="I384" t="n">
         <v>4.357477761752469</v>
       </c>
-      <c r="J384" t="inlineStr"/>
+      <c r="J384" t="n">
+        <v>3.72378018234094</v>
+      </c>
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
@@ -10122,7 +10552,9 @@
       <c r="I385" t="n">
         <v>4.362716386139382</v>
       </c>
-      <c r="J385" t="inlineStr"/>
+      <c r="J385" t="n">
+        <v>3.923255924575946</v>
+      </c>
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
@@ -10151,7 +10583,9 @@
       <c r="I386" t="n">
         <v>4.354141431184346</v>
       </c>
-      <c r="J386" t="inlineStr"/>
+      <c r="J386" t="n">
+        <v>3.94004018203459</v>
+      </c>
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
@@ -10180,7 +10614,9 @@
       <c r="I387" t="n">
         <v>4.358118089622206</v>
       </c>
-      <c r="J387" t="inlineStr"/>
+      <c r="J387" t="n">
+        <v>3.942682331011386</v>
+      </c>
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
@@ -10211,7 +10647,9 @@
       <c r="I388" t="n">
         <v>4.366278277705742</v>
       </c>
-      <c r="J388" t="inlineStr"/>
+      <c r="J388" t="n">
+        <v>3.87710054353757</v>
+      </c>
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
@@ -10240,7 +10678,9 @@
       <c r="I389" t="n">
         <v>4.371850028222321</v>
       </c>
-      <c r="J389" t="inlineStr"/>
+      <c r="J389" t="n">
+        <v>3.887412769449671</v>
+      </c>
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
@@ -10269,7 +10709,9 @@
       <c r="I390" t="n">
         <v>4.371092069621102</v>
       </c>
-      <c r="J390" t="inlineStr"/>
+      <c r="J390" t="n">
+        <v>3.81807748302197</v>
+      </c>
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
@@ -10300,7 +10742,9 @@
       <c r="I391" t="n">
         <v>4.37197629882038</v>
       </c>
-      <c r="J391" t="inlineStr"/>
+      <c r="J391" t="n">
+        <v>3.720697595023922</v>
+      </c>
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
@@ -10321,7 +10765,7 @@
         <v>4.613138355637268</v>
       </c>
       <c r="G392" t="n">
-        <v>4.528289141652134</v>
+        <v>4.52720864451838</v>
       </c>
       <c r="H392" t="n">
         <v>9.1</v>
@@ -10329,7 +10773,9 @@
       <c r="I392" t="n">
         <v>4.367547313409047</v>
       </c>
-      <c r="J392" t="inlineStr"/>
+      <c r="J392" t="n">
+        <v>3.740420924409831</v>
+      </c>
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
@@ -10358,7 +10804,9 @@
       <c r="I393" t="n">
         <v>4.37020705786854</v>
       </c>
-      <c r="J393" t="inlineStr"/>
+      <c r="J393" t="n">
+        <v>3.779372393310901</v>
+      </c>
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -10389,7 +10837,9 @@
       <c r="I394" t="n">
         <v>4.374120463102784</v>
       </c>
-      <c r="J394" t="inlineStr"/>
+      <c r="J394" t="n">
+        <v>3.852849633341334</v>
+      </c>
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
@@ -10418,7 +10868,9 @@
       <c r="I395" t="n">
         <v>4.37462430490712</v>
       </c>
-      <c r="J395" t="inlineStr"/>
+      <c r="J395" t="n">
+        <v>3.890191789722997</v>
+      </c>
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -10447,7 +10899,9 @@
       <c r="I396" t="n">
         <v>4.37260741275739</v>
       </c>
-      <c r="J396" t="inlineStr"/>
+      <c r="J396" t="n">
+        <v>3.978274575412832</v>
+      </c>
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
@@ -10478,7 +10932,9 @@
       <c r="I397" t="n">
         <v>4.376008562348319</v>
       </c>
-      <c r="J397" t="inlineStr"/>
+      <c r="J397" t="n">
+        <v>3.996069257730837</v>
+      </c>
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
@@ -10507,7 +10963,9 @@
       <c r="I398" t="n">
         <v>4.367039892365558</v>
       </c>
-      <c r="J398" t="inlineStr"/>
+      <c r="J398" t="n">
+        <v>4.036455378979721</v>
+      </c>
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -10536,7 +10994,9 @@
       <c r="I399" t="n">
         <v>4.369194655858504</v>
       </c>
-      <c r="J399" t="inlineStr"/>
+      <c r="J399" t="n">
+        <v>3.968405451542542</v>
+      </c>
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
@@ -10567,7 +11027,9 @@
       <c r="I400" t="n">
         <v>4.380149874661021</v>
       </c>
-      <c r="J400" t="inlineStr"/>
+      <c r="J400" t="n">
+        <v>3.980005562040444</v>
+      </c>
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
@@ -10596,7 +11058,9 @@
       <c r="I401" t="n">
         <v>4.38414938005486</v>
       </c>
-      <c r="J401" t="inlineStr"/>
+      <c r="J401" t="n">
+        <v>4.073107249536162</v>
+      </c>
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
@@ -10625,7 +11089,9 @@
       <c r="I402" t="n">
         <v>4.390366758948883</v>
       </c>
-      <c r="J402" t="inlineStr"/>
+      <c r="J402" t="n">
+        <v>4.176995536319429</v>
+      </c>
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
@@ -10656,7 +11122,9 @@
       <c r="I403" t="n">
         <v>4.391605609454205</v>
       </c>
-      <c r="J403" t="inlineStr"/>
+      <c r="J403" t="n">
+        <v>4.154444238812214</v>
+      </c>
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
@@ -10685,7 +11153,9 @@
       <c r="I404" t="n">
         <v>4.38937457233642</v>
       </c>
-      <c r="J404" t="inlineStr"/>
+      <c r="J404" t="n">
+        <v>4.151654664766028</v>
+      </c>
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
@@ -10714,7 +11184,9 @@
       <c r="I405" t="n">
         <v>4.390862483336281</v>
       </c>
-      <c r="J405" t="inlineStr"/>
+      <c r="J405" t="n">
+        <v>4.13999027392105</v>
+      </c>
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
@@ -10745,7 +11217,9 @@
       <c r="I406" t="n">
         <v>4.394819456472634</v>
       </c>
-      <c r="J406" t="inlineStr"/>
+      <c r="J406" t="n">
+        <v>4.214586887675727</v>
+      </c>
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
@@ -10774,7 +11248,9 @@
       <c r="I407" t="n">
         <v>4.397161522258152</v>
       </c>
-      <c r="J407" t="inlineStr"/>
+      <c r="J407" t="n">
+        <v>4.256446001229222</v>
+      </c>
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
@@ -10803,7 +11279,9 @@
       <c r="I408" t="n">
         <v>4.391729410135267</v>
       </c>
-      <c r="J408" t="inlineStr"/>
+      <c r="J408" t="n">
+        <v>4.042416369390097</v>
+      </c>
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
@@ -10834,7 +11312,9 @@
       <c r="I409" t="n">
         <v>4.391234115424795</v>
       </c>
-      <c r="J409" t="inlineStr"/>
+      <c r="J409" t="n">
+        <v>3.91970493549282</v>
+      </c>
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
@@ -10863,7 +11343,9 @@
       <c r="I410" t="n">
         <v>4.380901001386372</v>
       </c>
-      <c r="J410" t="inlineStr"/>
+      <c r="J410" t="n">
+        <v>3.951995940956316</v>
+      </c>
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
@@ -10892,7 +11374,9 @@
       <c r="I411" t="n">
         <v>4.384024637336554</v>
       </c>
-      <c r="J411" t="inlineStr"/>
+      <c r="J411" t="n">
+        <v>4.031523920579169</v>
+      </c>
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
@@ -10923,7 +11407,9 @@
       <c r="I412" t="n">
         <v>4.394078715698023</v>
       </c>
-      <c r="J412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>4.069336966934754</v>
+      </c>
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
@@ -10952,7 +11438,9 @@
       <c r="I413" t="n">
         <v>4.401216329067023</v>
       </c>
-      <c r="J413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>4.149176032590502</v>
+      </c>
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
@@ -10981,7 +11469,9 @@
       <c r="I414" t="n">
         <v>4.40256428589143</v>
       </c>
-      <c r="J414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>4.15522486667411</v>
+      </c>
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
@@ -11012,7 +11502,9 @@
       <c r="I415" t="n">
         <v>4.404154986746883</v>
       </c>
-      <c r="J415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>4.040681297369372</v>
+      </c>
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
@@ -11041,7 +11533,9 @@
       <c r="I416" t="n">
         <v>4.399620943074833</v>
       </c>
-      <c r="J416" t="inlineStr"/>
+      <c r="J416" t="n">
+        <v>4.042662882146143</v>
+      </c>
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
@@ -11070,7 +11564,9 @@
       <c r="I417" t="n">
         <v>4.400971050674819</v>
       </c>
-      <c r="J417" t="inlineStr"/>
+      <c r="J417" t="n">
+        <v>3.971495134668775</v>
+      </c>
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
@@ -11101,7 +11597,9 @@
       <c r="I418" t="n">
         <v>4.403054001865957</v>
       </c>
-      <c r="J418" t="inlineStr"/>
+      <c r="J418" t="n">
+        <v>4.044767571245441</v>
+      </c>
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
@@ -11130,7 +11628,9 @@
       <c r="I419" t="n">
         <v>4.404521712501253</v>
       </c>
-      <c r="J419" t="inlineStr"/>
+      <c r="J419" t="n">
+        <v>3.989422056160758</v>
+      </c>
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
@@ -11159,7 +11659,9 @@
       <c r="I420" t="n">
         <v>4.401338945706255</v>
       </c>
-      <c r="J420" t="inlineStr"/>
+      <c r="J420" t="n">
+        <v>4.046530996907043</v>
+      </c>
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
@@ -11190,7 +11692,9 @@
       <c r="I421" t="n">
         <v>4.404521712501253</v>
       </c>
-      <c r="J421" t="inlineStr"/>
+      <c r="J421" t="n">
+        <v>4.103737820516812</v>
+      </c>
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
@@ -11219,7 +11723,9 @@
       <c r="I422" t="n">
         <v>4.3945726038424</v>
       </c>
-      <c r="J422" t="inlineStr"/>
+      <c r="J422" t="n">
+        <v>4.049006550182978</v>
+      </c>
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
@@ -11248,7 +11754,9 @@
       <c r="I423" t="n">
         <v>4.396299293960601</v>
       </c>
-      <c r="J423" t="inlineStr"/>
+      <c r="J423" t="n">
+        <v>3.932625449438198</v>
+      </c>
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
@@ -11279,7 +11787,9 @@
       <c r="I424" t="n">
         <v>4.401584133889412</v>
       </c>
-      <c r="J424" t="inlineStr"/>
+      <c r="J424" t="n">
+        <v>3.364990262308884</v>
+      </c>
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
@@ -11308,7 +11818,9 @@
       <c r="I425" t="n">
         <v>4.404399485525607</v>
       </c>
-      <c r="J425" t="inlineStr"/>
+      <c r="J425" t="n">
+        <v>2.828586956758972</v>
+      </c>
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
@@ -11329,7 +11841,7 @@
         <v>4.505349850705881</v>
       </c>
       <c r="G426" t="n">
-        <v>4.526126978647638</v>
+        <v>4.525044141508807</v>
       </c>
       <c r="H426" t="n">
         <v>7.7</v>
@@ -11337,7 +11849,9 @@
       <c r="I426" t="n">
         <v>4.403421131528038</v>
       </c>
-      <c r="J426" t="inlineStr"/>
+      <c r="J426" t="n">
+        <v>3.293966764135656</v>
+      </c>
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
@@ -11368,7 +11882,9 @@
       <c r="I427" t="n">
         <v>4.40684119104832</v>
       </c>
-      <c r="J427" t="inlineStr"/>
+      <c r="J427" t="n">
+        <v>3.577415741641218</v>
+      </c>
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
@@ -11397,7 +11913,9 @@
       <c r="I428" t="n">
         <v>4.403421131528038</v>
       </c>
-      <c r="J428" t="inlineStr"/>
+      <c r="J428" t="n">
+        <v>3.630192492919949</v>
+      </c>
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
@@ -11426,7 +11944,9 @@
       <c r="I429" t="n">
         <v>4.399252415338951</v>
       </c>
-      <c r="J429" t="inlineStr"/>
+      <c r="J429" t="n">
+        <v>3.632975395179463</v>
+      </c>
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
@@ -11457,7 +11977,9 @@
       <c r="I430" t="n">
         <v>4.399989335048054</v>
       </c>
-      <c r="J430" t="inlineStr"/>
+      <c r="J430" t="n">
+        <v>3.546503597848869</v>
+      </c>
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
@@ -11486,7 +12008,9 @@
       <c r="I431" t="n">
         <v>4.401829261970061</v>
       </c>
-      <c r="J431" t="inlineStr"/>
+      <c r="J431" t="n">
+        <v>3.530209220637321</v>
+      </c>
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
@@ -11515,7 +12039,9 @@
       <c r="I432" t="n">
         <v>4.398514952178684</v>
       </c>
-      <c r="J432" t="inlineStr"/>
+      <c r="J432" t="n">
+        <v>3.585243142644741</v>
+      </c>
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
@@ -11546,7 +12072,9 @@
       <c r="I433" t="n">
         <v>4.401706705440709</v>
       </c>
-      <c r="J433" t="inlineStr"/>
+      <c r="J433" t="n">
+        <v>3.715456581471767</v>
+      </c>
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
@@ -11575,7 +12103,9 @@
       <c r="I434" t="n">
         <v>4.403421131528038</v>
       </c>
-      <c r="J434" t="inlineStr"/>
+      <c r="J434" t="n">
+        <v>3.806683943350821</v>
+      </c>
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
@@ -11604,7 +12134,9 @@
       <c r="I435" t="n">
         <v>4.405498990859024</v>
       </c>
-      <c r="J435" t="inlineStr"/>
+      <c r="J435" t="n">
+        <v>3.941193556138346</v>
+      </c>
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
@@ -11635,7 +12167,9 @@
       <c r="I436" t="n">
         <v>4.414856779264584</v>
       </c>
-      <c r="J436" t="inlineStr"/>
+      <c r="J436" t="n">
+        <v>4.006798574135988</v>
+      </c>
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -11664,7 +12198,9 @@
       <c r="I437" t="n">
         <v>4.420525933824491</v>
       </c>
-      <c r="J437" t="inlineStr"/>
+      <c r="J437" t="n">
+        <v>3.990881540777088</v>
+      </c>
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
@@ -11693,7 +12229,9 @@
       <c r="I438" t="n">
         <v>4.423168578005057</v>
       </c>
-      <c r="J438" t="inlineStr"/>
+      <c r="J438" t="n">
+        <v>4.032864642254908</v>
+      </c>
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -11724,7 +12262,9 @@
       <c r="I439" t="n">
         <v>4.425684604013345</v>
       </c>
-      <c r="J439" t="inlineStr"/>
+      <c r="J439" t="n">
+        <v>4.10641070405884</v>
+      </c>
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
@@ -11753,7 +12293,9 @@
       <c r="I440" t="n">
         <v>4.424966385165138</v>
       </c>
-      <c r="J440" t="inlineStr"/>
+      <c r="J440" t="n">
+        <v>4.152390485546104</v>
+      </c>
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -11782,7 +12324,9 @@
       <c r="I441" t="n">
         <v>4.428433007488037</v>
       </c>
-      <c r="J441" t="inlineStr"/>
+      <c r="J441" t="n">
+        <v>4.09602924423503</v>
+      </c>
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
@@ -11813,7 +12357,9 @@
       <c r="I442" t="n">
         <v>4.433076149349573</v>
       </c>
-      <c r="J442" t="inlineStr"/>
+      <c r="J442" t="n">
+        <v>4.147669026985889</v>
+      </c>
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
@@ -11842,7 +12388,9 @@
       <c r="I443" t="n">
         <v>4.441591872011272</v>
       </c>
-      <c r="J443" t="inlineStr"/>
+      <c r="J443" t="n">
+        <v>4.276778304247688</v>
+      </c>
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -11871,7 +12419,9 @@
       <c r="I444" t="n">
         <v>4.446057214331018</v>
       </c>
-      <c r="J444" t="inlineStr"/>
+      <c r="J444" t="n">
+        <v>4.26280668671896</v>
+      </c>
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
@@ -11902,7 +12452,9 @@
       <c r="I445" t="n">
         <v>4.450385972187225</v>
       </c>
-      <c r="J445" t="inlineStr"/>
+      <c r="J445" t="n">
+        <v>4.183807434906146</v>
+      </c>
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
@@ -11931,7 +12483,9 @@
       <c r="I446" t="n">
         <v>4.453416630760555</v>
       </c>
-      <c r="J446" t="inlineStr"/>
+      <c r="J446" t="n">
+        <v>4.336762122546151</v>
+      </c>
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
@@ -11960,7 +12514,9 @@
       <c r="I447" t="n">
         <v>4.462799844696365</v>
       </c>
-      <c r="J447" t="inlineStr"/>
+      <c r="J447" t="n">
+        <v>4.45013154764248</v>
+      </c>
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -11991,7 +12547,9 @@
       <c r="I448" t="n">
         <v>4.486836999026226</v>
       </c>
-      <c r="J448" t="inlineStr"/>
+      <c r="J448" t="n">
+        <v>4.667276390576368</v>
+      </c>
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
@@ -12020,7 +12578,9 @@
       <c r="I449" t="n">
         <v>4.492673154760945</v>
       </c>
-      <c r="J449" t="inlineStr"/>
+      <c r="J449" t="n">
+        <v>4.571257898024519</v>
+      </c>
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
@@ -12049,7 +12609,9 @@
       <c r="I450" t="n">
         <v>4.501031146246946</v>
       </c>
-      <c r="J450" t="inlineStr"/>
+      <c r="J450" t="n">
+        <v>4.674153604294284</v>
+      </c>
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
@@ -12080,7 +12642,9 @@
       <c r="I451" t="n">
         <v>4.50920979484218</v>
       </c>
-      <c r="J451" t="inlineStr"/>
+      <c r="J451" t="n">
+        <v>4.754784850242117</v>
+      </c>
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
@@ -12109,7 +12673,9 @@
       <c r="I452" t="n">
         <v>4.510419849442281</v>
       </c>
-      <c r="J452" t="inlineStr"/>
+      <c r="J452" t="n">
+        <v>4.700141350799962</v>
+      </c>
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
@@ -12138,7 +12704,9 @@
       <c r="I453" t="n">
         <v>4.516448255927287</v>
       </c>
-      <c r="J453" t="inlineStr"/>
+      <c r="J453" t="n">
+        <v>4.596898391001972</v>
+      </c>
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -12169,7 +12737,9 @@
       <c r="I454" t="n">
         <v>4.528289141652134</v>
       </c>
-      <c r="J454" t="inlineStr"/>
+      <c r="J454" t="n">
+        <v>4.506808766658857</v>
+      </c>
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
@@ -12198,7 +12768,9 @@
       <c r="I455" t="n">
         <v>4.542975582394973</v>
       </c>
-      <c r="J455" t="inlineStr"/>
+      <c r="J455" t="n">
+        <v>4.553728683004673</v>
+      </c>
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
@@ -12227,7 +12799,9 @@
       <c r="I456" t="n">
         <v>4.542336876816522</v>
       </c>
-      <c r="J456" t="inlineStr"/>
+      <c r="J456" t="n">
+        <v>4.495536876207816</v>
+      </c>
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
@@ -12258,7 +12832,9 @@
       <c r="I457" t="n">
         <v>4.538923540169165</v>
       </c>
-      <c r="J457" t="inlineStr"/>
+      <c r="J457" t="n">
+        <v>4.336248367125863</v>
+      </c>
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
@@ -12287,7 +12863,9 @@
       <c r="I458" t="n">
         <v>4.536891345234797</v>
       </c>
-      <c r="J458" t="inlineStr"/>
+      <c r="J458" t="n">
+        <v>4.338711749987938</v>
+      </c>
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
@@ -12316,7 +12894,9 @@
       <c r="I459" t="n">
         <v>4.544889255103161</v>
       </c>
-      <c r="J459" t="inlineStr"/>
+      <c r="J459" t="n">
+        <v>4.344819739223528</v>
+      </c>
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
@@ -12339,7 +12919,7 @@
         <v>4.642465970731788</v>
       </c>
       <c r="G460" t="n">
-        <v>4.59511985013459</v>
+        <v>4.594109238628667</v>
       </c>
       <c r="H460" t="n">
         <v>6.5</v>
@@ -12347,7 +12927,9 @@
       <c r="I460" t="n">
         <v>4.553876891600541</v>
       </c>
-      <c r="J460" t="inlineStr"/>
+      <c r="J460" t="n">
+        <v>4.294003512825759</v>
+      </c>
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
@@ -12376,7 +12958,9 @@
       <c r="I461" t="n">
         <v>4.560277417097355</v>
       </c>
-      <c r="J461" t="inlineStr"/>
+      <c r="J461" t="n">
+        <v>4.346035445366231</v>
+      </c>
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
@@ -12405,7 +12989,9 @@
       <c r="I462" t="n">
         <v>4.560591142590124</v>
       </c>
-      <c r="J462" t="inlineStr"/>
+      <c r="J462" t="n">
+        <v>4.240543635410012</v>
+      </c>
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
@@ -12436,7 +13022,9 @@
       <c r="I463" t="n">
         <v>4.563097409566184</v>
       </c>
-      <c r="J463" t="inlineStr"/>
+      <c r="J463" t="n">
+        <v>4.234707178138777</v>
+      </c>
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
@@ -12465,7 +13053,9 @@
       <c r="I464" t="n">
         <v>4.562262684976814</v>
       </c>
-      <c r="J464" t="inlineStr"/>
+      <c r="J464" t="n">
+        <v>4.282818716493589</v>
+      </c>
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
@@ -12494,7 +13084,9 @@
       <c r="I465" t="n">
         <v>4.567779796769532</v>
       </c>
-      <c r="J465" t="inlineStr"/>
+      <c r="J465" t="n">
+        <v>4.369098876045259</v>
+      </c>
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
@@ -12525,7 +13117,9 @@
       <c r="I466" t="n">
         <v>4.570889252011217</v>
       </c>
-      <c r="J466" t="inlineStr"/>
+      <c r="J466" t="n">
+        <v>4.474167239716883</v>
+      </c>
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
@@ -12554,7 +13148,9 @@
       <c r="I467" t="n">
         <v>4.571716809728872</v>
       </c>
-      <c r="J467" t="inlineStr"/>
+      <c r="J467" t="n">
+        <v>4.451725009980071</v>
+      </c>
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
@@ -12583,7 +13179,9 @@
       <c r="I468" t="n">
         <v>4.566221435849517</v>
       </c>
-      <c r="J468" t="inlineStr"/>
+      <c r="J468" t="n">
+        <v>4.340394919180895</v>
+      </c>
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
@@ -12614,7 +13212,9 @@
       <c r="I469" t="n">
         <v>4.567883601202075</v>
       </c>
-      <c r="J469" t="inlineStr"/>
+      <c r="J469" t="n">
+        <v>4.265496235442415</v>
+      </c>
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
@@ -12643,7 +13243,9 @@
       <c r="I470" t="n">
         <v>4.564348191467836</v>
       </c>
-      <c r="J470" t="inlineStr"/>
+      <c r="J470" t="n">
+        <v>4.296876699527028</v>
+      </c>
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
@@ -12672,7 +13274,9 @@
       <c r="I471" t="n">
         <v>4.570475216191205</v>
       </c>
-      <c r="J471" t="inlineStr"/>
+      <c r="J471" t="n">
+        <v>4.348135578866391</v>
+      </c>
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
@@ -12695,7 +13299,7 @@
         <v>4.634728988229636</v>
       </c>
       <c r="G472" t="n">
-        <v>4.607168188650764</v>
+        <v>4.606169686321175</v>
       </c>
       <c r="H472" t="n">
         <v>6.4</v>
@@ -12703,7 +13307,9 @@
       <c r="I472" t="n">
         <v>4.578004517915322</v>
       </c>
-      <c r="J472" t="inlineStr"/>
+      <c r="J472" t="n">
+        <v>4.363839210393138</v>
+      </c>
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
@@ -12732,7 +13338,9 @@
       <c r="I473" t="n">
         <v>4.583742238574471</v>
       </c>
-      <c r="J473" t="inlineStr"/>
+      <c r="J473" t="n">
+        <v>4.428892922417647</v>
+      </c>
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
@@ -12761,7 +13369,9 @@
       <c r="I474" t="n">
         <v>4.585885424576224</v>
       </c>
-      <c r="J474" t="inlineStr"/>
+      <c r="J474" t="n">
+        <v>4.325573254163131</v>
+      </c>
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
@@ -12792,7 +13402,9 @@
       <c r="I475" t="n">
         <v>4.588024027153121</v>
       </c>
-      <c r="J475" t="inlineStr"/>
+      <c r="J475" t="n">
+        <v>4.336605869027755</v>
+      </c>
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
@@ -12821,7 +13433,9 @@
       <c r="I476" t="n">
         <v>4.587820547652979</v>
       </c>
-      <c r="J476" t="inlineStr"/>
+      <c r="J476" t="n">
+        <v>4.363379549638092</v>
+      </c>
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
@@ -12850,7 +13464,9 @@
       <c r="I477" t="n">
         <v>4.589142424910894</v>
       </c>
-      <c r="J477" t="inlineStr"/>
+      <c r="J477" t="n">
+        <v>4.290099534882992</v>
+      </c>
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
@@ -12881,7 +13497,9 @@
       <c r="I478" t="n">
         <v>4.588125751378833</v>
       </c>
-      <c r="J478" t="inlineStr"/>
+      <c r="J478" t="n">
+        <v>4.19943491713264</v>
+      </c>
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
@@ -12910,7 +13528,9 @@
       <c r="I479" t="n">
         <v>4.591578232468624</v>
       </c>
-      <c r="J479" t="inlineStr"/>
+      <c r="J479" t="n">
+        <v>4.239276530032364</v>
+      </c>
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
@@ -12939,7 +13559,9 @@
       <c r="I480" t="n">
         <v>4.588430861983793</v>
       </c>
-      <c r="J480" t="inlineStr"/>
+      <c r="J480" t="n">
+        <v>4.247675134582752</v>
+      </c>
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
@@ -12970,7 +13592,9 @@
       <c r="I481" t="n">
         <v>4.591882291661156</v>
       </c>
-      <c r="J481" t="inlineStr"/>
+      <c r="J481" t="n">
+        <v>4.255407105448533</v>
+      </c>
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
@@ -12999,7 +13623,9 @@
       <c r="I482" t="n">
         <v>4.58934563564112</v>
       </c>
-      <c r="J482" t="inlineStr"/>
+      <c r="J482" t="n">
+        <v>4.338098261991652</v>
+      </c>
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
@@ -13028,7 +13654,9 @@
       <c r="I483" t="n">
         <v>4.593603549616626</v>
       </c>
-      <c r="J483" t="inlineStr"/>
+      <c r="J483" t="n">
+        <v>4.282915723826287</v>
+      </c>
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
@@ -13059,7 +13687,9 @@
       <c r="I484" t="n">
         <v>4.599655005299981</v>
       </c>
-      <c r="J484" t="inlineStr"/>
+      <c r="J484" t="n">
+        <v>4.209162600255272</v>
+      </c>
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
@@ -13088,7 +13718,9 @@
       <c r="I485" t="n">
         <v>4.605170185988092</v>
       </c>
-      <c r="J485" t="inlineStr"/>
+      <c r="J485" t="n">
+        <v>4.106844198800405</v>
+      </c>
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
@@ -13117,7 +13749,9 @@
       <c r="I486" t="n">
         <v>4.604670060946409</v>
       </c>
-      <c r="J486" t="inlineStr"/>
+      <c r="J486" t="n">
+        <v>4.045616674707757</v>
+      </c>
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
@@ -13148,7 +13782,9 @@
       <c r="I487" t="n">
         <v>4.607667066186679</v>
       </c>
-      <c r="J487" t="inlineStr"/>
+      <c r="J487" t="n">
+        <v>4.127689116814509</v>
+      </c>
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
@@ -13177,7 +13813,9 @@
       <c r="I488" t="n">
         <v>4.608065989100117</v>
       </c>
-      <c r="J488" t="inlineStr"/>
+      <c r="J488" t="n">
+        <v>4.108218266877361</v>
+      </c>
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
@@ -13206,7 +13844,9 @@
       <c r="I489" t="n">
         <v>4.609560534289384</v>
       </c>
-      <c r="J489" t="inlineStr"/>
+      <c r="J489" t="n">
+        <v>4.066468409690192</v>
+      </c>
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
@@ -13237,7 +13877,9 @@
       <c r="I490" t="n">
         <v>4.610356712675391</v>
       </c>
-      <c r="J490" t="inlineStr"/>
+      <c r="J490" t="n">
+        <v>4.059606205568766</v>
+      </c>
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
@@ -13266,7 +13908,9 @@
       <c r="I491" t="n">
         <v>4.612542940317504</v>
       </c>
-      <c r="J491" t="inlineStr"/>
+      <c r="J491" t="n">
+        <v>4.01624492921095</v>
+      </c>
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
@@ -13295,7 +13939,9 @@
       <c r="I492" t="n">
         <v>4.609660091260944</v>
       </c>
-      <c r="J492" t="inlineStr"/>
+      <c r="J492" t="n">
+        <v>4.010770119212157</v>
+      </c>
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
@@ -13318,7 +13964,7 @@
         <v>4.645351975620923</v>
       </c>
       <c r="G493" t="n">
-        <v>4.644390899141372</v>
+        <v>4.645351975620923</v>
       </c>
       <c r="H493" t="n">
         <v>6.3</v>
@@ -13326,7 +13972,9 @@
       <c r="I493" t="n">
         <v>4.611450423945242</v>
       </c>
-      <c r="J493" t="inlineStr"/>
+      <c r="J493" t="n">
+        <v>3.978058069709093</v>
+      </c>
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
@@ -13347,7 +13995,7 @@
         <v>4.633757642840004</v>
       </c>
       <c r="G494" t="n">
-        <v>4.646312129319266</v>
+        <v>4.647271362006727</v>
       </c>
       <c r="H494" t="n">
         <v>6.3</v>
@@ -13355,7 +14003,9 @@
       <c r="I494" t="n">
         <v>4.605869941102364</v>
       </c>
-      <c r="J494" t="inlineStr"/>
+      <c r="J494" t="n">
+        <v>4.03843794446973</v>
+      </c>
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
@@ -13376,7 +14026,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="G495" t="n">
-        <v>4.642465970731788</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="H495" t="n">
         <v>6.4</v>
@@ -13384,7 +14034,9 @@
       <c r="I495" t="n">
         <v>4.612344389736092</v>
       </c>
-      <c r="J495" t="inlineStr"/>
+      <c r="J495" t="n">
+        <v>4.093587337351482</v>
+      </c>
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
@@ -13415,7 +14067,9 @@
       <c r="I496" t="n">
         <v>4.624874769262426</v>
       </c>
-      <c r="J496" t="inlineStr"/>
+      <c r="J496" t="n">
+        <v>4.491170054663795</v>
+      </c>
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
@@ -13444,7 +14098,9 @@
       <c r="I497" t="n">
         <v>4.635117262356044</v>
       </c>
-      <c r="J497" t="inlineStr"/>
+      <c r="J497" t="n">
+        <v>4.60709889273138</v>
+      </c>
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
@@ -13465,7 +14121,7 @@
         <v>4.647271362006727</v>
       </c>
       <c r="G498" t="n">
-        <v>4.650143551630823</v>
+        <v>4.649187071404866</v>
       </c>
       <c r="H498" t="n">
         <v>6.4</v>
@@ -13473,7 +14129,9 @@
       <c r="I498" t="n">
         <v>4.635990328327978</v>
       </c>
-      <c r="J498" t="inlineStr"/>
+      <c r="J498" t="n">
+        <v>4.519425867367042</v>
+      </c>
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
@@ -13504,7 +14162,9 @@
       <c r="I499" t="n">
         <v>4.635020207956977</v>
       </c>
-      <c r="J499" t="inlineStr"/>
+      <c r="J499" t="n">
+        <v>4.30602016470409</v>
+      </c>
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
@@ -13533,7 +14193,9 @@
       <c r="I500" t="n">
         <v>4.637153231841142</v>
       </c>
-      <c r="J500" t="inlineStr"/>
+      <c r="J500" t="n">
+        <v>4.295395297499554</v>
+      </c>
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
@@ -13549,14 +14211,18 @@
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>4.647271362006727</v>
+      </c>
       <c r="H501" t="n">
         <v>6.4</v>
       </c>
       <c r="I501" t="n">
         <v>4.641405678570186</v>
       </c>
-      <c r="J501" t="inlineStr"/>
+      <c r="J501" t="n">
+        <v>4.363913651397029</v>
+      </c>
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14243,7 +14243,9 @@
       <c r="I502" t="n">
         <v>4.64736723468788</v>
       </c>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>4.596689494135473</v>
+      </c>
       <c r="K502" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,64 +421,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -509,7 +495,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -526,7 +512,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -543,7 +529,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -560,7 +546,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -577,7 +563,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -594,7 +580,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -611,7 +597,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -628,7 +614,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -645,7 +631,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -662,7 +648,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -679,7 +665,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -696,7 +682,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -713,7 +699,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -730,7 +716,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -747,7 +733,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -764,7 +750,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -781,7 +767,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -798,7 +784,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -815,7 +801,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -832,7 +818,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -849,7 +835,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -866,7 +852,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -883,7 +869,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -900,7 +886,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -917,7 +903,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -934,7 +920,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -951,7 +937,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -968,7 +954,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -985,7 +971,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1002,7 +988,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1019,7 +1005,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1036,7 +1022,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1053,7 +1039,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1070,7 +1056,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1087,7 +1073,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1104,7 +1090,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1121,7 +1107,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1138,7 +1124,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1155,7 +1141,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1172,7 +1158,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1189,7 +1175,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1206,7 +1192,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1223,7 +1209,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1240,7 +1226,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1257,7 +1243,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1274,7 +1260,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1291,7 +1277,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1308,7 +1294,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1325,7 +1311,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1342,7 +1328,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1359,7 +1345,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1376,7 +1362,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1393,7 +1379,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1410,7 +1396,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1427,7 +1413,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1444,7 +1430,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1461,7 +1447,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1478,7 +1464,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1495,7 +1481,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1512,7 +1498,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1529,7 +1515,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1546,7 +1532,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1563,7 +1549,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1580,7 +1566,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1597,7 +1583,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1614,7 +1600,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1631,7 +1617,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1648,7 +1634,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1665,7 +1651,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1682,7 +1668,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1699,7 +1685,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1716,7 +1702,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1735,7 +1721,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1754,7 +1740,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1773,7 +1759,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1792,7 +1778,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1811,7 +1797,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1830,7 +1816,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -1849,7 +1835,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -1868,7 +1854,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1887,7 +1873,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1906,7 +1892,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1925,7 +1911,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -1944,7 +1930,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -1963,7 +1949,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -1982,7 +1968,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2001,7 +1987,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2020,7 +2006,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2039,7 +2025,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2058,7 +2044,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2077,7 +2063,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2096,7 +2082,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2115,7 +2101,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2134,7 +2120,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2153,7 +2139,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2172,7 +2158,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2191,7 +2177,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2210,7 +2196,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2229,7 +2215,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2248,7 +2234,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2267,7 +2253,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2286,7 +2272,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2305,7 +2291,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2324,7 +2310,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2343,7 +2329,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2362,7 +2348,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2381,7 +2367,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2400,7 +2386,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2421,7 +2407,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2442,7 +2428,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2463,7 +2449,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2484,7 +2470,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2505,7 +2491,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2526,7 +2512,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2547,7 +2533,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2568,7 +2554,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2589,7 +2575,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2610,7 +2596,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2631,7 +2617,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2652,7 +2638,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2675,7 +2661,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2698,7 +2684,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -2723,7 +2709,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -2746,7 +2732,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -2769,7 +2755,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -2794,7 +2780,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -2817,7 +2803,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -2840,7 +2826,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -2865,7 +2851,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -2888,7 +2874,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -2911,7 +2897,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -2936,7 +2922,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -2959,7 +2945,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -2982,7 +2968,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3007,7 +2993,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3030,7 +3016,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3053,7 +3039,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3078,7 +3064,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3101,7 +3087,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3124,7 +3110,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3149,7 +3135,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3172,7 +3158,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3195,7 +3181,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3220,7 +3206,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3243,7 +3229,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3266,7 +3252,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3291,7 +3277,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3314,7 +3300,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3337,7 +3323,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3362,7 +3348,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3385,7 +3371,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3408,7 +3394,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3433,7 +3419,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3456,7 +3442,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3479,7 +3465,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -3504,7 +3490,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3527,7 +3513,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3550,7 +3536,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -3575,7 +3561,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3598,7 +3584,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -3621,7 +3607,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -3646,7 +3632,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -3669,7 +3655,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -3692,7 +3678,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -3717,7 +3703,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -3740,7 +3726,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -3763,7 +3749,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -3788,7 +3774,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -3813,7 +3799,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -3838,7 +3824,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -3865,7 +3851,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -3890,7 +3876,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -3915,7 +3901,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -3942,7 +3928,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -3967,7 +3953,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -3992,7 +3978,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4019,7 +4005,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4044,7 +4030,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4069,7 +4055,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4098,7 +4084,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4129,7 +4115,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4160,7 +4146,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4193,7 +4179,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4224,7 +4210,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4255,7 +4241,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4288,7 +4274,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4319,7 +4305,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4350,7 +4336,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -4383,7 +4369,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4414,7 +4400,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4445,7 +4431,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -4478,7 +4464,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4509,7 +4495,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -4540,7 +4526,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -4573,7 +4559,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -4604,7 +4590,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -4615,7 +4601,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E198" t="n">
-        <v>4.515245478460105</v>
+        <v>4.514150787600923</v>
       </c>
       <c r="F198" t="n">
         <v>4.719391330078114</v>
@@ -4635,7 +4621,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -4648,7 +4634,7 @@
         <v>4.629862798578463</v>
       </c>
       <c r="E199" t="n">
-        <v>4.515245478460105</v>
+        <v>4.514150787600923</v>
       </c>
       <c r="F199" t="n">
         <v>4.71760561531788</v>
@@ -4668,7 +4654,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -4699,7 +4685,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -4730,7 +4716,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -4763,7 +4749,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -4794,7 +4780,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -4825,7 +4811,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -4858,7 +4844,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -4889,7 +4875,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -4920,7 +4906,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -4953,7 +4939,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -4984,7 +4970,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5015,7 +5001,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5048,7 +5034,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5079,7 +5065,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5110,7 +5096,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5143,7 +5129,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5174,7 +5160,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5205,7 +5191,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5238,7 +5224,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5269,7 +5255,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5300,7 +5286,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -5333,7 +5319,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5364,7 +5350,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5395,7 +5381,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -5428,7 +5414,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5459,7 +5445,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5490,7 +5476,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -5523,7 +5509,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -5554,7 +5540,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -5585,7 +5571,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -5618,7 +5604,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -5649,7 +5635,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -5680,7 +5666,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -5713,7 +5699,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -5744,7 +5730,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -5775,7 +5761,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -5808,7 +5794,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -5839,7 +5825,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -5870,7 +5856,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -5903,7 +5889,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -5934,7 +5920,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -5965,7 +5951,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -5998,7 +5984,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6029,7 +6015,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6060,7 +6046,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6093,7 +6079,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6124,7 +6110,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6155,7 +6141,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6188,7 +6174,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6219,7 +6205,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6250,7 +6236,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6283,7 +6269,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -6314,7 +6300,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -6345,7 +6331,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -6378,7 +6364,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -6409,7 +6395,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -6440,7 +6426,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -6473,7 +6459,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -6504,7 +6490,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -6535,7 +6521,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -6568,7 +6554,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -6599,7 +6585,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -6630,7 +6616,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -6663,7 +6649,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -6694,7 +6680,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -6725,7 +6711,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -6758,7 +6744,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -6789,7 +6775,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -6820,7 +6806,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -6853,7 +6839,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -6884,7 +6870,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -6915,7 +6901,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -6948,7 +6934,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -6979,7 +6965,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7010,7 +6996,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7043,7 +7029,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7074,7 +7060,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7105,7 +7091,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7138,7 +7124,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7169,7 +7155,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7200,7 +7186,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7233,7 +7219,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7264,7 +7250,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7295,7 +7281,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -7328,7 +7314,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -7359,7 +7345,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -7390,7 +7376,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -7423,7 +7409,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -7454,7 +7440,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -7485,7 +7471,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -7518,7 +7504,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -7549,7 +7535,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -7580,7 +7566,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -7613,7 +7599,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -7644,7 +7630,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -7675,7 +7661,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -7708,7 +7694,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -7739,7 +7725,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -7770,7 +7756,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -7803,7 +7789,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -7834,7 +7820,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -7865,7 +7851,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -7898,7 +7884,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -7929,7 +7915,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -7960,7 +7946,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -7993,7 +7979,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8024,7 +8010,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8055,7 +8041,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8088,7 +8074,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8119,7 +8105,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8150,7 +8136,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8183,7 +8169,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8214,7 +8200,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8245,7 +8231,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8278,7 +8264,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8309,7 +8295,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -8340,7 +8326,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -8373,7 +8359,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -8404,7 +8390,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -8435,7 +8421,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -8468,7 +8454,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -8499,7 +8485,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -8530,7 +8516,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -8563,7 +8549,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -8594,7 +8580,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -8625,7 +8611,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -8658,7 +8644,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -8689,7 +8675,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -8720,7 +8706,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -8753,7 +8739,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -8784,7 +8770,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -8815,7 +8801,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -8848,7 +8834,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -8879,7 +8865,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -8910,7 +8896,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -8943,7 +8929,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -8974,7 +8960,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9005,7 +8991,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9038,7 +9024,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9069,7 +9055,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9100,7 +9086,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9133,7 +9119,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9164,7 +9150,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9175,7 +9161,7 @@
         <v>4.481871969643598</v>
       </c>
       <c r="E342" t="n">
-        <v>4.52720864451838</v>
+        <v>4.526126978647638</v>
       </c>
       <c r="F342" t="n">
         <v>4.543294782270004</v>
@@ -9195,7 +9181,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9228,7 +9214,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9259,7 +9245,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9290,7 +9276,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -9323,7 +9309,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -9354,7 +9340,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -9385,7 +9371,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -9418,7 +9404,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -9449,7 +9435,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -9480,7 +9466,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -9513,7 +9499,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -9544,7 +9530,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -9575,7 +9561,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -9608,7 +9594,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -9639,7 +9625,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -9670,7 +9656,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -9703,7 +9689,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -9734,7 +9720,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -9765,7 +9751,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -9798,7 +9784,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -9829,7 +9815,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -9860,7 +9846,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -9893,7 +9879,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -9924,7 +9910,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -9955,7 +9941,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -9988,7 +9974,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10019,7 +10005,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10050,7 +10036,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10083,7 +10069,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10114,7 +10100,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10145,7 +10131,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10178,7 +10164,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10209,7 +10195,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10240,7 +10226,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10273,7 +10259,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10304,7 +10290,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -10335,7 +10321,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -10368,7 +10354,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -10399,7 +10385,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -10430,7 +10416,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -10463,7 +10449,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -10494,7 +10480,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -10525,7 +10511,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -10558,7 +10544,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -10589,7 +10575,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -10620,7 +10606,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -10653,7 +10639,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -10684,7 +10670,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -10715,7 +10701,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -10748,7 +10734,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -10779,7 +10765,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -10810,7 +10796,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -10843,7 +10829,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -10874,7 +10860,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -10905,7 +10891,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -10938,7 +10924,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -10969,7 +10955,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11000,7 +10986,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11033,7 +11019,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11064,7 +11050,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11095,7 +11081,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11128,7 +11114,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11159,7 +11145,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11190,7 +11176,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11223,7 +11209,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11254,7 +11240,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11285,7 +11271,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -11318,7 +11304,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -11349,7 +11335,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -11380,7 +11366,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -11413,7 +11399,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -11444,7 +11430,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -11475,7 +11461,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -11508,7 +11494,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -11539,7 +11525,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -11570,7 +11556,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -11603,7 +11589,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -11634,7 +11620,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -11665,7 +11651,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -11698,7 +11684,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -11729,7 +11715,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -11760,7 +11746,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -11793,7 +11779,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -11824,7 +11810,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -11855,7 +11841,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -11888,7 +11874,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -11919,7 +11905,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -11950,7 +11936,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -11983,7 +11969,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12014,7 +12000,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12045,7 +12031,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12078,7 +12064,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12109,7 +12095,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12140,7 +12126,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12173,7 +12159,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12204,7 +12190,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12235,7 +12221,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12268,7 +12254,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12299,7 +12285,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -12310,7 +12296,7 @@
         <v>4.774068722449905</v>
       </c>
       <c r="E441" t="n">
-        <v>4.59511985013459</v>
+        <v>4.596129441335942</v>
       </c>
       <c r="F441" t="n">
         <v>4.599152113662528</v>
@@ -12330,7 +12316,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -12363,7 +12349,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -12394,7 +12380,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -12425,7 +12411,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -12458,7 +12444,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -12489,7 +12475,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -12520,7 +12506,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -12553,7 +12539,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -12584,7 +12570,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -12615,7 +12601,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -12648,7 +12634,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -12679,7 +12665,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -12710,7 +12696,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -12743,7 +12729,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -12774,7 +12760,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -12805,7 +12791,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -12838,7 +12824,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -12869,7 +12855,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -12900,7 +12886,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -12933,7 +12919,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -12944,7 +12930,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E461" t="n">
-        <v>4.612145799724517</v>
+        <v>4.611152257665639</v>
       </c>
       <c r="F461" t="n">
         <v>4.640537329825382</v>
@@ -12964,7 +12950,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -12995,7 +12981,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13028,7 +13014,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13059,7 +13045,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13070,7 +13056,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="E465" t="n">
-        <v>4.591071261608589</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="F465" t="n">
         <v>4.645351975620923</v>
@@ -13090,7 +13076,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13123,7 +13109,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13154,7 +13140,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13185,7 +13171,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13218,7 +13204,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13249,7 +13235,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13280,7 +13266,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -13313,7 +13299,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -13344,7 +13330,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -13375,7 +13361,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -13388,7 +13374,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="E475" t="n">
-        <v>4.581901559048737</v>
+        <v>4.580877493419047</v>
       </c>
       <c r="F475" t="n">
         <v>4.630837932736669</v>
@@ -13408,7 +13394,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -13419,7 +13405,7 @@
         <v>4.566429357671661</v>
       </c>
       <c r="E476" t="n">
-        <v>4.574710978503383</v>
+        <v>4.573679518896721</v>
       </c>
       <c r="F476" t="n">
         <v>4.623991940228679</v>
@@ -13439,7 +13425,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -13450,7 +13436,7 @@
         <v>4.570578741218473</v>
       </c>
       <c r="E477" t="n">
-        <v>4.579852378003801</v>
+        <v>4.581901559048737</v>
       </c>
       <c r="F477" t="n">
         <v>4.626931677769604</v>
@@ -13470,7 +13456,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -13503,7 +13489,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -13534,7 +13520,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -13565,7 +13551,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -13598,7 +13584,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -13629,7 +13615,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -13660,7 +13646,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -13693,7 +13679,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -13704,7 +13690,7 @@
         <v>4.552823705615882</v>
       </c>
       <c r="E485" t="n">
-        <v>4.584967478670572</v>
+        <v>4.583946549536464</v>
       </c>
       <c r="F485" t="n">
         <v>4.653007515402251</v>
@@ -13724,7 +13710,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -13735,7 +13721,7 @@
         <v>4.563305981889393</v>
       </c>
       <c r="E486" t="n">
-        <v>4.594109238628667</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="F486" t="n">
         <v>4.645351975620923</v>
@@ -13755,7 +13741,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -13768,7 +13754,7 @@
         <v>4.550714000192032</v>
       </c>
       <c r="E487" t="n">
-        <v>4.591071261608589</v>
+        <v>4.590056548178043</v>
       </c>
       <c r="F487" t="n">
         <v>4.649187071404866</v>
@@ -13788,7 +13774,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -13819,7 +13805,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -13830,7 +13816,7 @@
         <v>4.559126247486684</v>
       </c>
       <c r="E489" t="n">
-        <v>4.588024027153121</v>
+        <v>4.592084946439436</v>
       </c>
       <c r="F489" t="n">
         <v>4.647271362006727</v>
@@ -13850,7 +13836,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -13883,7 +13869,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -13914,7 +13900,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -13925,7 +13911,7 @@
         <v>4.575741375297279</v>
       </c>
       <c r="E492" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="F492" t="n">
         <v>4.642465970731788</v>
@@ -13945,7 +13931,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -13978,7 +13964,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14009,7 +13995,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14020,7 +14006,7 @@
         <v>4.588024027153121</v>
       </c>
       <c r="E495" t="n">
-        <v>4.580877493419047</v>
+        <v>4.579852378003801</v>
       </c>
       <c r="F495" t="n">
         <v>4.627909672957581</v>
@@ -14040,7 +14026,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14073,7 +14059,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14084,7 +14070,7 @@
         <v>4.540098189244376</v>
       </c>
       <c r="E497" t="n">
-        <v>4.588024027153121</v>
+        <v>4.58700621536042</v>
       </c>
       <c r="F497" t="n">
         <v>4.646312129319266</v>
@@ -14104,7 +14090,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14115,7 +14101,7 @@
         <v>4.546481189639412</v>
       </c>
       <c r="E498" t="n">
-        <v>4.590056548178043</v>
+        <v>4.589040804058207</v>
       </c>
       <c r="F498" t="n">
         <v>4.647271362006727</v>
@@ -14135,7 +14121,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14148,7 +14134,7 @@
         <v>4.560172820057356</v>
       </c>
       <c r="E499" t="n">
-        <v>4.589040804058207</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="F499" t="n">
         <v>4.631812116934513</v>
@@ -14168,7 +14154,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14179,7 +14165,7 @@
         <v>4.575741375297279</v>
       </c>
       <c r="E500" t="n">
-        <v>4.588024027153121</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="F500" t="n">
         <v>4.631812116934513</v>
@@ -14199,7 +14185,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14209,7 +14195,9 @@
       <c r="D501" t="n">
         <v>4.589040804058207</v>
       </c>
-      <c r="E501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>4.579852378003801</v>
+      </c>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="n">
         <v>4.647271362006727</v>
@@ -14226,7 +14214,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -14241,7 +14229,7 @@
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
-        <v>4.64736723468788</v>
+        <v>4.647463098178343</v>
       </c>
       <c r="J502" t="n">
         <v>4.596689494135473</v>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -2688,7 +2688,7 @@
         <v>34789</v>
       </c>
       <c r="B124" t="n">
-        <v>14.56397266529668</v>
+        <v>14.56174034364012</v>
       </c>
       <c r="C124" t="n">
         <v>7.58</v>
@@ -2759,7 +2759,7 @@
         <v>34880</v>
       </c>
       <c r="B127" t="n">
-        <v>14.57217778807063</v>
+        <v>14.56989233897174</v>
       </c>
       <c r="C127" t="n">
         <v>7.08</v>
@@ -2830,7 +2830,7 @@
         <v>34972</v>
       </c>
       <c r="B130" t="n">
-        <v>14.57441673333072</v>
+        <v>14.57214292384835</v>
       </c>
       <c r="C130" t="n">
         <v>6.5</v>
@@ -2901,7 +2901,7 @@
         <v>35064</v>
       </c>
       <c r="B133" t="n">
-        <v>14.57679491734394</v>
+        <v>14.57446387776937</v>
       </c>
       <c r="C133" t="n">
         <v>6.32</v>
@@ -2972,7 +2972,7 @@
         <v>35155</v>
       </c>
       <c r="B136" t="n">
-        <v>14.5785584045077</v>
+        <v>14.5763900291462</v>
       </c>
       <c r="C136" t="n">
         <v>5.5</v>
@@ -3043,7 +3043,7 @@
         <v>35246</v>
       </c>
       <c r="B139" t="n">
-        <v>14.58651435073905</v>
+        <v>14.58422206396621</v>
       </c>
       <c r="C139" t="n">
         <v>5.08</v>
@@ -3114,7 +3114,7 @@
         <v>35338</v>
       </c>
       <c r="B142" t="n">
-        <v>14.59083842063923</v>
+        <v>14.58858133141156</v>
       </c>
       <c r="C142" t="n">
         <v>4.86</v>
@@ -3185,7 +3185,7 @@
         <v>35430</v>
       </c>
       <c r="B145" t="n">
-        <v>14.59651718496794</v>
+        <v>14.59418081688001</v>
       </c>
       <c r="C145" t="n">
         <v>4.5</v>
@@ -3256,7 +3256,7 @@
         <v>35520</v>
       </c>
       <c r="B148" t="n">
-        <v>14.59935726010626</v>
+        <v>14.59699804875744</v>
       </c>
       <c r="C148" t="n">
         <v>4.5</v>
@@ -3327,7 +3327,7 @@
         <v>35611</v>
       </c>
       <c r="B151" t="n">
-        <v>14.61143145129054</v>
+        <v>14.60920337121466</v>
       </c>
       <c r="C151" t="n">
         <v>4.29</v>
@@ -3362,7 +3362,7 @@
         <v>4.407938016458383</v>
       </c>
       <c r="F152" t="n">
-        <v>4.683981366412381</v>
+        <v>4.683056724645162</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
         <v>35703</v>
       </c>
       <c r="B154" t="n">
-        <v>14.6188841166487</v>
+        <v>14.61666528270881</v>
       </c>
       <c r="C154" t="n">
         <v>4.31</v>
@@ -3469,7 +3469,7 @@
         <v>35795</v>
       </c>
       <c r="B157" t="n">
-        <v>14.62936795247762</v>
+        <v>14.62707537278031</v>
       </c>
       <c r="C157" t="n">
         <v>4.37</v>
@@ -3540,7 +3540,7 @@
         <v>35885</v>
       </c>
       <c r="B160" t="n">
-        <v>14.63668536316574</v>
+        <v>14.63439536349065</v>
       </c>
       <c r="C160" t="n">
         <v>4.11</v>
@@ -3611,7 +3611,7 @@
         <v>35976</v>
       </c>
       <c r="B163" t="n">
-        <v>14.64074447563629</v>
+        <v>14.63844637326051</v>
       </c>
       <c r="C163" t="n">
         <v>4.02</v>
@@ -3682,7 +3682,7 @@
         <v>36068</v>
       </c>
       <c r="B166" t="n">
-        <v>14.64562246799674</v>
+        <v>14.64343353156128</v>
       </c>
       <c r="C166" t="n">
         <v>3.93</v>
@@ -3753,7 +3753,7 @@
         <v>36160</v>
       </c>
       <c r="B169" t="n">
-        <v>14.64861344473465</v>
+        <v>14.6463506724115</v>
       </c>
       <c r="C169" t="n">
         <v>3.37</v>
@@ -3828,7 +3828,7 @@
         <v>36250</v>
       </c>
       <c r="B172" t="n">
-        <v>14.65856564478907</v>
+        <v>14.65627000371531</v>
       </c>
       <c r="C172" t="n">
         <v>3.0466957</v>
@@ -3865,7 +3865,7 @@
         <v>4.436751534363128</v>
       </c>
       <c r="F173" t="n">
-        <v>4.692264892839025</v>
+        <v>4.691347882229143</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
         <v>36341</v>
       </c>
       <c r="B175" t="n">
-        <v>14.66358938474639</v>
+        <v>14.66127444241175</v>
       </c>
       <c r="C175" t="n">
         <v>2.6266818</v>
@@ -3982,7 +3982,7 @@
         <v>36433</v>
       </c>
       <c r="B178" t="n">
-        <v>14.67621174820405</v>
+        <v>14.67396105302178</v>
       </c>
       <c r="C178" t="n">
         <v>2.7266818</v>
@@ -4059,7 +4059,7 @@
         <v>36525</v>
       </c>
       <c r="B181" t="n">
-        <v>14.6867800324089</v>
+        <v>14.68459344913467</v>
       </c>
       <c r="C181" t="n">
         <v>3.4460455</v>
@@ -4150,7 +4150,7 @@
         <v>36616</v>
       </c>
       <c r="B184" t="n">
-        <v>14.6995038990842</v>
+        <v>14.69715750415454</v>
       </c>
       <c r="C184" t="n">
         <v>3.7470435</v>
@@ -4245,7 +4245,7 @@
         <v>36707</v>
       </c>
       <c r="B187" t="n">
-        <v>14.70885490370678</v>
+        <v>14.7066067973274</v>
       </c>
       <c r="C187" t="n">
         <v>4.5017273</v>
@@ -4340,7 +4340,7 @@
         <v>36799</v>
       </c>
       <c r="B190" t="n">
-        <v>14.71525629309739</v>
+        <v>14.71298146263598</v>
       </c>
       <c r="C190" t="n">
         <v>4.8528095</v>
@@ -4435,7 +4435,7 @@
         <v>36891</v>
       </c>
       <c r="B193" t="n">
-        <v>14.72021875045736</v>
+        <v>14.71796594126744</v>
       </c>
       <c r="C193" t="n">
         <v>4.9391579</v>
@@ -4530,7 +4530,7 @@
         <v>36981</v>
       </c>
       <c r="B196" t="n">
-        <v>14.73097450814862</v>
+        <v>14.72868897159669</v>
       </c>
       <c r="C196" t="n">
         <v>4.7086364</v>
@@ -4625,7 +4625,7 @@
         <v>37072</v>
       </c>
       <c r="B199" t="n">
-        <v>14.73176124903681</v>
+        <v>14.72948709415201</v>
       </c>
       <c r="C199" t="n">
         <v>4.4535714</v>
@@ -4720,7 +4720,7 @@
         <v>37164</v>
       </c>
       <c r="B202" t="n">
-        <v>14.7334832745088</v>
+        <v>14.73120066950214</v>
       </c>
       <c r="C202" t="n">
         <v>3.98285</v>
@@ -4815,7 +4815,7 @@
         <v>37256</v>
       </c>
       <c r="B205" t="n">
-        <v>14.7332486419189</v>
+        <v>14.73097282675764</v>
       </c>
       <c r="C205" t="n">
         <v>3.3448889</v>
@@ -4910,7 +4910,7 @@
         <v>37346</v>
       </c>
       <c r="B208" t="n">
-        <v>14.73549226978364</v>
+        <v>14.73315964685367</v>
       </c>
       <c r="C208" t="n">
         <v>3.3908</v>
@@ -5005,7 +5005,7 @@
         <v>37437</v>
       </c>
       <c r="B211" t="n">
-        <v>14.74040873923174</v>
+        <v>14.73815649268911</v>
       </c>
       <c r="C211" t="n">
         <v>3.464</v>
@@ -5100,7 +5100,7 @@
         <v>37529</v>
       </c>
       <c r="B214" t="n">
-        <v>14.74435188064792</v>
+        <v>14.742108942983</v>
       </c>
       <c r="C214" t="n">
         <v>3.3101429</v>
@@ -5195,7 +5195,7 @@
         <v>37621</v>
       </c>
       <c r="B217" t="n">
-        <v>14.7466062732196</v>
+        <v>14.74432778467833</v>
       </c>
       <c r="C217" t="n">
         <v>2.94105</v>
@@ -5290,7 +5290,7 @@
         <v>37711</v>
       </c>
       <c r="B220" t="n">
-        <v>14.74389763319038</v>
+        <v>14.74161291800352</v>
       </c>
       <c r="C220" t="n">
         <v>2.5299524</v>
@@ -5385,7 +5385,7 @@
         <v>37802</v>
       </c>
       <c r="B223" t="n">
-        <v>14.7446122775835</v>
+        <v>14.7422313471886</v>
       </c>
       <c r="C223" t="n">
         <v>2.1518571</v>
@@ -5480,7 +5480,7 @@
         <v>37894</v>
       </c>
       <c r="B226" t="n">
-        <v>14.75061872611091</v>
+        <v>14.74837777756162</v>
       </c>
       <c r="C226" t="n">
         <v>2.1473182</v>
@@ -5575,7 +5575,7 @@
         <v>37986</v>
       </c>
       <c r="B229" t="n">
-        <v>14.75730336984359</v>
+        <v>14.75507131053681</v>
       </c>
       <c r="C229" t="n">
         <v>2.1463333</v>
@@ -5670,7 +5670,7 @@
         <v>38077</v>
       </c>
       <c r="B232" t="n">
-        <v>14.76258927806883</v>
+        <v>14.76034237049351</v>
       </c>
       <c r="C232" t="n">
         <v>2.0288261</v>
@@ -5765,7 +5765,7 @@
         <v>38168</v>
       </c>
       <c r="B235" t="n">
-        <v>14.76897525598721</v>
+        <v>14.76674011802344</v>
       </c>
       <c r="C235" t="n">
         <v>2.1126818</v>
@@ -5860,7 +5860,7 @@
         <v>38260</v>
       </c>
       <c r="B238" t="n">
-        <v>14.77087372276797</v>
+        <v>14.76864359990905</v>
       </c>
       <c r="C238" t="n">
         <v>2.1185909</v>
@@ -5955,7 +5955,7 @@
         <v>38352</v>
       </c>
       <c r="B241" t="n">
-        <v>14.77537995484875</v>
+        <v>14.77301870057139</v>
       </c>
       <c r="C241" t="n">
         <v>2.1731739</v>
@@ -6050,7 +6050,7 @@
         <v>38442</v>
       </c>
       <c r="B244" t="n">
-        <v>14.77823049771406</v>
+        <v>14.7759906388514</v>
       </c>
       <c r="C244" t="n">
         <v>2.1371905</v>
@@ -6145,7 +6145,7 @@
         <v>38533</v>
       </c>
       <c r="B247" t="n">
-        <v>14.78449449389503</v>
+        <v>14.78221866271872</v>
       </c>
       <c r="C247" t="n">
         <v>2.1110455</v>
@@ -6240,7 +6240,7 @@
         <v>38625</v>
       </c>
       <c r="B250" t="n">
-        <v>14.79166594295179</v>
+        <v>14.78938037518371</v>
       </c>
       <c r="C250" t="n">
         <v>2.1391364</v>
@@ -6335,7 +6335,7 @@
         <v>38717</v>
       </c>
       <c r="B253" t="n">
-        <v>14.79880896011677</v>
+        <v>14.79654912656796</v>
       </c>
       <c r="C253" t="n">
         <v>2.4728571</v>
@@ -6430,7 +6430,7 @@
         <v>38807</v>
       </c>
       <c r="B256" t="n">
-        <v>14.80824597546377</v>
+        <v>14.80595684371727</v>
       </c>
       <c r="C256" t="n">
         <v>2.7226087</v>
@@ -6525,7 +6525,7 @@
         <v>38898</v>
       </c>
       <c r="B259" t="n">
-        <v>14.81936382491253</v>
+        <v>14.81702370425498</v>
       </c>
       <c r="C259" t="n">
         <v>2.9856818</v>
@@ -6620,7 +6620,7 @@
         <v>38990</v>
       </c>
       <c r="B262" t="n">
-        <v>14.82459277311528</v>
+        <v>14.82231500314845</v>
       </c>
       <c r="C262" t="n">
         <v>3.335381</v>
@@ -6715,7 +6715,7 @@
         <v>39082</v>
       </c>
       <c r="B265" t="n">
-        <v>14.83626166048727</v>
+        <v>14.8340569303562</v>
       </c>
       <c r="C265" t="n">
         <v>3.6842105</v>
@@ -6810,7 +6810,7 @@
         <v>39172</v>
       </c>
       <c r="B268" t="n">
-        <v>14.84343414518113</v>
+        <v>14.84121091278576</v>
       </c>
       <c r="C268" t="n">
         <v>3.8909091</v>
@@ -6905,7 +6905,7 @@
         <v>39263</v>
       </c>
       <c r="B271" t="n">
-        <v>14.8501775717117</v>
+        <v>14.84782655040185</v>
       </c>
       <c r="C271" t="n">
         <v>4.1477619</v>
@@ -7000,7 +7000,7 @@
         <v>39355</v>
       </c>
       <c r="B274" t="n">
-        <v>14.85383487022786</v>
+        <v>14.8514969131103</v>
       </c>
       <c r="C274" t="n">
         <v>4.7417</v>
@@ -7095,7 +7095,7 @@
         <v>39447</v>
       </c>
       <c r="B277" t="n">
-        <v>14.85904288308209</v>
+        <v>14.85681511576285</v>
       </c>
       <c r="C277" t="n">
         <v>4.8483684</v>
@@ -7190,7 +7190,7 @@
         <v>39538</v>
       </c>
       <c r="B280" t="n">
-        <v>14.86564327422434</v>
+        <v>14.86337968159768</v>
       </c>
       <c r="C280" t="n">
         <v>4.5963684</v>
@@ -7285,7 +7285,7 @@
         <v>39629</v>
       </c>
       <c r="B283" t="n">
-        <v>14.86065649110242</v>
+        <v>14.85835703913653</v>
       </c>
       <c r="C283" t="n">
         <v>4.9405238</v>
@@ -7380,7 +7380,7 @@
         <v>39721</v>
       </c>
       <c r="B286" t="n">
-        <v>14.85505484598567</v>
+        <v>14.85271704894418</v>
       </c>
       <c r="C286" t="n">
         <v>5.0191818</v>
@@ -7475,7 +7475,7 @@
         <v>39813</v>
       </c>
       <c r="B289" t="n">
-        <v>14.83783226868557</v>
+        <v>14.83565274343464</v>
       </c>
       <c r="C289" t="n">
         <v>3.292619</v>
@@ -7570,7 +7570,7 @@
         <v>39903</v>
       </c>
       <c r="B292" t="n">
-        <v>14.80677324293882</v>
+        <v>14.80461552261501</v>
       </c>
       <c r="C292" t="n">
         <v>1.6354545</v>
@@ -7665,7 +7665,7 @@
         <v>39994</v>
       </c>
       <c r="B295" t="n">
-        <v>14.80679717910562</v>
+        <v>14.80454106357828</v>
       </c>
       <c r="C295" t="n">
         <v>1.2279091</v>
@@ -7760,7 +7760,7 @@
         <v>40086</v>
       </c>
       <c r="B298" t="n">
-        <v>14.81036519385139</v>
+        <v>14.80808032068062</v>
       </c>
       <c r="C298" t="n">
         <v>0.7720909</v>
@@ -7855,7 +7855,7 @@
         <v>40178</v>
       </c>
       <c r="B301" t="n">
-        <v>14.81463538411868</v>
+        <v>14.81229286906175</v>
       </c>
       <c r="C301" t="n">
         <v>0.7120455</v>
@@ -7950,7 +7950,7 @@
         <v>40268</v>
       </c>
       <c r="B304" t="n">
-        <v>14.81871075496855</v>
+        <v>14.81629477960883</v>
       </c>
       <c r="C304" t="n">
         <v>0.6449565</v>
@@ -8045,7 +8045,7 @@
         <v>40359</v>
       </c>
       <c r="B307" t="n">
-        <v>14.82802323567593</v>
+        <v>14.82569512164075</v>
       </c>
       <c r="C307" t="n">
         <v>0.7275909</v>
@@ -8140,7 +8140,7 @@
         <v>40451</v>
       </c>
       <c r="B310" t="n">
-        <v>14.83237960498131</v>
+        <v>14.83020526075002</v>
       </c>
       <c r="C310" t="n">
         <v>0.8804999999999999</v>
@@ -8235,7 +8235,7 @@
         <v>40543</v>
       </c>
       <c r="B313" t="n">
-        <v>14.83812550099255</v>
+        <v>14.8360023736148</v>
       </c>
       <c r="C313" t="n">
         <v>1.0216957</v>
@@ -8330,7 +8330,7 @@
         <v>40633</v>
       </c>
       <c r="B316" t="n">
-        <v>14.84767733501041</v>
+        <v>14.84523471965953</v>
       </c>
       <c r="C316" t="n">
         <v>1.1755217</v>
@@ -8425,7 +8425,7 @@
         <v>40724</v>
       </c>
       <c r="B319" t="n">
-        <v>14.84775534726671</v>
+        <v>14.84554485335728</v>
       </c>
       <c r="C319" t="n">
         <v>1.4885909</v>
@@ -8520,7 +8520,7 @@
         <v>40816</v>
       </c>
       <c r="B322" t="n">
-        <v>14.84787224739182</v>
+        <v>14.84574332272363</v>
       </c>
       <c r="C322" t="n">
         <v>1.5364545</v>
@@ -8615,7 +8615,7 @@
         <v>40908</v>
       </c>
       <c r="B325" t="n">
-        <v>14.84481703332711</v>
+        <v>14.84268713670085</v>
       </c>
       <c r="C325" t="n">
         <v>1.4260952</v>
@@ -8710,7 +8710,7 @@
         <v>40999</v>
       </c>
       <c r="B328" t="n">
-        <v>14.84273804533222</v>
+        <v>14.84050231976047</v>
       </c>
       <c r="C328" t="n">
         <v>0.8584545</v>
@@ -8722,7 +8722,7 @@
         <v>4.542230386214217</v>
       </c>
       <c r="F328" t="n">
-        <v>4.598145571051127</v>
+        <v>4.597138014290827</v>
       </c>
       <c r="G328" t="n">
         <v>4.472780997942346</v>
@@ -8805,7 +8805,7 @@
         <v>41090</v>
       </c>
       <c r="B331" t="n">
-        <v>14.83916615544417</v>
+        <v>14.83697052720373</v>
       </c>
       <c r="C331" t="n">
         <v>0.6588571</v>
@@ -8900,7 +8900,7 @@
         <v>41182</v>
       </c>
       <c r="B334" t="n">
-        <v>14.83761178424063</v>
+        <v>14.83546401706878</v>
       </c>
       <c r="C334" t="n">
         <v>0.2463</v>
@@ -8995,7 +8995,7 @@
         <v>41274</v>
       </c>
       <c r="B337" t="n">
-        <v>14.83328488393849</v>
+        <v>14.83148559826941</v>
       </c>
       <c r="C337" t="n">
         <v>0.1854737</v>
@@ -9090,7 +9090,7 @@
         <v>41364</v>
       </c>
       <c r="B340" t="n">
-        <v>14.8302661973433</v>
+        <v>14.8283935201919</v>
       </c>
       <c r="C340" t="n">
         <v>0.20605</v>
@@ -9185,7 +9185,7 @@
         <v>41455</v>
       </c>
       <c r="B343" t="n">
-        <v>14.83700815369242</v>
+        <v>14.83531525366833</v>
       </c>
       <c r="C343" t="n">
         <v>0.21025</v>
@@ -9280,7 +9280,7 @@
         <v>41547</v>
       </c>
       <c r="B346" t="n">
-        <v>14.83954526679433</v>
+        <v>14.83785925022513</v>
       </c>
       <c r="C346" t="n">
         <v>0.2232381</v>
@@ -9375,7 +9375,7 @@
         <v>41639</v>
       </c>
       <c r="B349" t="n">
-        <v>14.84166548070914</v>
+        <v>14.84006732438519</v>
       </c>
       <c r="C349" t="n">
         <v>0.2735</v>
@@ -9470,7 +9470,7 @@
         <v>41729</v>
       </c>
       <c r="B352" t="n">
-        <v>14.84661636991319</v>
+        <v>14.84485197222049</v>
       </c>
       <c r="C352" t="n">
         <v>0.3053333</v>
@@ -9565,7 +9565,7 @@
         <v>41820</v>
       </c>
       <c r="B355" t="n">
-        <v>14.84905134793195</v>
+        <v>14.84717089105898</v>
       </c>
       <c r="C355" t="n">
         <v>0.2414286</v>
@@ -9660,7 +9660,7 @@
         <v>41912</v>
       </c>
       <c r="B358" t="n">
-        <v>14.85355987916528</v>
+        <v>14.85179773188037</v>
       </c>
       <c r="C358" t="n">
         <v>0.09709089999999999</v>
@@ -9755,7 +9755,7 @@
         <v>42004</v>
       </c>
       <c r="B361" t="n">
-        <v>14.85753478775617</v>
+        <v>14.85592022897781</v>
       </c>
       <c r="C361" t="n">
         <v>0.0809048</v>
@@ -9850,7 +9850,7 @@
         <v>42094</v>
       </c>
       <c r="B364" t="n">
-        <v>14.86545431506541</v>
+        <v>14.86371270600937</v>
       </c>
       <c r="C364" t="n">
         <v>0.0271818</v>
@@ -9945,7 +9945,7 @@
         <v>42185</v>
       </c>
       <c r="B367" t="n">
-        <v>14.86981687343376</v>
+        <v>14.86814508395178</v>
       </c>
       <c r="C367" t="n">
         <v>-0.0139091</v>
@@ -10040,7 +10040,7 @@
         <v>42277</v>
       </c>
       <c r="B370" t="n">
-        <v>14.87390986801318</v>
+        <v>14.87247968171065</v>
       </c>
       <c r="C370" t="n">
         <v>-0.0370455</v>
@@ -10135,7 +10135,7 @@
         <v>42369</v>
       </c>
       <c r="B373" t="n">
-        <v>14.87867896825107</v>
+        <v>14.87751321762999</v>
       </c>
       <c r="C373" t="n">
         <v>-0.1263182</v>
@@ -10230,7 +10230,7 @@
         <v>42460</v>
       </c>
       <c r="B376" t="n">
-        <v>14.88373679798353</v>
+        <v>14.88243301970313</v>
       </c>
       <c r="C376" t="n">
         <v>-0.2285238</v>
@@ -10325,7 +10325,7 @@
         <v>42551</v>
       </c>
       <c r="B379" t="n">
-        <v>14.88559589485</v>
+        <v>14.88439972555791</v>
       </c>
       <c r="C379" t="n">
         <v>-0.2679091</v>
@@ -10420,7 +10420,7 @@
         <v>42643</v>
       </c>
       <c r="B382" t="n">
-        <v>14.89056704096543</v>
+        <v>14.88950165065845</v>
       </c>
       <c r="C382" t="n">
         <v>-0.3016364</v>
@@ -10515,7 +10515,7 @@
         <v>42735</v>
       </c>
       <c r="B385" t="n">
-        <v>14.89856504928438</v>
+        <v>14.89753888985429</v>
       </c>
       <c r="C385" t="n">
         <v>-0.3157619</v>
@@ -10610,7 +10610,7 @@
         <v>42825</v>
       </c>
       <c r="B388" t="n">
-        <v>14.90621526394778</v>
+        <v>14.90515350878153</v>
       </c>
       <c r="C388" t="n">
         <v>-0.3293478</v>
@@ -10705,7 +10705,7 @@
         <v>42916</v>
       </c>
       <c r="B391" t="n">
-        <v>14.91308073715821</v>
+        <v>14.91197013120231</v>
       </c>
       <c r="C391" t="n">
         <v>-0.33</v>
@@ -10800,7 +10800,7 @@
         <v>43008</v>
       </c>
       <c r="B394" t="n">
-        <v>14.92076361450949</v>
+        <v>14.91980623222326</v>
       </c>
       <c r="C394" t="n">
         <v>-0.329381</v>
@@ -10895,7 +10895,7 @@
         <v>43100</v>
       </c>
       <c r="B397" t="n">
-        <v>14.92886727796077</v>
+        <v>14.92797673679345</v>
       </c>
       <c r="C397" t="n">
         <v>-0.3278947</v>
@@ -10990,7 +10990,7 @@
         <v>43190</v>
       </c>
       <c r="B400" t="n">
-        <v>14.9292114391288</v>
+        <v>14.92820190328119</v>
       </c>
       <c r="C400" t="n">
         <v>-0.3279048</v>
@@ -11085,7 +11085,7 @@
         <v>43281</v>
       </c>
       <c r="B403" t="n">
-        <v>14.93413326279648</v>
+        <v>14.93319347405587</v>
       </c>
       <c r="C403" t="n">
         <v>-0.3220476</v>
@@ -11180,7 +11180,7 @@
         <v>43373</v>
       </c>
       <c r="B406" t="n">
-        <v>14.9356834702308</v>
+        <v>14.93504393318707</v>
       </c>
       <c r="C406" t="n">
         <v>-0.31885</v>
@@ -11275,7 +11275,7 @@
         <v>43465</v>
       </c>
       <c r="B409" t="n">
-        <v>14.9407314436899</v>
+        <v>14.94045125878421</v>
       </c>
       <c r="C409" t="n">
         <v>-0.3118947</v>
@@ -11370,7 +11370,7 @@
         <v>43555</v>
       </c>
       <c r="B412" t="n">
-        <v>14.94828128086647</v>
+        <v>14.94760897536523</v>
       </c>
       <c r="C412" t="n">
         <v>-0.3091905</v>
@@ -11465,7 +11465,7 @@
         <v>43646</v>
       </c>
       <c r="B415" t="n">
-        <v>14.95147418538848</v>
+        <v>14.95095432964196</v>
       </c>
       <c r="C415" t="n">
         <v>-0.3289</v>
@@ -11560,7 +11560,7 @@
         <v>43738</v>
       </c>
       <c r="B418" t="n">
-        <v>14.95407684855603</v>
+        <v>14.95371006312793</v>
       </c>
       <c r="C418" t="n">
         <v>-0.4175714</v>
@@ -11655,7 +11655,7 @@
         <v>43830</v>
       </c>
       <c r="B421" t="n">
-        <v>14.95247770427171</v>
+        <v>14.9519562517649</v>
       </c>
       <c r="C421" t="n">
         <v>-0.3947</v>
@@ -11750,7 +11750,7 @@
         <v>43921</v>
       </c>
       <c r="B424" t="n">
-        <v>14.92051503963275</v>
+        <v>14.92034617482485</v>
       </c>
       <c r="C424" t="n">
         <v>-0.4166364</v>
@@ -11845,7 +11845,7 @@
         <v>44012</v>
       </c>
       <c r="B427" t="n">
-        <v>14.80253807449116</v>
+        <v>14.80207237339749</v>
       </c>
       <c r="C427" t="n">
         <v>-0.376</v>
@@ -11940,7 +11940,7 @@
         <v>44104</v>
       </c>
       <c r="B430" t="n">
-        <v>14.91158853798336</v>
+        <v>14.91125453696241</v>
       </c>
       <c r="C430" t="n">
         <v>-0.4913636</v>
@@ -12035,7 +12035,7 @@
         <v>44196</v>
       </c>
       <c r="B433" t="n">
-        <v>14.9143152614528</v>
+        <v>14.91440817258973</v>
       </c>
       <c r="C433" t="n">
         <v>-0.5380909</v>
@@ -12078,7 +12078,7 @@
         <v>4.607168188650764</v>
       </c>
       <c r="F434" t="n">
-        <v>4.588024027153121</v>
+        <v>4.589040804058207</v>
       </c>
       <c r="G434" t="n">
         <v>4.528289141652134</v>
@@ -12130,7 +12130,7 @@
         <v>44286</v>
       </c>
       <c r="B436" t="n">
-        <v>14.92328471491544</v>
+        <v>14.92311687879352</v>
       </c>
       <c r="C436" t="n">
         <v>-0.539087</v>
@@ -12225,7 +12225,7 @@
         <v>44377</v>
       </c>
       <c r="B439" t="n">
-        <v>14.94442237770282</v>
+        <v>14.9441760897247</v>
       </c>
       <c r="C439" t="n">
         <v>-0.5429091</v>
@@ -12268,7 +12268,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="F440" t="n">
-        <v>4.60816569496789</v>
+        <v>4.607168188650764</v>
       </c>
       <c r="G440" t="n">
         <v>4.617098756853365</v>
@@ -12320,7 +12320,7 @@
         <v>44469</v>
       </c>
       <c r="B442" t="n">
-        <v>14.96260093036375</v>
+        <v>14.96294897840894</v>
       </c>
       <c r="C442" t="n">
         <v>-0.5450455</v>
@@ -12363,7 +12363,7 @@
         <v>4.598145571051127</v>
       </c>
       <c r="F443" t="n">
-        <v>4.619073091157083</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="G443" t="n">
         <v>4.632785353021065</v>
@@ -12415,7 +12415,7 @@
         <v>44561</v>
       </c>
       <c r="B445" t="n">
-        <v>14.96976882101587</v>
+        <v>14.97002697974659</v>
       </c>
       <c r="C445" t="n">
         <v>-0.5819565</v>
@@ -12510,7 +12510,7 @@
         <v>44651</v>
       </c>
       <c r="B448" t="n">
-        <v>14.97733110836712</v>
+        <v>14.97746108521897</v>
       </c>
       <c r="C448" t="n">
         <v>-0.4954348</v>
@@ -12605,7 +12605,7 @@
         <v>44742</v>
       </c>
       <c r="B451" t="n">
-        <v>14.9867228180386</v>
+        <v>14.98682216519458</v>
       </c>
       <c r="C451" t="n">
         <v>-0.2392273</v>
@@ -12679,7 +12679,7 @@
         <v>4.630837932736669</v>
       </c>
       <c r="F453" t="n">
-        <v>4.623010104116422</v>
+        <v>4.623991940228679</v>
       </c>
       <c r="G453" t="n">
         <v>4.61512051684126</v>
@@ -12700,7 +12700,7 @@
         <v>44834</v>
       </c>
       <c r="B454" t="n">
-        <v>14.99213309024946</v>
+        <v>14.99222505737438</v>
       </c>
       <c r="C454" t="n">
         <v>1.0108636</v>
@@ -12743,7 +12743,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="F455" t="n">
-        <v>4.627909672957581</v>
+        <v>4.628886712605407</v>
       </c>
       <c r="G455" t="n">
         <v>4.61015772749913</v>
@@ -12795,7 +12795,7 @@
         <v>44926</v>
       </c>
       <c r="B457" t="n">
-        <v>14.99157993755498</v>
+        <v>14.9916006369467</v>
       </c>
       <c r="C457" t="n">
         <v>2.0634762</v>
@@ -12890,7 +12890,7 @@
         <v>45016</v>
       </c>
       <c r="B460" t="n">
-        <v>14.98965342069371</v>
+        <v>14.98970012216437</v>
       </c>
       <c r="C460" t="n">
         <v>2.9105652</v>
@@ -12985,7 +12985,7 @@
         <v>45107</v>
       </c>
       <c r="B463" t="n">
-        <v>14.99168932174032</v>
+        <v>14.991823737469</v>
       </c>
       <c r="C463" t="n">
         <v>3.5358636</v>
@@ -12997,7 +12997,7 @@
         <v>4.623010104116422</v>
       </c>
       <c r="F463" t="n">
-        <v>4.649187071404866</v>
+        <v>4.648229675448539</v>
       </c>
       <c r="G463" t="n">
         <v>4.606169686321175</v>
@@ -13080,7 +13080,7 @@
         <v>45199</v>
       </c>
       <c r="B466" t="n">
-        <v>14.99353840384202</v>
+        <v>14.99389859559869</v>
       </c>
       <c r="C466" t="n">
         <v>3.8800476</v>
@@ -13175,7 +13175,7 @@
         <v>45291</v>
       </c>
       <c r="B469" t="n">
-        <v>14.9936556704911</v>
+        <v>14.99446144898631</v>
       </c>
       <c r="C469" t="n">
         <v>3.9348947</v>
@@ -13270,7 +13270,7 @@
         <v>45382</v>
       </c>
       <c r="B472" t="n">
-        <v>14.99799277499076</v>
+        <v>14.99917400642879</v>
       </c>
       <c r="C472" t="n">
         <v>3.9231</v>
@@ -13365,7 +13365,7 @@
         <v>45473</v>
       </c>
       <c r="B475" t="n">
-        <v>15.00031491585883</v>
+        <v>15.00167256757779</v>
       </c>
       <c r="C475" t="n">
         <v>3.7245</v>
@@ -13408,7 +13408,7 @@
         <v>4.573679518896721</v>
       </c>
       <c r="F476" t="n">
-        <v>4.623991940228679</v>
+        <v>4.623010104116422</v>
       </c>
       <c r="G476" t="n">
         <v>4.609162207257629</v>
@@ -13439,7 +13439,7 @@
         <v>4.581901559048737</v>
       </c>
       <c r="F477" t="n">
-        <v>4.626931677769604</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="G477" t="n">
         <v>4.621043535144381</v>
@@ -13460,7 +13460,7 @@
         <v>45565</v>
       </c>
       <c r="B478" t="n">
-        <v>15.00568905682406</v>
+        <v>15.00722045930218</v>
       </c>
       <c r="C478" t="n">
         <v>3.4337143</v>
@@ -13472,7 +13472,7 @@
         <v>4.571613402459248</v>
       </c>
       <c r="F478" t="n">
-        <v>4.623991940228679</v>
+        <v>4.624972813284271</v>
       </c>
       <c r="G478" t="n">
         <v>4.625952725170619</v>
@@ -13534,7 +13534,7 @@
         <v>4.573679518896721</v>
       </c>
       <c r="F480" t="n">
-        <v>4.636668853047462</v>
+        <v>4.637637376125593</v>
       </c>
       <c r="G480" t="n">
         <v>4.622027303054514</v>
@@ -13555,7 +13555,7 @@
         <v>45657</v>
       </c>
       <c r="B481" t="n">
-        <v>15.00896146072162</v>
+        <v>15.01020681789196</v>
       </c>
       <c r="C481" t="n">
         <v>2.8246</v>
@@ -13650,7 +13650,7 @@
         <v>45747</v>
       </c>
       <c r="B484" t="n">
-        <v>15.01385327303958</v>
+        <v>15.01508803698453</v>
       </c>
       <c r="C484" t="n">
         <v>2.4424286</v>
@@ -13662,7 +13662,7 @@
         <v>4.620058798481842</v>
       </c>
       <c r="F484" t="n">
-        <v>4.653007515402251</v>
+        <v>4.653960350157523</v>
       </c>
       <c r="G484" t="n">
         <v>4.628886712605407</v>
@@ -13745,7 +13745,7 @@
         <v>45838</v>
       </c>
       <c r="B487" t="n">
-        <v>15.01419135428395</v>
+        <v>15.01535072469466</v>
       </c>
       <c r="C487" t="n">
         <v>1.983619</v>
@@ -13757,7 +13757,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F487" t="n">
-        <v>4.649187071404866</v>
+        <v>4.648229675448539</v>
       </c>
       <c r="G487" t="n">
         <v>4.639571612705423</v>
@@ -13788,7 +13788,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="F488" t="n">
-        <v>4.654912277882906</v>
+        <v>4.653960350157523</v>
       </c>
       <c r="G488" t="n">
         <v>4.638604962074329</v>
@@ -13819,7 +13819,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="F489" t="n">
-        <v>4.647271362006727</v>
+        <v>4.646312129319266</v>
       </c>
       <c r="G489" t="n">
         <v>4.638604962074329</v>
@@ -13840,7 +13840,7 @@
         <v>45930</v>
       </c>
       <c r="B490" t="n">
-        <v>15.01730027107971</v>
+        <v>15.01852123959857</v>
       </c>
       <c r="C490" t="n">
         <v>2.0272727</v>
@@ -13883,7 +13883,7 @@
         <v>4.589040804058207</v>
       </c>
       <c r="F491" t="n">
-        <v>4.653007515402251</v>
+        <v>4.653960350157523</v>
       </c>
       <c r="G491" t="n">
         <v>4.643428898105181</v>
@@ -13914,7 +13914,7 @@
         <v>4.593097604753822</v>
       </c>
       <c r="F492" t="n">
-        <v>4.642465970731788</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="G492" t="n">
         <v>4.644390899141372</v>
@@ -13935,7 +13935,7 @@
         <v>46022</v>
       </c>
       <c r="B493" t="n">
-        <v>15.01962842176857</v>
+        <v>15.02085655902386</v>
       </c>
       <c r="C493" t="n">
         <v>2.0484286</v>
@@ -14009,7 +14009,7 @@
         <v>4.579852378003801</v>
       </c>
       <c r="F495" t="n">
-        <v>4.627909672957581</v>
+        <v>4.628886712605407</v>
       </c>
       <c r="G495" t="n">
         <v>4.643428898105181</v>
@@ -14030,7 +14030,7 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>15.01952979121237</v>
+        <v>15.02087010032441</v>
       </c>
       <c r="C496" t="n">
         <v>2.1094091</v>
@@ -14042,7 +14042,7 @@
         <v>4.584967478670572</v>
       </c>
       <c r="F496" t="n">
-        <v>4.646312129319266</v>
+        <v>4.647271362006727</v>
       </c>
       <c r="G496" t="n">
         <v>4.651099117876491</v>
@@ -14073,7 +14073,7 @@
         <v>4.58700621536042</v>
       </c>
       <c r="F497" t="n">
-        <v>4.646312129319266</v>
+        <v>4.647271362006727</v>
       </c>
       <c r="G497" t="n">
         <v>4.647271362006727</v>
@@ -14104,7 +14104,7 @@
         <v>4.589040804058207</v>
       </c>
       <c r="F498" t="n">
-        <v>4.647271362006727</v>
+        <v>4.648229675448539</v>
       </c>
       <c r="G498" t="n">
         <v>4.649187071404866</v>
@@ -14125,7 +14125,7 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>15.02583978734803</v>
+        <v>15.02729934774091</v>
       </c>
       <c r="C499" t="n">
         <v>2.339</v>
@@ -14168,7 +14168,7 @@
         <v>4.584967478670572</v>
       </c>
       <c r="F500" t="n">
-        <v>4.631812116934513</v>
+        <v>4.633757642840004</v>
       </c>
       <c r="G500" t="n">
         <v>4.646312129319266</v>
@@ -14198,7 +14198,9 @@
       <c r="E501" t="n">
         <v>4.579852378003801</v>
       </c>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="n">
+        <v>4.652053771886941</v>
+      </c>
       <c r="G501" t="n">
         <v>4.647271362006727</v>
       </c>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,64 +435,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -495,7 +509,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -512,7 +526,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -529,7 +543,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -546,7 +560,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -563,7 +577,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -580,7 +594,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -597,7 +611,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -614,7 +628,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -631,7 +645,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -648,7 +662,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -665,7 +679,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -682,7 +696,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -699,7 +713,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -716,7 +730,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -733,7 +747,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -750,7 +764,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -767,7 +781,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -784,7 +798,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -801,7 +815,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -818,7 +832,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -835,7 +849,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -852,7 +866,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -869,7 +883,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -886,7 +900,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -903,7 +917,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -920,7 +934,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -937,7 +951,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -954,7 +968,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -971,7 +985,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -988,7 +1002,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1005,7 +1019,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1022,7 +1036,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1039,7 +1053,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1056,7 +1070,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1073,7 +1087,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1090,7 +1104,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1107,7 +1121,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1124,7 +1138,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1141,7 +1155,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1158,7 +1172,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1175,7 +1189,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1192,7 +1206,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1209,7 +1223,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1226,7 +1240,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1243,7 +1257,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1260,7 +1274,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1277,7 +1291,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1294,7 +1308,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1311,7 +1325,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1328,7 +1342,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1345,7 +1359,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1362,7 +1376,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1379,7 +1393,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1396,7 +1410,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1413,7 +1427,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1430,7 +1444,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1447,7 +1461,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1464,7 +1478,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1481,7 +1495,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1498,7 +1512,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1515,7 +1529,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1532,7 +1546,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1549,7 +1563,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1566,7 +1580,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1583,7 +1597,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1600,7 +1614,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1617,7 +1631,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1634,7 +1648,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1651,7 +1665,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1668,7 +1682,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1685,7 +1699,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1702,7 +1716,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1721,7 +1735,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1740,7 +1754,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1759,7 +1773,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1778,7 +1792,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1797,7 +1811,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1816,7 +1830,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -1835,7 +1849,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -1854,7 +1868,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1873,7 +1887,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1892,7 +1906,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1911,7 +1925,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -1930,7 +1944,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -1949,7 +1963,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -1968,7 +1982,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -1987,7 +2001,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2006,7 +2020,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2025,7 +2039,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -2044,7 +2058,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2063,7 +2077,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2082,7 +2096,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2101,7 +2115,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2120,7 +2134,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2139,7 +2153,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2158,7 +2172,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2177,7 +2191,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2196,7 +2210,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2215,7 +2229,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2234,7 +2248,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2253,7 +2267,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2272,7 +2286,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2291,7 +2305,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2310,7 +2324,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2329,7 +2343,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2348,7 +2362,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2367,7 +2381,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -2386,7 +2400,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2407,7 +2421,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2428,7 +2442,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -2449,7 +2463,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2470,7 +2484,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2491,7 +2505,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2512,7 +2526,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2533,7 +2547,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2554,7 +2568,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2575,7 +2589,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2596,7 +2610,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2617,7 +2631,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2638,7 +2652,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2661,7 +2675,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2684,7 +2698,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -2709,7 +2723,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -2732,7 +2746,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -2755,7 +2769,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -2780,7 +2794,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -2803,7 +2817,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -2826,7 +2840,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -2851,7 +2865,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -2874,7 +2888,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -2897,7 +2911,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -2922,7 +2936,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -2945,7 +2959,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -2968,7 +2982,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -2993,7 +3007,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3016,7 +3030,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3039,7 +3053,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3064,7 +3078,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3087,7 +3101,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3110,7 +3124,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3135,7 +3149,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3158,7 +3172,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3181,7 +3195,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3206,7 +3220,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3229,7 +3243,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3252,7 +3266,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3277,7 +3291,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3300,7 +3314,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3323,7 +3337,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3348,7 +3362,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3371,7 +3385,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3394,7 +3408,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3419,7 +3433,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -3442,7 +3456,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3465,7 +3479,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -3490,7 +3504,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3513,7 +3527,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -3536,7 +3550,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -3561,7 +3575,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3584,7 +3598,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -3607,7 +3621,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -3632,7 +3646,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -3655,7 +3669,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -3678,7 +3692,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -3703,7 +3717,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -3726,7 +3740,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -3749,7 +3763,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -3774,7 +3788,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -3799,7 +3813,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -3824,7 +3838,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -3851,7 +3865,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -3876,7 +3890,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -3901,7 +3915,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -3928,7 +3942,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -3953,7 +3967,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -3978,7 +3992,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4005,7 +4019,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4030,7 +4044,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4055,7 +4069,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4084,7 +4098,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4115,7 +4129,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4146,7 +4160,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4179,7 +4193,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4210,7 +4224,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4241,7 +4255,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4274,7 +4288,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -4305,7 +4319,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -4336,7 +4350,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -4369,7 +4383,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4400,7 +4414,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -4431,7 +4445,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -4464,7 +4478,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4495,7 +4509,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -4526,7 +4540,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -4559,7 +4573,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -4590,7 +4604,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -4621,7 +4635,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -4654,7 +4668,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -4685,7 +4699,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -4716,7 +4730,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -4749,7 +4763,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -4780,7 +4794,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -4811,7 +4825,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -4844,7 +4858,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -4875,7 +4889,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -4906,7 +4920,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -4939,7 +4953,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -4970,7 +4984,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5001,7 +5015,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5034,7 +5048,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5065,7 +5079,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5096,7 +5110,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5129,7 +5143,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5160,7 +5174,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5191,7 +5205,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5224,7 +5238,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5255,7 +5269,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5286,7 +5300,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -5319,7 +5333,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -5350,7 +5364,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -5381,7 +5395,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -5414,7 +5428,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -5445,7 +5459,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -5476,7 +5490,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -5509,7 +5523,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -5540,7 +5554,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -5571,7 +5585,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -5604,7 +5618,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -5635,7 +5649,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -5666,7 +5680,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -5699,7 +5713,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -5730,7 +5744,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -5761,7 +5775,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -5794,7 +5808,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -5825,7 +5839,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -5856,7 +5870,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -5889,7 +5903,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -5920,7 +5934,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -5951,7 +5965,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -5984,7 +5998,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6015,7 +6029,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6046,7 +6060,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6079,7 +6093,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6110,7 +6124,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6141,7 +6155,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6174,7 +6188,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6205,7 +6219,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6236,7 +6250,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6269,7 +6283,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -6300,7 +6314,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -6331,7 +6345,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -6364,7 +6378,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -6395,7 +6409,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -6426,7 +6440,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -6459,7 +6473,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -6490,7 +6504,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -6521,7 +6535,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -6554,7 +6568,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -6585,7 +6599,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -6616,7 +6630,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -6649,7 +6663,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -6680,7 +6694,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -6711,7 +6725,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -6744,7 +6758,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -6775,7 +6789,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -6806,7 +6820,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -6839,7 +6853,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -6870,7 +6884,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -6901,7 +6915,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -6934,7 +6948,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -6965,7 +6979,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -6996,7 +7010,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7029,7 +7043,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7060,7 +7074,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7091,7 +7105,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7124,7 +7138,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7155,7 +7169,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7186,7 +7200,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7219,7 +7233,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7250,7 +7264,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7281,7 +7295,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -7314,7 +7328,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -7345,7 +7359,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -7376,7 +7390,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -7409,7 +7423,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -7440,7 +7454,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -7471,7 +7485,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -7504,7 +7518,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -7535,7 +7549,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -7566,7 +7580,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -7599,7 +7613,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -7630,7 +7644,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -7661,7 +7675,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -7694,7 +7708,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -7725,7 +7739,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -7756,7 +7770,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -7789,7 +7803,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -7820,7 +7834,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -7851,7 +7865,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -7884,7 +7898,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -7915,7 +7929,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -7946,7 +7960,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -7979,7 +7993,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8010,7 +8024,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8041,7 +8055,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8074,7 +8088,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8105,7 +8119,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8136,7 +8150,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8169,7 +8183,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8200,7 +8214,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8231,7 +8245,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8264,7 +8278,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8295,7 +8309,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -8326,7 +8340,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -8359,7 +8373,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -8390,7 +8404,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -8421,7 +8435,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -8454,7 +8468,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -8485,7 +8499,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -8516,7 +8530,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -8549,7 +8563,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -8580,7 +8594,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -8611,7 +8625,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -8644,7 +8658,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -8675,7 +8689,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -8706,7 +8720,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -8739,7 +8753,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -8770,7 +8784,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -8801,7 +8815,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -8834,7 +8848,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -8865,7 +8879,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -8896,7 +8910,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -8929,7 +8943,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -8960,7 +8974,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -8991,7 +9005,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9024,7 +9038,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9055,7 +9069,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9086,7 +9100,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9119,7 +9133,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9150,7 +9164,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9181,7 +9195,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9214,7 +9228,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9245,7 +9259,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9276,7 +9290,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -9309,7 +9323,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -9340,7 +9354,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -9371,7 +9385,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -9404,7 +9418,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -9435,7 +9449,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -9466,7 +9480,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -9499,7 +9513,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -9530,7 +9544,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -9561,7 +9575,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -9594,7 +9608,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -9625,7 +9639,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -9656,7 +9670,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -9689,7 +9703,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -9720,7 +9734,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -9751,7 +9765,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -9784,7 +9798,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -9815,7 +9829,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -9846,7 +9860,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -9879,7 +9893,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -9910,7 +9924,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -9941,7 +9955,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -9974,7 +9988,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10005,7 +10019,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10036,7 +10050,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10069,7 +10083,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10100,7 +10114,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10131,7 +10145,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10164,7 +10178,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10195,7 +10209,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10226,7 +10240,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10259,7 +10273,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10290,7 +10304,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -10321,7 +10335,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -10354,7 +10368,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -10385,7 +10399,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -10416,7 +10430,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -10449,7 +10463,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -10480,7 +10494,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -10511,7 +10525,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -10544,7 +10558,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -10575,7 +10589,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -10606,7 +10620,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -10639,7 +10653,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -10670,7 +10684,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -10701,7 +10715,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -10734,7 +10748,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -10765,7 +10779,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -10796,7 +10810,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -10829,7 +10843,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -10860,7 +10874,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -10891,7 +10905,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -10924,7 +10938,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -10955,7 +10969,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -10986,7 +11000,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11019,7 +11033,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11050,7 +11064,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11081,7 +11095,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11114,7 +11128,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11145,7 +11159,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11176,7 +11190,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11209,7 +11223,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11240,7 +11254,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11271,7 +11285,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -11304,7 +11318,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -11335,7 +11349,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -11366,7 +11380,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -11399,7 +11413,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -11430,7 +11444,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -11461,7 +11475,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -11494,7 +11508,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -11525,7 +11539,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -11556,7 +11570,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -11589,7 +11603,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -11620,7 +11634,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -11651,7 +11665,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -11684,7 +11698,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -11715,7 +11729,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -11746,7 +11760,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -11779,7 +11793,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -11810,7 +11824,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -11841,7 +11855,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -11874,7 +11888,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -11905,7 +11919,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -11936,7 +11950,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -11969,7 +11983,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12000,7 +12014,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12031,7 +12045,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12064,7 +12078,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12095,7 +12109,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12126,7 +12140,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12159,7 +12173,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12190,7 +12204,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12221,7 +12235,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12254,7 +12268,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12285,7 +12299,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -12316,7 +12330,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -12349,7 +12363,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -12380,7 +12394,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -12411,7 +12425,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -12444,7 +12458,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -12475,7 +12489,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -12506,7 +12520,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -12539,7 +12553,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -12570,7 +12584,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -12601,7 +12615,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -12634,7 +12648,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -12665,7 +12679,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -12696,7 +12710,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -12729,7 +12743,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -12760,7 +12774,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -12791,7 +12805,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -12824,7 +12838,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -12855,7 +12869,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -12886,7 +12900,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -12919,7 +12933,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -12950,7 +12964,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -12981,7 +12995,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13014,7 +13028,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13045,7 +13059,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13076,7 +13090,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13109,7 +13123,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13140,7 +13154,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13171,7 +13185,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13204,7 +13218,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13235,7 +13249,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13266,7 +13280,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -13299,7 +13313,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -13330,7 +13344,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -13361,7 +13375,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -13394,7 +13408,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -13425,7 +13439,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -13456,7 +13470,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -13489,7 +13503,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -13520,7 +13534,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -13551,7 +13565,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -13584,7 +13598,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -13615,7 +13629,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -13646,7 +13660,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -13679,7 +13693,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -13710,7 +13724,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -13741,7 +13755,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -13774,7 +13788,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -13805,7 +13819,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -13836,7 +13850,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -13869,7 +13883,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -13900,7 +13914,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -13931,7 +13945,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -13964,7 +13978,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -13995,7 +14009,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14026,7 +14040,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14059,7 +14073,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14090,7 +14104,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14121,7 +14135,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14154,7 +14168,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14185,7 +14199,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14216,7 +14230,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>

--- a/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/EA_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K502"/>
+  <dimension ref="A1:K503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>4.52178857704904</v>
+        <v>4.520701029361642</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -719,7 +719,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>4.589040804058207</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -736,7 +736,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>4.590056548178043</v>
+        <v>4.589040804058207</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>4.654912277882906</v>
+        <v>4.653960350157523</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1365,7 +1365,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>4.71492104994721</v>
+        <v>4.714024590900173</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>4.722953221644475</v>
+        <v>4.722063937459591</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>4.523960130562548</v>
+        <v>4.522874943261261</v>
       </c>
       <c r="E88" t="n">
         <v>4.351567427189173</v>
@@ -2140,7 +2140,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>4.30406509320417</v>
+        <v>4.302712827954156</v>
       </c>
       <c r="E96" t="n">
         <v>4.305415532302042</v>
@@ -2235,7 +2235,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>4.290459441148391</v>
+        <v>4.289088639014612</v>
       </c>
       <c r="E101" t="n">
         <v>4.276666119016055</v>
@@ -2944,7 +2944,7 @@
         <v>5.81</v>
       </c>
       <c r="D134" t="n">
-        <v>4.55597994179732</v>
+        <v>4.554928969551344</v>
       </c>
       <c r="E134" t="n">
         <v>4.355425952876702</v>
@@ -3109,7 +3109,7 @@
         <v>5.08</v>
       </c>
       <c r="D141" t="n">
-        <v>4.553876891600541</v>
+        <v>4.552823705615882</v>
       </c>
       <c r="E141" t="n">
         <v>4.359269647551265</v>
@@ -3322,7 +3322,7 @@
         <v>4.3</v>
       </c>
       <c r="D150" t="n">
-        <v>4.652053771886941</v>
+        <v>4.651099117876491</v>
       </c>
       <c r="E150" t="n">
         <v>4.380775852772229</v>
@@ -3677,7 +3677,7 @@
         <v>3.93</v>
       </c>
       <c r="D165" t="n">
-        <v>4.72384171570559</v>
+        <v>4.722953221644475</v>
       </c>
       <c r="E165" t="n">
         <v>4.43438186500781</v>
@@ -4232,7 +4232,7 @@
         <v>4.3620455</v>
       </c>
       <c r="D186" t="n">
-        <v>4.776599301615622</v>
+        <v>4.775756486563625</v>
       </c>
       <c r="E186" t="n">
         <v>4.511957804265912</v>
@@ -4550,7 +4550,7 @@
         <v>4.7086364</v>
       </c>
       <c r="D196" t="n">
-        <v>4.689511334421843</v>
+        <v>4.688591794127164</v>
       </c>
       <c r="E196" t="n">
         <v>4.520701029361642</v>
@@ -4581,7 +4581,7 @@
         <v>4.682</v>
       </c>
       <c r="D197" t="n">
-        <v>4.658710952916121</v>
+        <v>4.657762636107262</v>
       </c>
       <c r="E197" t="n">
         <v>4.51085950651685</v>
@@ -4707,7 +4707,7 @@
         <v>4.3535217</v>
       </c>
       <c r="D201" t="n">
-        <v>4.606169686321175</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="E201" t="n">
         <v>4.519612297626445</v>
@@ -5025,7 +5025,7 @@
         <v>3.464</v>
       </c>
       <c r="D211" t="n">
-        <v>4.56746831880408</v>
+        <v>4.566429357671661</v>
       </c>
       <c r="E211" t="n">
         <v>4.511957804265912</v>
@@ -5056,7 +5056,7 @@
         <v>3.41</v>
       </c>
       <c r="D212" t="n">
-        <v>4.554928969551344</v>
+        <v>4.553876891600541</v>
       </c>
       <c r="E212" t="n">
         <v>4.503137460422939</v>
@@ -5182,7 +5182,7 @@
         <v>3.1241429</v>
       </c>
       <c r="D216" t="n">
-        <v>4.528289141652134</v>
+        <v>4.52720864451838</v>
       </c>
       <c r="E216" t="n">
         <v>4.51085950651685</v>
@@ -5721,7 +5721,7 @@
         <v>2.04875</v>
       </c>
       <c r="D233" t="n">
-        <v>4.603168183317418</v>
+        <v>4.602165676967792</v>
       </c>
       <c r="E233" t="n">
         <v>4.532599493153256</v>
@@ -5911,7 +5911,7 @@
         <v>2.1473333</v>
       </c>
       <c r="D239" t="n">
-        <v>4.616110126026426</v>
+        <v>4.61512051684126</v>
       </c>
       <c r="E239" t="n">
         <v>4.540098189244376</v>
@@ -6006,7 +6006,7 @@
         <v>2.1454286</v>
       </c>
       <c r="D242" t="n">
-        <v>4.611152257665639</v>
+        <v>4.61015772749913</v>
       </c>
       <c r="E242" t="n">
         <v>4.539030383483547</v>
@@ -6576,7 +6576,7 @@
         <v>3.1021905</v>
       </c>
       <c r="D260" t="n">
-        <v>4.695924549256556</v>
+        <v>4.695010889987881</v>
       </c>
       <c r="E260" t="n">
         <v>4.591071261608589</v>
@@ -6607,7 +6607,7 @@
         <v>3.2264783</v>
       </c>
       <c r="D261" t="n">
-        <v>4.700480365792417</v>
+        <v>4.699570861409576</v>
       </c>
       <c r="E261" t="n">
         <v>4.593097604753822</v>
@@ -7811,7 +7811,7 @@
         <v>0.7375</v>
       </c>
       <c r="D299" t="n">
-        <v>4.489759334476764</v>
+        <v>4.490881039585964</v>
       </c>
       <c r="E299" t="n">
         <v>4.467056883858457</v>
@@ -8697,7 +8697,7 @@
         <v>1.0482857</v>
       </c>
       <c r="D327" t="n">
-        <v>4.520701029361642</v>
+        <v>4.52178857704904</v>
       </c>
       <c r="E327" t="n">
         <v>4.544358046591334</v>
@@ -9058,7 +9058,7 @@
         <v>4.449685283147696</v>
       </c>
       <c r="H338" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="I338" t="n">
         <v>4.332705079341171</v>
@@ -10376,7 +10376,7 @@
         <v>-0.2945238</v>
       </c>
       <c r="D380" t="n">
-        <v>4.644390899141372</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="E380" t="n">
         <v>4.565389315976247</v>
@@ -10915,7 +10915,7 @@
         <v>-0.3278947</v>
       </c>
       <c r="D397" t="n">
-        <v>4.751864565138895</v>
+        <v>4.752727750345706</v>
       </c>
       <c r="E397" t="n">
         <v>4.633757642840004</v>
@@ -11167,7 +11167,7 @@
         <v>-0.319</v>
       </c>
       <c r="D405" t="n">
-        <v>4.709530201312334</v>
+        <v>4.708628894356321</v>
       </c>
       <c r="E405" t="n">
         <v>4.617098756853365</v>
@@ -11262,7 +11262,7 @@
         <v>-0.3163636</v>
       </c>
       <c r="D408" t="n">
-        <v>4.705920089088234</v>
+        <v>4.706823839714591</v>
       </c>
       <c r="E408" t="n">
         <v>4.598145571051127</v>
@@ -11485,7 +11485,7 @@
         <v>-0.3289</v>
       </c>
       <c r="D415" t="n">
-        <v>4.640537329825382</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="E415" t="n">
         <v>4.597138014290827</v>
@@ -11516,7 +11516,7 @@
         <v>-0.3648696</v>
       </c>
       <c r="D416" t="n">
-        <v>4.630837932736669</v>
+        <v>4.629862798578463</v>
       </c>
       <c r="E416" t="n">
         <v>4.59511985013459</v>
@@ -11706,7 +11706,7 @@
         <v>-0.3911364</v>
       </c>
       <c r="D422" t="n">
-        <v>4.65586330030361</v>
+        <v>4.65681341913993</v>
       </c>
       <c r="E422" t="n">
         <v>4.599152113662528</v>
@@ -11927,7 +11927,7 @@
         <v>-0.4797143</v>
       </c>
       <c r="D429" t="n">
-        <v>4.503137460422939</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="E429" t="n">
         <v>4.539030383483547</v>
@@ -12055,7 +12055,7 @@
         <v>-0.5380909</v>
       </c>
       <c r="D433" t="n">
-        <v>4.571613402459248</v>
+        <v>4.572646994282532</v>
       </c>
       <c r="E433" t="n">
         <v>4.591071261608589</v>
@@ -12402,7 +12402,7 @@
         <v>-0.5673636</v>
       </c>
       <c r="D444" t="n">
-        <v>4.766438333584214</v>
+        <v>4.767289035464526</v>
       </c>
       <c r="E444" t="n">
         <v>4.605170185988092</v>
@@ -12435,7 +12435,7 @@
         <v>-0.5819565</v>
       </c>
       <c r="D445" t="n">
-        <v>4.751000634199631</v>
+        <v>4.751864565138895</v>
       </c>
       <c r="E445" t="n">
         <v>4.624972813284271</v>
@@ -12604,7 +12604,7 @@
         <v>4.625952725170619</v>
       </c>
       <c r="H450" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I450" t="n">
         <v>4.501031146246946</v>
@@ -12656,7 +12656,7 @@
         <v>0.036619</v>
       </c>
       <c r="D452" t="n">
-        <v>4.601162164590552</v>
+        <v>4.600157644164547</v>
       </c>
       <c r="E452" t="n">
         <v>4.61015772749913</v>
@@ -12720,7 +12720,7 @@
         <v>1.0108636</v>
       </c>
       <c r="D454" t="n">
-        <v>4.554928969551344</v>
+        <v>4.553876891600541</v>
       </c>
       <c r="E454" t="n">
         <v>4.641502115235482</v>
@@ -12751,7 +12751,7 @@
         <v>1.4276667</v>
       </c>
       <c r="D455" t="n">
-        <v>4.544358046591334</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="E455" t="n">
         <v>4.631812116934513</v>
@@ -13005,7 +13005,7 @@
         <v>3.5358636</v>
       </c>
       <c r="D463" t="n">
-        <v>4.564348191467836</v>
+        <v>4.563305981889393</v>
       </c>
       <c r="E463" t="n">
         <v>4.623010104116422</v>
@@ -13036,7 +13036,7 @@
         <v>3.6718095</v>
       </c>
       <c r="D464" t="n">
-        <v>4.554928969551344</v>
+        <v>4.553876891600541</v>
       </c>
       <c r="E464" t="n">
         <v>4.59511985013459</v>
@@ -13131,7 +13131,7 @@
         <v>3.9676364</v>
       </c>
       <c r="D467" t="n">
-        <v>4.539030383483547</v>
+        <v>4.540098189244376</v>
       </c>
       <c r="E467" t="n">
         <v>4.583946549536464</v>
@@ -13195,7 +13195,7 @@
         <v>3.9348947</v>
       </c>
       <c r="D469" t="n">
-        <v>4.570578741218473</v>
+        <v>4.571613402459248</v>
       </c>
       <c r="E469" t="n">
         <v>4.591071261608589</v>
@@ -13352,7 +13352,7 @@
         <v>3.8126818</v>
       </c>
       <c r="D474" t="n">
-        <v>4.570578741218473</v>
+        <v>4.56954300834494</v>
       </c>
       <c r="E474" t="n">
         <v>4.564348191467836</v>
@@ -13511,7 +13511,7 @@
         <v>3.1666087</v>
       </c>
       <c r="D479" t="n">
-        <v>4.566429357671661</v>
+        <v>4.56746831880408</v>
       </c>
       <c r="E479" t="n">
         <v>4.573679518896721</v>
@@ -13575,7 +13575,7 @@
         <v>2.8246</v>
       </c>
       <c r="D481" t="n">
-        <v>4.540098189244376</v>
+        <v>4.541164856012179</v>
       </c>
       <c r="E481" t="n">
         <v>4.56954300834494</v>
@@ -13637,7 +13637,7 @@
         <v>2.52495</v>
       </c>
       <c r="D483" t="n">
-        <v>4.56746831880408</v>
+        <v>4.5685062016165</v>
       </c>
       <c r="E483" t="n">
         <v>4.594109238628667</v>
@@ -13827,7 +13827,7 @@
         <v>2.0210952</v>
       </c>
       <c r="D489" t="n">
-        <v>4.559126247486684</v>
+        <v>4.558078578454241</v>
       </c>
       <c r="E489" t="n">
         <v>4.592084946439436</v>
@@ -13860,7 +13860,7 @@
         <v>2.0272727</v>
       </c>
       <c r="D490" t="n">
-        <v>4.563305981889393</v>
+        <v>4.562262684976814</v>
       </c>
       <c r="E490" t="n">
         <v>4.585987366571318</v>
@@ -13891,7 +13891,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="E491" t="n">
         <v>4.589040804058207</v>
@@ -13922,7 +13922,7 @@
         <v>2.04165</v>
       </c>
       <c r="D492" t="n">
-        <v>4.575741375297279</v>
+        <v>4.576770711466393</v>
       </c>
       <c r="E492" t="n">
         <v>4.593097604753822</v>
@@ -13955,7 +13955,7 @@
         <v>2.0484286</v>
       </c>
       <c r="D493" t="n">
-        <v>4.572646994282532</v>
+        <v>4.573679518896721</v>
       </c>
       <c r="E493" t="n">
         <v>4.589040804058207</v>
@@ -14112,7 +14112,7 @@
         <v>2.2261</v>
       </c>
       <c r="D498" t="n">
-        <v>4.546481189639412</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="E498" t="n">
         <v>4.589040804058207</v>
@@ -14145,7 +14145,7 @@
         <v>2.339</v>
       </c>
       <c r="D499" t="n">
-        <v>4.560172820057356</v>
+        <v>4.559126247486684</v>
       </c>
       <c r="E499" t="n">
         <v>4.588024027153121</v>
@@ -14176,7 +14176,7 @@
         <v>2.4253913</v>
       </c>
       <c r="D500" t="n">
-        <v>4.575741375297279</v>
+        <v>4.574710978503383</v>
       </c>
       <c r="E500" t="n">
         <v>4.584967478670572</v>
@@ -14188,7 +14188,7 @@
         <v>4.646312129319266</v>
       </c>
       <c r="H500" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I500" t="n">
         <v>4.637153231841142</v>
@@ -14207,7 +14207,7 @@
         <v>2.5131429</v>
       </c>
       <c r="D501" t="n">
-        <v>4.589040804058207</v>
+        <v>4.58700621536042</v>
       </c>
       <c r="E501" t="n">
         <v>4.579852378003801</v>
@@ -14219,7 +14219,7 @@
         <v>4.647271362006727</v>
       </c>
       <c r="H501" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I501" t="n">
         <v>4.641405678570186</v>
@@ -14233,17 +14233,21 @@
       <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="n">
+        <v>15.03144340499226</v>
+      </c>
       <c r="C502" t="n">
         <v>2.6350455</v>
       </c>
       <c r="D502" t="n">
-        <v>4.583946549536464</v>
+        <v>4.579852378003801</v>
       </c>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
+      <c r="H502" t="n">
+        <v>6.5</v>
+      </c>
       <c r="I502" t="n">
         <v>4.647463098178343</v>
       </c>
@@ -14251,6 +14255,23 @@
         <v>4.596689494135473</v>
       </c>
       <c r="K502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="n">
+        <v>4.573679518896721</v>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
